--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:42:29+00:00</t>
+    <t>2024-03-04T16:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3296,13 +3296,13 @@
     <t>Practitioner.qualification:exercicePro.period.start</t>
   </si>
   <si>
+    <t>[Donnée restreinte] : Date à partir de laquelle le professionnel exerce cette profession (dateEffetExercice).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.end</t>
+  </si>
+  <si>
     <t>[Donnée restreinte] : Date à partir de laquelle le professionnel n’exerce plus cette profession (dateFinEffetExercice).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.period.end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
   </si>
   <si>
     <t>Practitioner.qualification:exercicePro.issuer</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T10:45:14+00:00</t>
+    <t>2024-03-07T10:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -17338,7 +17338,7 @@
         <v>75</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>73</v>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11057" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="978">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -842,8 +842,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -1711,7 +1711,19 @@
     <t>Practitioner.identifier:identifiantInterne.period</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
     <t>Practitioner.identifier:identifiantInterne.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Practitioner.active</t>
@@ -6072,7 +6084,7 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>119</v>
@@ -6084,7 +6096,7 @@
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -6189,7 +6201,7 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>119</v>
@@ -6419,7 +6431,7 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>119</v>
@@ -6649,7 +6661,7 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>102</v>
@@ -6766,7 +6778,7 @@
         <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>119</v>
@@ -6996,7 +7008,7 @@
         <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>119</v>
@@ -7226,7 +7238,7 @@
         <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>102</v>
@@ -7343,7 +7355,7 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>119</v>
@@ -7573,7 +7585,7 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>119</v>
@@ -7805,7 +7817,7 @@
         <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>102</v>
@@ -8037,7 +8049,7 @@
         <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>119</v>
@@ -8049,7 +8061,7 @@
         <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -8390,7 +8402,7 @@
         <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>119</v>
@@ -8620,7 +8632,7 @@
         <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>119</v>
@@ -8850,7 +8862,7 @@
         <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>102</v>
@@ -8967,7 +8979,7 @@
         <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>119</v>
@@ -9197,7 +9209,7 @@
         <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>119</v>
@@ -9427,7 +9439,7 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
@@ -9544,7 +9556,7 @@
         <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>119</v>
@@ -9774,7 +9786,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>119</v>
@@ -10006,7 +10018,7 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -10238,7 +10250,7 @@
         <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>102</v>
@@ -10587,7 +10599,7 @@
         <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>119</v>
@@ -10599,7 +10611,7 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -10704,7 +10716,7 @@
         <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>119</v>
@@ -10934,7 +10946,7 @@
         <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>119</v>
@@ -11164,7 +11176,7 @@
         <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>102</v>
@@ -11281,7 +11293,7 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>119</v>
@@ -11511,7 +11523,7 @@
         <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>119</v>
@@ -11743,7 +11755,7 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -11975,7 +11987,7 @@
         <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>119</v>
@@ -11987,7 +11999,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -12328,7 +12340,7 @@
         <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>119</v>
@@ -12558,7 +12570,7 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>119</v>
@@ -12788,7 +12800,7 @@
         <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>102</v>
@@ -12905,7 +12917,7 @@
         <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>119</v>
@@ -13135,7 +13147,7 @@
         <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>119</v>
@@ -13365,7 +13377,7 @@
         <v>90</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>102</v>
@@ -13597,7 +13609,7 @@
         <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>102</v>
@@ -19816,7 +19828,7 @@
         <v>80</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>119</v>
@@ -19828,7 +19840,7 @@
         <v>78</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>78</v>
@@ -19935,7 +19947,7 @@
         <v>90</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>102</v>
@@ -20054,7 +20066,7 @@
         <v>90</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>102</v>
@@ -20171,7 +20183,7 @@
         <v>90</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>102</v>
@@ -20288,7 +20300,7 @@
         <v>90</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>102</v>
@@ -20345,7 +20357,9 @@
       <c r="M146" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="N146" s="2"/>
+      <c r="N146" t="s" s="2">
+        <v>542</v>
+      </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -20403,10 +20417,10 @@
         <v>90</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>102</v>
+        <v>543</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>78</v>
@@ -20426,7 +20440,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>475</v>
@@ -20520,10 +20534,10 @@
         <v>90</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>102</v>
+        <v>545</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>78</v>
@@ -20543,10 +20557,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20572,67 +20586,67 @@
         <v>297</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="N148" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="P148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q148" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="R148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF148" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="P148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q148" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="R148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20653,21 +20667,21 @@
         <v>78</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20690,19 +20704,19 @@
         <v>78</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>78</v>
@@ -20751,7 +20765,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20769,13 +20783,13 @@
         <v>78</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>78</v>
@@ -20783,10 +20797,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20898,10 +20912,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21015,13 +21029,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>78</v>
@@ -21043,13 +21057,13 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21132,10 +21146,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21161,16 +21175,16 @@
         <v>176</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>78</v>
@@ -21199,7 +21213,7 @@
       </c>
       <c r="Y153" s="2"/>
       <c r="Z153" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>78</v>
@@ -21217,7 +21231,7 @@
         <v>78</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -21235,13 +21249,13 @@
         <v>78</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>78</v>
@@ -21249,10 +21263,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21278,16 +21292,16 @@
         <v>104</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>78</v>
@@ -21336,7 +21350,7 @@
         <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21354,10 +21368,10 @@
         <v>78</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>78</v>
@@ -21368,14 +21382,14 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -21397,13 +21411,13 @@
         <v>104</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21453,7 +21467,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21471,13 +21485,13 @@
         <v>78</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>78</v>
@@ -21485,14 +21499,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -21514,13 +21528,13 @@
         <v>104</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -21570,7 +21584,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21588,13 +21602,13 @@
         <v>78</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>78</v>
@@ -21602,10 +21616,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21631,10 +21645,10 @@
         <v>104</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -21664,10 +21678,10 @@
         <v>158</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>78</v>
@@ -21685,7 +21699,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21703,13 +21717,13 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>78</v>
@@ -21717,10 +21731,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21746,10 +21760,10 @@
         <v>104</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -21779,10 +21793,10 @@
         <v>158</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>78</v>
@@ -21800,7 +21814,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21818,10 +21832,10 @@
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>78</v>
@@ -21832,10 +21846,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21861,14 +21875,14 @@
         <v>253</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
@@ -21917,7 +21931,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21935,10 +21949,10 @@
         <v>78</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>474</v>
@@ -21949,10 +21963,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21975,19 +21989,19 @@
         <v>78</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>78</v>
@@ -22024,17 +22038,17 @@
         <v>78</v>
       </c>
       <c r="AB160" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AC160" s="2"/>
       <c r="AD160" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE160" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -22046,19 +22060,19 @@
         <v>209</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>78</v>
@@ -22066,13 +22080,13 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>78</v>
@@ -22094,19 +22108,19 @@
         <v>78</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>78</v>
@@ -22155,7 +22169,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -22167,19 +22181,19 @@
         <v>209</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>78</v>
@@ -22187,10 +22201,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22302,10 +22316,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22419,13 +22433,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>78</v>
@@ -22447,13 +22461,13 @@
         <v>78</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -22536,10 +22550,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22651,10 +22665,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22766,10 +22780,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22809,7 +22823,7 @@
       </c>
       <c r="Q167" s="2"/>
       <c r="R167" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="S167" t="s" s="2">
         <v>78</v>
@@ -22883,10 +22897,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22927,7 +22941,7 @@
         <v>78</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>78</v>
@@ -22946,7 +22960,7 @@
       </c>
       <c r="Y168" s="2"/>
       <c r="Z168" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>78</v>
@@ -22996,13 +23010,13 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>78</v>
@@ -23024,13 +23038,13 @@
         <v>78</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23113,10 +23127,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23228,10 +23242,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23322,7 +23336,7 @@
         <v>80</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>119</v>
@@ -23334,7 +23348,7 @@
         <v>78</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>78</v>
@@ -23345,10 +23359,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C172" t="s" s="2">
         <v>312</v>
@@ -23376,7 +23390,7 @@
         <v>111</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>202</v>
@@ -23439,7 +23453,7 @@
         <v>80</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>119</v>
@@ -23462,10 +23476,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23577,10 +23591,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23669,7 +23683,7 @@
         <v>80</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>119</v>
@@ -23692,10 +23706,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23809,10 +23823,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23872,7 +23886,7 @@
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>78</v>
@@ -23899,7 +23913,7 @@
         <v>90</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>102</v>
@@ -23922,13 +23936,13 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>78</v>
@@ -23953,7 +23967,7 @@
         <v>111</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="M177" t="s" s="2">
         <v>202</v>
@@ -24016,7 +24030,7 @@
         <v>80</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>119</v>
@@ -24039,10 +24053,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24154,10 +24168,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24246,7 +24260,7 @@
         <v>80</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>119</v>
@@ -24269,10 +24283,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24312,7 +24326,7 @@
       </c>
       <c r="Q180" s="2"/>
       <c r="R180" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>78</v>
@@ -24386,10 +24400,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24478,7 +24492,7 @@
         <v>90</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>102</v>
@@ -24501,13 +24515,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>78</v>
@@ -24595,7 +24609,7 @@
         <v>80</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>119</v>
@@ -24618,10 +24632,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24733,10 +24747,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24825,7 +24839,7 @@
         <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>119</v>
@@ -24848,10 +24862,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24891,7 +24905,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>78</v>
@@ -24965,10 +24979,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25057,7 +25071,7 @@
         <v>90</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>102</v>
@@ -25080,13 +25094,13 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="D187" t="s" s="2">
         <v>78</v>
@@ -25111,7 +25125,7 @@
         <v>111</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="M187" t="s" s="2">
         <v>202</v>
@@ -25174,7 +25188,7 @@
         <v>80</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>119</v>
@@ -25197,10 +25211,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25312,10 +25326,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25404,7 +25418,7 @@
         <v>80</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>119</v>
@@ -25427,10 +25441,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25470,7 +25484,7 @@
       </c>
       <c r="Q190" s="2"/>
       <c r="R190" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="S190" t="s" s="2">
         <v>78</v>
@@ -25544,10 +25558,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25636,7 +25650,7 @@
         <v>90</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>102</v>
@@ -25659,13 +25673,13 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D192" t="s" s="2">
         <v>78</v>
@@ -25753,7 +25767,7 @@
         <v>80</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ192" t="s" s="2">
         <v>119</v>
@@ -25776,10 +25790,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25891,10 +25905,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25983,7 +25997,7 @@
         <v>80</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ194" t="s" s="2">
         <v>119</v>
@@ -26006,10 +26020,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26049,7 +26063,7 @@
       </c>
       <c r="Q195" s="2"/>
       <c r="R195" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="S195" t="s" s="2">
         <v>78</v>
@@ -26123,10 +26137,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26215,7 +26229,7 @@
         <v>90</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ196" t="s" s="2">
         <v>102</v>
@@ -26238,13 +26252,13 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D197" t="s" s="2">
         <v>78</v>
@@ -26269,7 +26283,7 @@
         <v>111</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="M197" t="s" s="2">
         <v>202</v>
@@ -26332,7 +26346,7 @@
         <v>80</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>119</v>
@@ -26355,10 +26369,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26470,10 +26484,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26562,7 +26576,7 @@
         <v>80</v>
       </c>
       <c r="AI199" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ199" t="s" s="2">
         <v>119</v>
@@ -26585,10 +26599,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26628,7 +26642,7 @@
       </c>
       <c r="Q200" s="2"/>
       <c r="R200" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="S200" t="s" s="2">
         <v>78</v>
@@ -26702,10 +26716,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26794,7 +26808,7 @@
         <v>90</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ201" t="s" s="2">
         <v>102</v>
@@ -26817,13 +26831,13 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>78</v>
@@ -26848,7 +26862,7 @@
         <v>111</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="M202" t="s" s="2">
         <v>202</v>
@@ -26911,7 +26925,7 @@
         <v>80</v>
       </c>
       <c r="AI202" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ202" t="s" s="2">
         <v>119</v>
@@ -26934,10 +26948,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27049,10 +27063,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27141,7 +27155,7 @@
         <v>80</v>
       </c>
       <c r="AI204" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ204" t="s" s="2">
         <v>119</v>
@@ -27164,10 +27178,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27207,7 +27221,7 @@
       </c>
       <c r="Q205" s="2"/>
       <c r="R205" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="S205" t="s" s="2">
         <v>78</v>
@@ -27281,10 +27295,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27373,7 +27387,7 @@
         <v>90</v>
       </c>
       <c r="AI206" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ206" t="s" s="2">
         <v>102</v>
@@ -27396,10 +27410,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27439,7 +27453,7 @@
       </c>
       <c r="Q207" s="2"/>
       <c r="R207" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="S207" t="s" s="2">
         <v>78</v>
@@ -27513,10 +27527,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27605,7 +27619,7 @@
         <v>90</v>
       </c>
       <c r="AI208" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ208" t="s" s="2">
         <v>102</v>
@@ -27628,10 +27642,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27657,10 +27671,10 @@
         <v>176</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -27672,7 +27686,7 @@
         <v>78</v>
       </c>
       <c r="S209" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="T209" t="s" s="2">
         <v>78</v>
@@ -27690,10 +27704,10 @@
         <v>236</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>78</v>
@@ -27711,7 +27725,7 @@
         <v>78</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
@@ -27720,7 +27734,7 @@
         <v>90</v>
       </c>
       <c r="AI209" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="AJ209" t="s" s="2">
         <v>102</v>
@@ -27729,13 +27743,13 @@
         <v>78</v>
       </c>
       <c r="AL209" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="AM209" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>78</v>
@@ -27743,10 +27757,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27772,16 +27786,16 @@
         <v>104</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>78</v>
@@ -27830,7 +27844,7 @@
         <v>78</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>79</v>
@@ -27848,10 +27862,10 @@
         <v>78</v>
       </c>
       <c r="AL210" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="AM210" t="s" s="2">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="AN210" t="s" s="2">
         <v>467</v>
@@ -27862,10 +27876,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27891,16 +27905,16 @@
         <v>176</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>78</v>
@@ -27928,10 +27942,10 @@
         <v>236</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>78</v>
@@ -27949,7 +27963,7 @@
         <v>78</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>79</v>
@@ -27967,13 +27981,13 @@
         <v>78</v>
       </c>
       <c r="AL211" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="AM211" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>78</v>
@@ -27981,10 +27995,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28007,16 +28021,16 @@
         <v>91</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
@@ -28066,7 +28080,7 @@
         <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
@@ -28098,10 +28112,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28127,10 +28141,10 @@
         <v>253</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -28181,7 +28195,7 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>79</v>
@@ -28202,7 +28216,7 @@
         <v>199</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AN213" t="s" s="2">
         <v>474</v>
@@ -28213,10 +28227,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28239,19 +28253,19 @@
         <v>78</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="O214" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -28300,7 +28314,7 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
@@ -28318,13 +28332,13 @@
         <v>78</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>78</v>
@@ -28332,10 +28346,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28361,14 +28375,14 @@
         <v>176</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>78</v>
@@ -28396,10 +28410,10 @@
         <v>236</v>
       </c>
       <c r="Y215" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="Z215" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>78</v>
@@ -28417,7 +28431,7 @@
         <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -28435,13 +28449,13 @@
         <v>78</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>78</v>
@@ -28449,10 +28463,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28475,17 +28489,17 @@
         <v>91</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" t="s" s="2">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>78</v>
@@ -28534,7 +28548,7 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28552,13 +28566,13 @@
         <v>78</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>78</v>
@@ -28566,10 +28580,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28592,17 +28606,17 @@
         <v>78</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
@@ -28651,7 +28665,7 @@
         <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>
@@ -28672,10 +28686,10 @@
         <v>78</v>
       </c>
       <c r="AM217" t="s" s="2">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>78</v>
@@ -28683,10 +28697,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28709,13 +28723,13 @@
         <v>78</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -28754,7 +28768,7 @@
         <v>78</v>
       </c>
       <c r="AB218" t="s" s="2">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="AC218" s="2"/>
       <c r="AD218" t="s" s="2">
@@ -28764,7 +28778,7 @@
         <v>117</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>79</v>
@@ -28782,13 +28796,13 @@
         <v>78</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="AM218" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="AO218" t="s" s="2">
         <v>78</v>
@@ -28796,10 +28810,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -28911,10 +28925,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29028,14 +29042,14 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="E221" s="2"/>
       <c r="F221" t="s" s="2">
@@ -29057,10 +29071,10 @@
         <v>111</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="N221" t="s" s="2">
         <v>114</v>
@@ -29115,7 +29129,7 @@
         <v>78</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>79</v>
@@ -29147,10 +29161,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29176,14 +29190,14 @@
         <v>362</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>78</v>
@@ -29232,7 +29246,7 @@
         <v>78</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>79</v>
@@ -29253,7 +29267,7 @@
         <v>78</v>
       </c>
       <c r="AM222" t="s" s="2">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="AN222" t="s" s="2">
         <v>78</v>
@@ -29264,10 +29278,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29293,10 +29307,10 @@
         <v>233</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -29327,25 +29341,25 @@
       </c>
       <c r="Y223" s="2"/>
       <c r="Z223" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="AA223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE223" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF223" t="s" s="2">
         <v>824</v>
-      </c>
-      <c r="AA223" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB223" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC223" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD223" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE223" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF223" t="s" s="2">
-        <v>821</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>90</v>
@@ -29366,10 +29380,10 @@
         <v>78</v>
       </c>
       <c r="AM223" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="AO223" t="s" s="2">
         <v>78</v>
@@ -29377,10 +29391,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29406,14 +29420,14 @@
         <v>253</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" t="s" s="2">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>78</v>
@@ -29462,7 +29476,7 @@
         <v>78</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>79</v>
@@ -29483,10 +29497,10 @@
         <v>78</v>
       </c>
       <c r="AM224" t="s" s="2">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>78</v>
@@ -29494,10 +29508,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29523,10 +29537,10 @@
         <v>476</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -29577,7 +29591,7 @@
         <v>78</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>79</v>
@@ -29598,7 +29612,7 @@
         <v>78</v>
       </c>
       <c r="AM225" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="AN225" t="s" s="2">
         <v>78</v>
@@ -29609,13 +29623,13 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="D226" t="s" s="2">
         <v>78</v>
@@ -29637,13 +29651,13 @@
         <v>78</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -29694,7 +29708,7 @@
         <v>78</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>79</v>
@@ -29712,13 +29726,13 @@
         <v>78</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="AM226" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="AN226" t="s" s="2">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="AO226" t="s" s="2">
         <v>78</v>
@@ -29726,10 +29740,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -29841,10 +29855,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -29954,13 +29968,13 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="D229" t="s" s="2">
         <v>78</v>
@@ -29982,13 +29996,13 @@
         <v>78</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -30071,10 +30085,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30186,10 +30200,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30280,7 +30294,7 @@
         <v>80</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ231" t="s" s="2">
         <v>119</v>
@@ -30292,7 +30306,7 @@
         <v>78</v>
       </c>
       <c r="AM231" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN231" t="s" s="2">
         <v>78</v>
@@ -30303,13 +30317,13 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D232" t="s" s="2">
         <v>78</v>
@@ -30397,7 +30411,7 @@
         <v>80</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>119</v>
@@ -30420,10 +30434,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30535,10 +30549,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30627,7 +30641,7 @@
         <v>80</v>
       </c>
       <c r="AI234" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ234" t="s" s="2">
         <v>119</v>
@@ -30650,10 +30664,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30693,7 +30707,7 @@
       </c>
       <c r="Q235" s="2"/>
       <c r="R235" t="s" s="2">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="S235" t="s" s="2">
         <v>78</v>
@@ -30767,10 +30781,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -30830,7 +30844,7 @@
       </c>
       <c r="Y236" s="2"/>
       <c r="Z236" t="s" s="2">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="AA236" t="s" s="2">
         <v>78</v>
@@ -30857,7 +30871,7 @@
         <v>90</v>
       </c>
       <c r="AI236" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ236" t="s" s="2">
         <v>102</v>
@@ -30880,13 +30894,13 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="D237" t="s" s="2">
         <v>78</v>
@@ -30974,7 +30988,7 @@
         <v>80</v>
       </c>
       <c r="AI237" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ237" t="s" s="2">
         <v>119</v>
@@ -30997,10 +31011,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -31112,10 +31126,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31204,7 +31218,7 @@
         <v>80</v>
       </c>
       <c r="AI239" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ239" t="s" s="2">
         <v>119</v>
@@ -31227,10 +31241,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31270,7 +31284,7 @@
       </c>
       <c r="Q240" s="2"/>
       <c r="R240" t="s" s="2">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="S240" t="s" s="2">
         <v>78</v>
@@ -31344,10 +31358,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31407,7 +31421,7 @@
       </c>
       <c r="Y241" s="2"/>
       <c r="Z241" t="s" s="2">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="AA241" t="s" s="2">
         <v>78</v>
@@ -31434,7 +31448,7 @@
         <v>90</v>
       </c>
       <c r="AI241" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ241" t="s" s="2">
         <v>102</v>
@@ -31457,13 +31471,13 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="D242" t="s" s="2">
         <v>78</v>
@@ -31551,7 +31565,7 @@
         <v>80</v>
       </c>
       <c r="AI242" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ242" t="s" s="2">
         <v>119</v>
@@ -31574,10 +31588,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31689,10 +31703,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31781,7 +31795,7 @@
         <v>80</v>
       </c>
       <c r="AI244" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ244" t="s" s="2">
         <v>119</v>
@@ -31804,10 +31818,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -31847,7 +31861,7 @@
       </c>
       <c r="Q245" s="2"/>
       <c r="R245" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="S245" t="s" s="2">
         <v>78</v>
@@ -31921,10 +31935,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -31984,7 +31998,7 @@
       </c>
       <c r="Y246" s="2"/>
       <c r="Z246" t="s" s="2">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>78</v>
@@ -32011,7 +32025,7 @@
         <v>90</v>
       </c>
       <c r="AI246" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ246" t="s" s="2">
         <v>102</v>
@@ -32034,10 +32048,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32077,7 +32091,7 @@
       </c>
       <c r="Q247" s="2"/>
       <c r="R247" t="s" s="2">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="S247" t="s" s="2">
         <v>78</v>
@@ -32151,10 +32165,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32243,7 +32257,7 @@
         <v>90</v>
       </c>
       <c r="AI248" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ248" t="s" s="2">
         <v>102</v>
@@ -32266,14 +32280,14 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="E249" s="2"/>
       <c r="F249" t="s" s="2">
@@ -32295,10 +32309,10 @@
         <v>111</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="N249" t="s" s="2">
         <v>114</v>
@@ -32353,7 +32367,7 @@
         <v>78</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>79</v>
@@ -32385,10 +32399,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32414,14 +32428,14 @@
         <v>362</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" t="s" s="2">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="P250" t="s" s="2">
         <v>78</v>
@@ -32470,7 +32484,7 @@
         <v>78</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>79</v>
@@ -32491,7 +32505,7 @@
         <v>78</v>
       </c>
       <c r="AM250" t="s" s="2">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="AN250" t="s" s="2">
         <v>78</v>
@@ -32502,10 +32516,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32531,10 +32545,10 @@
         <v>233</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="N251" s="2"/>
       <c r="O251" s="2"/>
@@ -32565,25 +32579,25 @@
       </c>
       <c r="Y251" s="2"/>
       <c r="Z251" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="AA251" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB251" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC251" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD251" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE251" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF251" t="s" s="2">
         <v>824</v>
-      </c>
-      <c r="AA251" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB251" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC251" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD251" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE251" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF251" t="s" s="2">
-        <v>821</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>90</v>
@@ -32604,10 +32618,10 @@
         <v>78</v>
       </c>
       <c r="AM251" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="AN251" t="s" s="2">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="AO251" t="s" s="2">
         <v>78</v>
@@ -32615,10 +32629,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32730,10 +32744,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -32824,7 +32838,7 @@
         <v>80</v>
       </c>
       <c r="AI253" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ253" t="s" s="2">
         <v>119</v>
@@ -32836,7 +32850,7 @@
         <v>78</v>
       </c>
       <c r="AM253" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN253" t="s" s="2">
         <v>78</v>
@@ -32847,10 +32861,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -32922,14 +32936,14 @@
         <v>78</v>
       </c>
       <c r="AB254" t="s" s="2">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="AC254" s="2"/>
       <c r="AD254" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE254" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="AF254" t="s" s="2">
         <v>398</v>
@@ -32941,7 +32955,7 @@
         <v>80</v>
       </c>
       <c r="AI254" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ254" t="s" s="2">
         <v>102</v>
@@ -32964,13 +32978,13 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>78</v>
@@ -33033,7 +33047,7 @@
       </c>
       <c r="Y255" s="2"/>
       <c r="Z255" t="s" s="2">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="AA255" t="s" s="2">
         <v>78</v>
@@ -33060,7 +33074,7 @@
         <v>80</v>
       </c>
       <c r="AI255" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ255" t="s" s="2">
         <v>102</v>
@@ -33083,13 +33097,13 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="D256" t="s" s="2">
         <v>78</v>
@@ -33152,7 +33166,7 @@
       </c>
       <c r="Y256" s="2"/>
       <c r="Z256" t="s" s="2">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="AA256" t="s" s="2">
         <v>78</v>
@@ -33179,7 +33193,7 @@
         <v>80</v>
       </c>
       <c r="AI256" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ256" t="s" s="2">
         <v>102</v>
@@ -33202,10 +33216,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -33298,7 +33312,7 @@
         <v>90</v>
       </c>
       <c r="AI257" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ257" t="s" s="2">
         <v>102</v>
@@ -33321,10 +33335,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33350,14 +33364,14 @@
         <v>253</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" t="s" s="2">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>78</v>
@@ -33406,7 +33420,7 @@
         <v>78</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>79</v>
@@ -33427,10 +33441,10 @@
         <v>78</v>
       </c>
       <c r="AM258" t="s" s="2">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="AN258" t="s" s="2">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="AO258" t="s" s="2">
         <v>78</v>
@@ -33438,10 +33452,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33553,10 +33567,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33647,7 +33661,7 @@
         <v>80</v>
       </c>
       <c r="AI260" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ260" t="s" s="2">
         <v>119</v>
@@ -33659,7 +33673,7 @@
         <v>78</v>
       </c>
       <c r="AM260" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN260" t="s" s="2">
         <v>78</v>
@@ -33670,10 +33684,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33699,7 +33713,7 @@
         <v>260</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="M261" t="s" s="2">
         <v>262</v>
@@ -33787,10 +33801,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33816,7 +33830,7 @@
         <v>260</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="M262" t="s" s="2">
         <v>271</v>
@@ -33906,10 +33920,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -33932,13 +33946,13 @@
         <v>78</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="N263" s="2"/>
       <c r="O263" s="2"/>
@@ -33989,7 +34003,7 @@
         <v>78</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>79</v>
@@ -34010,7 +34024,7 @@
         <v>78</v>
       </c>
       <c r="AM263" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="AN263" t="s" s="2">
         <v>78</v>
@@ -34021,13 +34035,13 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D264" t="s" s="2">
         <v>78</v>
@@ -34049,13 +34063,13 @@
         <v>78</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="N264" s="2"/>
       <c r="O264" s="2"/>
@@ -34106,7 +34120,7 @@
         <v>78</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>79</v>
@@ -34124,13 +34138,13 @@
         <v>78</v>
       </c>
       <c r="AL264" t="s" s="2">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="AM264" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="AN264" t="s" s="2">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="AO264" t="s" s="2">
         <v>78</v>
@@ -34138,10 +34152,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -34253,10 +34267,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34370,14 +34384,14 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="E267" s="2"/>
       <c r="F267" t="s" s="2">
@@ -34399,10 +34413,10 @@
         <v>111</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="N267" t="s" s="2">
         <v>114</v>
@@ -34457,7 +34471,7 @@
         <v>78</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>79</v>
@@ -34489,10 +34503,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34518,14 +34532,14 @@
         <v>362</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="N268" s="2"/>
       <c r="O268" t="s" s="2">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="P268" t="s" s="2">
         <v>78</v>
@@ -34574,7 +34588,7 @@
         <v>78</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>79</v>
@@ -34595,7 +34609,7 @@
         <v>78</v>
       </c>
       <c r="AM268" t="s" s="2">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="AN268" t="s" s="2">
         <v>78</v>
@@ -34606,10 +34620,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -34635,10 +34649,10 @@
         <v>233</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="N269" s="2"/>
       <c r="O269" s="2"/>
@@ -34669,25 +34683,25 @@
       </c>
       <c r="Y269" s="2"/>
       <c r="Z269" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="AA269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF269" t="s" s="2">
         <v>824</v>
-      </c>
-      <c r="AA269" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB269" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC269" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD269" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE269" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF269" t="s" s="2">
-        <v>821</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>90</v>
@@ -34708,10 +34722,10 @@
         <v>78</v>
       </c>
       <c r="AM269" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="AN269" t="s" s="2">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="AO269" t="s" s="2">
         <v>78</v>
@@ -34719,10 +34733,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -34834,10 +34848,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -34928,7 +34942,7 @@
         <v>80</v>
       </c>
       <c r="AI271" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ271" t="s" s="2">
         <v>119</v>
@@ -34940,7 +34954,7 @@
         <v>78</v>
       </c>
       <c r="AM271" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN271" t="s" s="2">
         <v>78</v>
@@ -34951,10 +34965,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -35026,14 +35040,14 @@
         <v>78</v>
       </c>
       <c r="AB272" t="s" s="2">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="AC272" s="2"/>
       <c r="AD272" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE272" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="AF272" t="s" s="2">
         <v>398</v>
@@ -35045,7 +35059,7 @@
         <v>80</v>
       </c>
       <c r="AI272" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ272" t="s" s="2">
         <v>102</v>
@@ -35068,13 +35082,13 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>78</v>
@@ -35099,7 +35113,7 @@
         <v>154</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="M273" t="s" s="2">
         <v>395</v>
@@ -35137,7 +35151,7 @@
       </c>
       <c r="Y273" s="2"/>
       <c r="Z273" t="s" s="2">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="AA273" t="s" s="2">
         <v>78</v>
@@ -35164,7 +35178,7 @@
         <v>80</v>
       </c>
       <c r="AI273" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ273" t="s" s="2">
         <v>102</v>
@@ -35187,10 +35201,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C274" t="s" s="2">
         <v>337</v>
@@ -35218,7 +35232,7 @@
         <v>154</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="M274" t="s" s="2">
         <v>395</v>
@@ -35283,7 +35297,7 @@
         <v>80</v>
       </c>
       <c r="AI274" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ274" t="s" s="2">
         <v>102</v>
@@ -35306,10 +35320,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -35402,7 +35416,7 @@
         <v>90</v>
       </c>
       <c r="AI275" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ275" t="s" s="2">
         <v>102</v>
@@ -35425,10 +35439,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -35454,14 +35468,14 @@
         <v>253</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="N276" s="2"/>
       <c r="O276" t="s" s="2">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="P276" t="s" s="2">
         <v>78</v>
@@ -35510,7 +35524,7 @@
         <v>78</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>79</v>
@@ -35531,10 +35545,10 @@
         <v>78</v>
       </c>
       <c r="AM276" t="s" s="2">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="AN276" t="s" s="2">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="AO276" t="s" s="2">
         <v>78</v>
@@ -35542,10 +35556,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -35657,10 +35671,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35751,7 +35765,7 @@
         <v>80</v>
       </c>
       <c r="AI278" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ278" t="s" s="2">
         <v>119</v>
@@ -35763,7 +35777,7 @@
         <v>78</v>
       </c>
       <c r="AM278" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN278" t="s" s="2">
         <v>78</v>
@@ -35774,10 +35788,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35803,7 +35817,7 @@
         <v>260</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="M279" t="s" s="2">
         <v>262</v>
@@ -35891,10 +35905,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -35920,7 +35934,7 @@
         <v>260</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="M280" t="s" s="2">
         <v>271</v>
@@ -36010,10 +36024,10 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -36039,10 +36053,10 @@
         <v>476</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="N281" s="2"/>
       <c r="O281" s="2"/>
@@ -36093,7 +36107,7 @@
         <v>78</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>79</v>
@@ -36114,7 +36128,7 @@
         <v>78</v>
       </c>
       <c r="AM281" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="AN281" t="s" s="2">
         <v>78</v>
@@ -36125,13 +36139,13 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="D282" t="s" s="2">
         <v>78</v>
@@ -36153,13 +36167,13 @@
         <v>78</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="N282" s="2"/>
       <c r="O282" s="2"/>
@@ -36210,7 +36224,7 @@
         <v>78</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>79</v>
@@ -36228,13 +36242,13 @@
         <v>78</v>
       </c>
       <c r="AL282" t="s" s="2">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="AM282" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="AN282" t="s" s="2">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="AO282" t="s" s="2">
         <v>78</v>
@@ -36242,10 +36256,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -36357,10 +36371,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -36474,14 +36488,14 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="E285" s="2"/>
       <c r="F285" t="s" s="2">
@@ -36503,10 +36517,10 @@
         <v>111</v>
       </c>
       <c r="L285" t="s" s="2">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="M285" t="s" s="2">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="N285" t="s" s="2">
         <v>114</v>
@@ -36561,7 +36575,7 @@
         <v>78</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="AG285" t="s" s="2">
         <v>79</v>
@@ -36593,10 +36607,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -36622,14 +36636,14 @@
         <v>362</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="N286" s="2"/>
       <c r="O286" t="s" s="2">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="P286" t="s" s="2">
         <v>78</v>
@@ -36678,7 +36692,7 @@
         <v>78</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>79</v>
@@ -36699,7 +36713,7 @@
         <v>78</v>
       </c>
       <c r="AM286" t="s" s="2">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="AN286" t="s" s="2">
         <v>78</v>
@@ -36710,10 +36724,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -36739,10 +36753,10 @@
         <v>233</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="N287" s="2"/>
       <c r="O287" s="2"/>
@@ -36773,25 +36787,25 @@
       </c>
       <c r="Y287" s="2"/>
       <c r="Z287" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="AA287" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB287" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC287" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD287" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE287" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF287" t="s" s="2">
         <v>824</v>
-      </c>
-      <c r="AA287" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB287" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC287" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD287" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE287" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF287" t="s" s="2">
-        <v>821</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>90</v>
@@ -36806,16 +36820,16 @@
         <v>102</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM287" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="AN287" t="s" s="2">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="AO287" t="s" s="2">
         <v>78</v>
@@ -36823,10 +36837,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -36938,10 +36952,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -37032,7 +37046,7 @@
         <v>80</v>
       </c>
       <c r="AI289" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ289" t="s" s="2">
         <v>119</v>
@@ -37044,7 +37058,7 @@
         <v>78</v>
       </c>
       <c r="AM289" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN289" t="s" s="2">
         <v>78</v>
@@ -37055,10 +37069,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -37130,7 +37144,7 @@
         <v>78</v>
       </c>
       <c r="AB290" t="s" s="2">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="AC290" s="2"/>
       <c r="AD290" t="s" s="2">
@@ -37149,7 +37163,7 @@
         <v>80</v>
       </c>
       <c r="AI290" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ290" t="s" s="2">
         <v>102</v>
@@ -37172,13 +37186,13 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="D291" t="s" s="2">
         <v>78</v>
@@ -37203,7 +37217,7 @@
         <v>154</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="M291" t="s" s="2">
         <v>395</v>
@@ -37241,7 +37255,7 @@
       </c>
       <c r="Y291" s="2"/>
       <c r="Z291" t="s" s="2">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="AA291" t="s" s="2">
         <v>78</v>
@@ -37268,7 +37282,7 @@
         <v>80</v>
       </c>
       <c r="AI291" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ291" t="s" s="2">
         <v>102</v>
@@ -37291,13 +37305,13 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="D292" t="s" s="2">
         <v>78</v>
@@ -37322,7 +37336,7 @@
         <v>154</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="M292" t="s" s="2">
         <v>395</v>
@@ -37360,7 +37374,7 @@
       </c>
       <c r="Y292" s="2"/>
       <c r="Z292" t="s" s="2">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="AA292" t="s" s="2">
         <v>78</v>
@@ -37387,7 +37401,7 @@
         <v>80</v>
       </c>
       <c r="AI292" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ292" t="s" s="2">
         <v>102</v>
@@ -37410,10 +37424,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -37506,7 +37520,7 @@
         <v>90</v>
       </c>
       <c r="AI293" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ293" t="s" s="2">
         <v>102</v>
@@ -37529,10 +37543,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -37558,14 +37572,14 @@
         <v>253</v>
       </c>
       <c r="L294" t="s" s="2">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="M294" t="s" s="2">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="N294" s="2"/>
       <c r="O294" t="s" s="2">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="P294" t="s" s="2">
         <v>78</v>
@@ -37614,7 +37628,7 @@
         <v>78</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>79</v>
@@ -37635,10 +37649,10 @@
         <v>78</v>
       </c>
       <c r="AM294" t="s" s="2">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="AN294" t="s" s="2">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="AO294" t="s" s="2">
         <v>78</v>
@@ -37646,10 +37660,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -37761,10 +37775,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -37855,7 +37869,7 @@
         <v>80</v>
       </c>
       <c r="AI296" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ296" t="s" s="2">
         <v>119</v>
@@ -37867,7 +37881,7 @@
         <v>78</v>
       </c>
       <c r="AM296" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN296" t="s" s="2">
         <v>78</v>
@@ -37878,10 +37892,10 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -37907,7 +37921,7 @@
         <v>260</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="M297" t="s" s="2">
         <v>262</v>
@@ -37978,7 +37992,7 @@
         <v>102</v>
       </c>
       <c r="AK297" t="s" s="2">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="AL297" t="s" s="2">
         <v>266</v>
@@ -37995,10 +38009,10 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -38024,7 +38038,7 @@
         <v>260</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="M298" t="s" s="2">
         <v>271</v>
@@ -38097,7 +38111,7 @@
         <v>102</v>
       </c>
       <c r="AK298" t="s" s="2">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="AL298" t="s" s="2">
         <v>275</v>
@@ -38114,10 +38128,10 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -38143,10 +38157,10 @@
         <v>476</v>
       </c>
       <c r="L299" t="s" s="2">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="M299" t="s" s="2">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="N299" s="2"/>
       <c r="O299" s="2"/>
@@ -38197,7 +38211,7 @@
         <v>78</v>
       </c>
       <c r="AF299" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="AG299" t="s" s="2">
         <v>79</v>
@@ -38218,7 +38232,7 @@
         <v>78</v>
       </c>
       <c r="AM299" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="AN299" t="s" s="2">
         <v>78</v>
@@ -38229,10 +38243,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -38255,19 +38269,19 @@
         <v>78</v>
       </c>
       <c r="K300" t="s" s="2">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="L300" t="s" s="2">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="M300" t="s" s="2">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="N300" t="s" s="2">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="O300" t="s" s="2">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="P300" t="s" s="2">
         <v>78</v>
@@ -38296,7 +38310,7 @@
       </c>
       <c r="Y300" s="2"/>
       <c r="Z300" t="s" s="2">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="AA300" t="s" s="2">
         <v>78</v>
@@ -38314,7 +38328,7 @@
         <v>78</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>79</v>
@@ -38332,10 +38346,10 @@
         <v>78</v>
       </c>
       <c r="AL300" t="s" s="2">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="AM300" t="s" s="2">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="AN300" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11057" uniqueCount="975">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -842,8 +842,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t>ele-1
-per-1</t>
+    <t xml:space="preserve">per-1
+</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -1711,19 +1711,7 @@
     <t>Practitioner.identifier:identifiantInterne.period</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
-  </si>
-  <si>
     <t>Practitioner.identifier:identifiantInterne.assigner</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Practitioner.active</t>
@@ -6084,7 +6072,7 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>119</v>
@@ -6096,7 +6084,7 @@
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -6201,7 +6189,7 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>119</v>
@@ -6431,7 +6419,7 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>119</v>
@@ -6661,7 +6649,7 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>102</v>
@@ -6778,7 +6766,7 @@
         <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>119</v>
@@ -7008,7 +6996,7 @@
         <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>119</v>
@@ -7238,7 +7226,7 @@
         <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>102</v>
@@ -7355,7 +7343,7 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>119</v>
@@ -7585,7 +7573,7 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>119</v>
@@ -7817,7 +7805,7 @@
         <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>102</v>
@@ -8049,7 +8037,7 @@
         <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>119</v>
@@ -8061,7 +8049,7 @@
         <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -8402,7 +8390,7 @@
         <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>119</v>
@@ -8632,7 +8620,7 @@
         <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>119</v>
@@ -8862,7 +8850,7 @@
         <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>102</v>
@@ -8979,7 +8967,7 @@
         <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>119</v>
@@ -9209,7 +9197,7 @@
         <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>119</v>
@@ -9439,7 +9427,7 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
@@ -9556,7 +9544,7 @@
         <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>119</v>
@@ -9786,7 +9774,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>119</v>
@@ -10018,7 +10006,7 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -10250,7 +10238,7 @@
         <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>102</v>
@@ -10599,7 +10587,7 @@
         <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>119</v>
@@ -10611,7 +10599,7 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -10716,7 +10704,7 @@
         <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>119</v>
@@ -10946,7 +10934,7 @@
         <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>119</v>
@@ -11176,7 +11164,7 @@
         <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>102</v>
@@ -11293,7 +11281,7 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>119</v>
@@ -11523,7 +11511,7 @@
         <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>119</v>
@@ -11755,7 +11743,7 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -11987,7 +11975,7 @@
         <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>119</v>
@@ -11999,7 +11987,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -12340,7 +12328,7 @@
         <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>119</v>
@@ -12570,7 +12558,7 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>119</v>
@@ -12800,7 +12788,7 @@
         <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>102</v>
@@ -12917,7 +12905,7 @@
         <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>119</v>
@@ -13147,7 +13135,7 @@
         <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>119</v>
@@ -13377,7 +13365,7 @@
         <v>90</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>102</v>
@@ -13609,7 +13597,7 @@
         <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>102</v>
@@ -19828,7 +19816,7 @@
         <v>80</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>119</v>
@@ -19840,7 +19828,7 @@
         <v>78</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>78</v>
@@ -19947,7 +19935,7 @@
         <v>90</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>102</v>
@@ -20066,7 +20054,7 @@
         <v>90</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>102</v>
@@ -20183,7 +20171,7 @@
         <v>90</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>102</v>
@@ -20300,7 +20288,7 @@
         <v>90</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>102</v>
@@ -20357,9 +20345,7 @@
       <c r="M146" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="N146" t="s" s="2">
-        <v>542</v>
-      </c>
+      <c r="N146" s="2"/>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -20417,10 +20403,10 @@
         <v>90</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>543</v>
+        <v>102</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>78</v>
@@ -20440,7 +20426,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>475</v>
@@ -20534,10 +20520,10 @@
         <v>90</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>545</v>
+        <v>102</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>78</v>
@@ -20557,10 +20543,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20586,23 +20572,23 @@
         <v>297</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="O148" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="P148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q148" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="N148" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="P148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q148" t="s" s="2">
-        <v>551</v>
-      </c>
       <c r="R148" t="s" s="2">
         <v>78</v>
       </c>
@@ -20646,7 +20632,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20667,21 +20653,21 @@
         <v>78</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20704,19 +20690,19 @@
         <v>78</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="L149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>78</v>
@@ -20765,7 +20751,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20783,13 +20769,13 @@
         <v>78</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>78</v>
@@ -20797,10 +20783,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20912,10 +20898,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21029,13 +21015,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>78</v>
@@ -21057,13 +21043,13 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21146,10 +21132,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21175,16 +21161,16 @@
         <v>176</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="O153" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>78</v>
@@ -21213,7 +21199,7 @@
       </c>
       <c r="Y153" s="2"/>
       <c r="Z153" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>78</v>
@@ -21231,7 +21217,7 @@
         <v>78</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -21249,13 +21235,13 @@
         <v>78</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>78</v>
@@ -21263,10 +21249,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21292,16 +21278,16 @@
         <v>104</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="O154" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>78</v>
@@ -21350,7 +21336,7 @@
         <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21368,10 +21354,10 @@
         <v>78</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>78</v>
@@ -21382,14 +21368,14 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -21411,13 +21397,13 @@
         <v>104</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21467,7 +21453,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21485,13 +21471,13 @@
         <v>78</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>78</v>
@@ -21499,14 +21485,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -21528,13 +21514,13 @@
         <v>104</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -21584,7 +21570,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21602,13 +21588,13 @@
         <v>78</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>78</v>
@@ -21616,10 +21602,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21645,10 +21631,10 @@
         <v>104</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -21678,10 +21664,10 @@
         <v>158</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>78</v>
@@ -21699,7 +21685,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21717,13 +21703,13 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>78</v>
@@ -21731,10 +21717,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21760,10 +21746,10 @@
         <v>104</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -21793,10 +21779,10 @@
         <v>158</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>78</v>
@@ -21814,7 +21800,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21832,10 +21818,10 @@
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>78</v>
@@ -21846,10 +21832,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21875,14 +21861,14 @@
         <v>253</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
@@ -21931,7 +21917,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21949,10 +21935,10 @@
         <v>78</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>474</v>
@@ -21963,10 +21949,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21989,19 +21975,19 @@
         <v>78</v>
       </c>
       <c r="K160" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="L160" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="N160" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="L160" t="s" s="2">
+      <c r="O160" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>78</v>
@@ -22038,17 +22024,17 @@
         <v>78</v>
       </c>
       <c r="AB160" t="s" s="2">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="AC160" s="2"/>
       <c r="AD160" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE160" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -22060,19 +22046,19 @@
         <v>209</v>
       </c>
       <c r="AJ160" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AK160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL160" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AN160" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="AK160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL160" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AM160" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>78</v>
@@ -22080,13 +22066,13 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>78</v>
@@ -22108,19 +22094,19 @@
         <v>78</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>78</v>
@@ -22169,7 +22155,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -22181,19 +22167,19 @@
         <v>209</v>
       </c>
       <c r="AJ161" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AK161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL161" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AM161" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AN161" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="AK161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL161" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AM161" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="AN161" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>78</v>
@@ -22201,10 +22187,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22316,10 +22302,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22433,13 +22419,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>78</v>
@@ -22461,13 +22447,13 @@
         <v>78</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -22550,10 +22536,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22665,10 +22651,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22780,10 +22766,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22823,7 +22809,7 @@
       </c>
       <c r="Q167" s="2"/>
       <c r="R167" t="s" s="2">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="S167" t="s" s="2">
         <v>78</v>
@@ -22897,10 +22883,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22941,7 +22927,7 @@
         <v>78</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>78</v>
@@ -22960,7 +22946,7 @@
       </c>
       <c r="Y168" s="2"/>
       <c r="Z168" t="s" s="2">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>78</v>
@@ -23010,13 +22996,13 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>78</v>
@@ -23038,13 +23024,13 @@
         <v>78</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23127,10 +23113,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23242,10 +23228,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23336,7 +23322,7 @@
         <v>80</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>119</v>
@@ -23348,7 +23334,7 @@
         <v>78</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>78</v>
@@ -23359,10 +23345,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C172" t="s" s="2">
         <v>312</v>
@@ -23390,7 +23376,7 @@
         <v>111</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>202</v>
@@ -23453,7 +23439,7 @@
         <v>80</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>119</v>
@@ -23476,10 +23462,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23591,10 +23577,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23683,7 +23669,7 @@
         <v>80</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>119</v>
@@ -23706,10 +23692,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23823,10 +23809,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23886,7 +23872,7 @@
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>78</v>
@@ -23913,7 +23899,7 @@
         <v>90</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>102</v>
@@ -23936,13 +23922,13 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>78</v>
@@ -23967,7 +23953,7 @@
         <v>111</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="M177" t="s" s="2">
         <v>202</v>
@@ -24030,7 +24016,7 @@
         <v>80</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>119</v>
@@ -24053,10 +24039,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24168,10 +24154,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24260,7 +24246,7 @@
         <v>80</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>119</v>
@@ -24283,10 +24269,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24326,7 +24312,7 @@
       </c>
       <c r="Q180" s="2"/>
       <c r="R180" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>78</v>
@@ -24400,10 +24386,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24492,7 +24478,7 @@
         <v>90</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>102</v>
@@ -24515,13 +24501,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>78</v>
@@ -24609,7 +24595,7 @@
         <v>80</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>119</v>
@@ -24632,10 +24618,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24747,10 +24733,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24839,7 +24825,7 @@
         <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>119</v>
@@ -24862,10 +24848,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24905,7 +24891,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>78</v>
@@ -24979,10 +24965,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25071,7 +25057,7 @@
         <v>90</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>102</v>
@@ -25094,13 +25080,13 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D187" t="s" s="2">
         <v>78</v>
@@ -25125,7 +25111,7 @@
         <v>111</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="M187" t="s" s="2">
         <v>202</v>
@@ -25188,7 +25174,7 @@
         <v>80</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>119</v>
@@ -25211,10 +25197,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25326,10 +25312,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25418,7 +25404,7 @@
         <v>80</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>119</v>
@@ -25441,10 +25427,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25484,7 +25470,7 @@
       </c>
       <c r="Q190" s="2"/>
       <c r="R190" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S190" t="s" s="2">
         <v>78</v>
@@ -25558,10 +25544,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25650,7 +25636,7 @@
         <v>90</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>102</v>
@@ -25673,13 +25659,13 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="D192" t="s" s="2">
         <v>78</v>
@@ -25767,7 +25753,7 @@
         <v>80</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ192" t="s" s="2">
         <v>119</v>
@@ -25790,10 +25776,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25905,10 +25891,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25997,7 +25983,7 @@
         <v>80</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ194" t="s" s="2">
         <v>119</v>
@@ -26020,10 +26006,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26063,7 +26049,7 @@
       </c>
       <c r="Q195" s="2"/>
       <c r="R195" t="s" s="2">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="S195" t="s" s="2">
         <v>78</v>
@@ -26137,10 +26123,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26229,7 +26215,7 @@
         <v>90</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ196" t="s" s="2">
         <v>102</v>
@@ -26252,13 +26238,13 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D197" t="s" s="2">
         <v>78</v>
@@ -26283,7 +26269,7 @@
         <v>111</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="M197" t="s" s="2">
         <v>202</v>
@@ -26346,7 +26332,7 @@
         <v>80</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>119</v>
@@ -26369,10 +26355,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26484,10 +26470,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26576,7 +26562,7 @@
         <v>80</v>
       </c>
       <c r="AI199" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ199" t="s" s="2">
         <v>119</v>
@@ -26599,10 +26585,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26642,7 +26628,7 @@
       </c>
       <c r="Q200" s="2"/>
       <c r="R200" t="s" s="2">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="S200" t="s" s="2">
         <v>78</v>
@@ -26716,10 +26702,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26808,7 +26794,7 @@
         <v>90</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ201" t="s" s="2">
         <v>102</v>
@@ -26831,13 +26817,13 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>78</v>
@@ -26862,7 +26848,7 @@
         <v>111</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="M202" t="s" s="2">
         <v>202</v>
@@ -26925,7 +26911,7 @@
         <v>80</v>
       </c>
       <c r="AI202" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ202" t="s" s="2">
         <v>119</v>
@@ -26948,10 +26934,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27063,10 +27049,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27155,7 +27141,7 @@
         <v>80</v>
       </c>
       <c r="AI204" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ204" t="s" s="2">
         <v>119</v>
@@ -27178,10 +27164,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27221,7 +27207,7 @@
       </c>
       <c r="Q205" s="2"/>
       <c r="R205" t="s" s="2">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="S205" t="s" s="2">
         <v>78</v>
@@ -27295,10 +27281,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27387,7 +27373,7 @@
         <v>90</v>
       </c>
       <c r="AI206" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ206" t="s" s="2">
         <v>102</v>
@@ -27410,10 +27396,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27453,7 +27439,7 @@
       </c>
       <c r="Q207" s="2"/>
       <c r="R207" t="s" s="2">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="S207" t="s" s="2">
         <v>78</v>
@@ -27527,10 +27513,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27619,7 +27605,7 @@
         <v>90</v>
       </c>
       <c r="AI208" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ208" t="s" s="2">
         <v>102</v>
@@ -27642,10 +27628,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27671,10 +27657,10 @@
         <v>176</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -27686,7 +27672,7 @@
         <v>78</v>
       </c>
       <c r="S209" t="s" s="2">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="T209" t="s" s="2">
         <v>78</v>
@@ -27704,37 +27690,37 @@
         <v>236</v>
       </c>
       <c r="Y209" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="Z209" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="AA209" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB209" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC209" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD209" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE209" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF209" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="AG209" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH209" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI209" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="Z209" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="AA209" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB209" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC209" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD209" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE209" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF209" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="AG209" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH209" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI209" t="s" s="2">
-        <v>735</v>
       </c>
       <c r="AJ209" t="s" s="2">
         <v>102</v>
@@ -27743,13 +27729,13 @@
         <v>78</v>
       </c>
       <c r="AL209" t="s" s="2">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="AM209" t="s" s="2">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>78</v>
@@ -27757,10 +27743,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27786,16 +27772,16 @@
         <v>104</v>
       </c>
       <c r="L210" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="M210" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="N210" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="O210" t="s" s="2">
         <v>741</v>
-      </c>
-      <c r="M210" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="N210" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="O210" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>78</v>
@@ -27844,7 +27830,7 @@
         <v>78</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>79</v>
@@ -27862,10 +27848,10 @@
         <v>78</v>
       </c>
       <c r="AL210" t="s" s="2">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="AM210" t="s" s="2">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="AN210" t="s" s="2">
         <v>467</v>
@@ -27876,10 +27862,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27905,16 +27891,16 @@
         <v>176</v>
       </c>
       <c r="L211" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="M211" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="N211" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="O211" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="M211" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="N211" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="O211" t="s" s="2">
-        <v>753</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>78</v>
@@ -27942,10 +27928,10 @@
         <v>236</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>78</v>
@@ -27963,7 +27949,7 @@
         <v>78</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>79</v>
@@ -27981,13 +27967,13 @@
         <v>78</v>
       </c>
       <c r="AL211" t="s" s="2">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="AM211" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>78</v>
@@ -27995,10 +27981,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28021,16 +28007,16 @@
         <v>91</v>
       </c>
       <c r="K212" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="L212" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="M212" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="N212" t="s" s="2">
         <v>761</v>
-      </c>
-      <c r="L212" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="M212" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="N212" t="s" s="2">
-        <v>764</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
@@ -28080,7 +28066,7 @@
         <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
@@ -28112,10 +28098,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28141,10 +28127,10 @@
         <v>253</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -28195,7 +28181,7 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>79</v>
@@ -28216,7 +28202,7 @@
         <v>199</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="AN213" t="s" s="2">
         <v>474</v>
@@ -28227,10 +28213,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28253,19 +28239,19 @@
         <v>78</v>
       </c>
       <c r="K214" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="L214" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="M214" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="N214" t="s" s="2">
         <v>772</v>
       </c>
-      <c r="L214" t="s" s="2">
+      <c r="O214" t="s" s="2">
         <v>773</v>
-      </c>
-      <c r="M214" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="N214" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="O214" t="s" s="2">
-        <v>776</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -28314,7 +28300,7 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
@@ -28332,13 +28318,13 @@
         <v>78</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>78</v>
@@ -28346,10 +28332,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28375,14 +28361,14 @@
         <v>176</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>78</v>
@@ -28410,10 +28396,10 @@
         <v>236</v>
       </c>
       <c r="Y215" t="s" s="2">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="Z215" t="s" s="2">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>78</v>
@@ -28431,7 +28417,7 @@
         <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -28449,13 +28435,13 @@
         <v>78</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>78</v>
@@ -28463,10 +28449,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28489,17 +28475,17 @@
         <v>91</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" t="s" s="2">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>78</v>
@@ -28548,7 +28534,7 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28566,13 +28552,13 @@
         <v>78</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>78</v>
@@ -28580,10 +28566,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28606,17 +28592,17 @@
         <v>78</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
@@ -28665,7 +28651,7 @@
         <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>
@@ -28686,10 +28672,10 @@
         <v>78</v>
       </c>
       <c r="AM217" t="s" s="2">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>78</v>
@@ -28697,10 +28683,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28723,13 +28709,13 @@
         <v>78</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -28768,7 +28754,7 @@
         <v>78</v>
       </c>
       <c r="AB218" t="s" s="2">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="AC218" s="2"/>
       <c r="AD218" t="s" s="2">
@@ -28778,7 +28764,7 @@
         <v>117</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>79</v>
@@ -28796,13 +28782,13 @@
         <v>78</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="AM218" t="s" s="2">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="AO218" t="s" s="2">
         <v>78</v>
@@ -28810,10 +28796,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -28925,10 +28911,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29042,14 +29028,14 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="E221" s="2"/>
       <c r="F221" t="s" s="2">
@@ -29071,10 +29057,10 @@
         <v>111</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="N221" t="s" s="2">
         <v>114</v>
@@ -29129,7 +29115,7 @@
         <v>78</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>79</v>
@@ -29161,10 +29147,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29190,14 +29176,14 @@
         <v>362</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>78</v>
@@ -29246,7 +29232,7 @@
         <v>78</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>79</v>
@@ -29267,7 +29253,7 @@
         <v>78</v>
       </c>
       <c r="AM222" t="s" s="2">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="AN222" t="s" s="2">
         <v>78</v>
@@ -29278,10 +29264,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29307,10 +29293,10 @@
         <v>233</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -29341,7 +29327,7 @@
       </c>
       <c r="Y223" s="2"/>
       <c r="Z223" t="s" s="2">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>78</v>
@@ -29359,7 +29345,7 @@
         <v>78</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>90</v>
@@ -29380,10 +29366,10 @@
         <v>78</v>
       </c>
       <c r="AM223" t="s" s="2">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="AO223" t="s" s="2">
         <v>78</v>
@@ -29391,10 +29377,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29420,14 +29406,14 @@
         <v>253</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" t="s" s="2">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>78</v>
@@ -29476,7 +29462,7 @@
         <v>78</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>79</v>
@@ -29497,10 +29483,10 @@
         <v>78</v>
       </c>
       <c r="AM224" t="s" s="2">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>78</v>
@@ -29508,10 +29494,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29537,10 +29523,10 @@
         <v>476</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -29591,7 +29577,7 @@
         <v>78</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>79</v>
@@ -29612,7 +29598,7 @@
         <v>78</v>
       </c>
       <c r="AM225" t="s" s="2">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="AN225" t="s" s="2">
         <v>78</v>
@@ -29623,13 +29609,13 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="D226" t="s" s="2">
         <v>78</v>
@@ -29651,13 +29637,13 @@
         <v>78</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -29708,7 +29694,7 @@
         <v>78</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>79</v>
@@ -29726,13 +29712,13 @@
         <v>78</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="AM226" t="s" s="2">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="AN226" t="s" s="2">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="AO226" t="s" s="2">
         <v>78</v>
@@ -29740,10 +29726,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -29855,10 +29841,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -29968,13 +29954,13 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="D229" t="s" s="2">
         <v>78</v>
@@ -29996,13 +29982,13 @@
         <v>78</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -30085,10 +30071,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30200,10 +30186,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30294,7 +30280,7 @@
         <v>80</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ231" t="s" s="2">
         <v>119</v>
@@ -30306,7 +30292,7 @@
         <v>78</v>
       </c>
       <c r="AM231" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN231" t="s" s="2">
         <v>78</v>
@@ -30317,13 +30303,13 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="D232" t="s" s="2">
         <v>78</v>
@@ -30411,7 +30397,7 @@
         <v>80</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>119</v>
@@ -30434,10 +30420,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30549,10 +30535,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30641,7 +30627,7 @@
         <v>80</v>
       </c>
       <c r="AI234" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ234" t="s" s="2">
         <v>119</v>
@@ -30664,10 +30650,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30707,7 +30693,7 @@
       </c>
       <c r="Q235" s="2"/>
       <c r="R235" t="s" s="2">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="S235" t="s" s="2">
         <v>78</v>
@@ -30781,10 +30767,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -30844,7 +30830,7 @@
       </c>
       <c r="Y236" s="2"/>
       <c r="Z236" t="s" s="2">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="AA236" t="s" s="2">
         <v>78</v>
@@ -30871,7 +30857,7 @@
         <v>90</v>
       </c>
       <c r="AI236" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ236" t="s" s="2">
         <v>102</v>
@@ -30894,13 +30880,13 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="D237" t="s" s="2">
         <v>78</v>
@@ -30988,7 +30974,7 @@
         <v>80</v>
       </c>
       <c r="AI237" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ237" t="s" s="2">
         <v>119</v>
@@ -31011,10 +30997,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -31126,10 +31112,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31218,7 +31204,7 @@
         <v>80</v>
       </c>
       <c r="AI239" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ239" t="s" s="2">
         <v>119</v>
@@ -31241,10 +31227,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31284,7 +31270,7 @@
       </c>
       <c r="Q240" s="2"/>
       <c r="R240" t="s" s="2">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="S240" t="s" s="2">
         <v>78</v>
@@ -31358,10 +31344,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31421,7 +31407,7 @@
       </c>
       <c r="Y241" s="2"/>
       <c r="Z241" t="s" s="2">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="AA241" t="s" s="2">
         <v>78</v>
@@ -31448,7 +31434,7 @@
         <v>90</v>
       </c>
       <c r="AI241" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ241" t="s" s="2">
         <v>102</v>
@@ -31471,13 +31457,13 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="D242" t="s" s="2">
         <v>78</v>
@@ -31565,7 +31551,7 @@
         <v>80</v>
       </c>
       <c r="AI242" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ242" t="s" s="2">
         <v>119</v>
@@ -31588,10 +31574,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31703,10 +31689,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31795,7 +31781,7 @@
         <v>80</v>
       </c>
       <c r="AI244" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ244" t="s" s="2">
         <v>119</v>
@@ -31818,10 +31804,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -31861,7 +31847,7 @@
       </c>
       <c r="Q245" s="2"/>
       <c r="R245" t="s" s="2">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="S245" t="s" s="2">
         <v>78</v>
@@ -31935,10 +31921,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -31998,7 +31984,7 @@
       </c>
       <c r="Y246" s="2"/>
       <c r="Z246" t="s" s="2">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>78</v>
@@ -32025,7 +32011,7 @@
         <v>90</v>
       </c>
       <c r="AI246" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ246" t="s" s="2">
         <v>102</v>
@@ -32048,10 +32034,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32091,7 +32077,7 @@
       </c>
       <c r="Q247" s="2"/>
       <c r="R247" t="s" s="2">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="S247" t="s" s="2">
         <v>78</v>
@@ -32165,10 +32151,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32257,7 +32243,7 @@
         <v>90</v>
       </c>
       <c r="AI248" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ248" t="s" s="2">
         <v>102</v>
@@ -32280,14 +32266,14 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="E249" s="2"/>
       <c r="F249" t="s" s="2">
@@ -32309,10 +32295,10 @@
         <v>111</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="N249" t="s" s="2">
         <v>114</v>
@@ -32367,7 +32353,7 @@
         <v>78</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>79</v>
@@ -32399,10 +32385,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32428,14 +32414,14 @@
         <v>362</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" t="s" s="2">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="P250" t="s" s="2">
         <v>78</v>
@@ -32484,7 +32470,7 @@
         <v>78</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>79</v>
@@ -32505,7 +32491,7 @@
         <v>78</v>
       </c>
       <c r="AM250" t="s" s="2">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="AN250" t="s" s="2">
         <v>78</v>
@@ -32516,10 +32502,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32545,10 +32531,10 @@
         <v>233</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="N251" s="2"/>
       <c r="O251" s="2"/>
@@ -32579,7 +32565,7 @@
       </c>
       <c r="Y251" s="2"/>
       <c r="Z251" t="s" s="2">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="AA251" t="s" s="2">
         <v>78</v>
@@ -32597,7 +32583,7 @@
         <v>78</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>90</v>
@@ -32618,10 +32604,10 @@
         <v>78</v>
       </c>
       <c r="AM251" t="s" s="2">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="AN251" t="s" s="2">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="AO251" t="s" s="2">
         <v>78</v>
@@ -32629,10 +32615,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32744,10 +32730,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -32838,7 +32824,7 @@
         <v>80</v>
       </c>
       <c r="AI253" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ253" t="s" s="2">
         <v>119</v>
@@ -32850,7 +32836,7 @@
         <v>78</v>
       </c>
       <c r="AM253" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN253" t="s" s="2">
         <v>78</v>
@@ -32861,10 +32847,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -32936,14 +32922,14 @@
         <v>78</v>
       </c>
       <c r="AB254" t="s" s="2">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="AC254" s="2"/>
       <c r="AD254" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE254" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="AF254" t="s" s="2">
         <v>398</v>
@@ -32955,7 +32941,7 @@
         <v>80</v>
       </c>
       <c r="AI254" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ254" t="s" s="2">
         <v>102</v>
@@ -32978,13 +32964,13 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B255" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="C255" t="s" s="2">
         <v>891</v>
-      </c>
-      <c r="C255" t="s" s="2">
-        <v>894</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>78</v>
@@ -33047,7 +33033,7 @@
       </c>
       <c r="Y255" s="2"/>
       <c r="Z255" t="s" s="2">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="AA255" t="s" s="2">
         <v>78</v>
@@ -33074,7 +33060,7 @@
         <v>80</v>
       </c>
       <c r="AI255" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ255" t="s" s="2">
         <v>102</v>
@@ -33097,13 +33083,13 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="D256" t="s" s="2">
         <v>78</v>
@@ -33166,7 +33152,7 @@
       </c>
       <c r="Y256" s="2"/>
       <c r="Z256" t="s" s="2">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="AA256" t="s" s="2">
         <v>78</v>
@@ -33193,7 +33179,7 @@
         <v>80</v>
       </c>
       <c r="AI256" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ256" t="s" s="2">
         <v>102</v>
@@ -33216,10 +33202,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -33312,7 +33298,7 @@
         <v>90</v>
       </c>
       <c r="AI257" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ257" t="s" s="2">
         <v>102</v>
@@ -33335,10 +33321,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33364,14 +33350,14 @@
         <v>253</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" t="s" s="2">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>78</v>
@@ -33420,7 +33406,7 @@
         <v>78</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>79</v>
@@ -33441,10 +33427,10 @@
         <v>78</v>
       </c>
       <c r="AM258" t="s" s="2">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="AN258" t="s" s="2">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="AO258" t="s" s="2">
         <v>78</v>
@@ -33452,10 +33438,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33567,10 +33553,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33661,7 +33647,7 @@
         <v>80</v>
       </c>
       <c r="AI260" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ260" t="s" s="2">
         <v>119</v>
@@ -33673,7 +33659,7 @@
         <v>78</v>
       </c>
       <c r="AM260" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN260" t="s" s="2">
         <v>78</v>
@@ -33684,10 +33670,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33713,7 +33699,7 @@
         <v>260</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="M261" t="s" s="2">
         <v>262</v>
@@ -33801,10 +33787,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33830,7 +33816,7 @@
         <v>260</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="M262" t="s" s="2">
         <v>271</v>
@@ -33920,10 +33906,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -33946,13 +33932,13 @@
         <v>78</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="N263" s="2"/>
       <c r="O263" s="2"/>
@@ -34003,7 +33989,7 @@
         <v>78</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>79</v>
@@ -34024,7 +34010,7 @@
         <v>78</v>
       </c>
       <c r="AM263" t="s" s="2">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="AN263" t="s" s="2">
         <v>78</v>
@@ -34035,13 +34021,13 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="D264" t="s" s="2">
         <v>78</v>
@@ -34063,13 +34049,13 @@
         <v>78</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="N264" s="2"/>
       <c r="O264" s="2"/>
@@ -34120,7 +34106,7 @@
         <v>78</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>79</v>
@@ -34138,13 +34124,13 @@
         <v>78</v>
       </c>
       <c r="AL264" t="s" s="2">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="AM264" t="s" s="2">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="AN264" t="s" s="2">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="AO264" t="s" s="2">
         <v>78</v>
@@ -34152,10 +34138,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -34267,10 +34253,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34384,14 +34370,14 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="E267" s="2"/>
       <c r="F267" t="s" s="2">
@@ -34413,10 +34399,10 @@
         <v>111</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="N267" t="s" s="2">
         <v>114</v>
@@ -34471,7 +34457,7 @@
         <v>78</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>79</v>
@@ -34503,10 +34489,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34532,14 +34518,14 @@
         <v>362</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="N268" s="2"/>
       <c r="O268" t="s" s="2">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="P268" t="s" s="2">
         <v>78</v>
@@ -34588,7 +34574,7 @@
         <v>78</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>79</v>
@@ -34609,7 +34595,7 @@
         <v>78</v>
       </c>
       <c r="AM268" t="s" s="2">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="AN268" t="s" s="2">
         <v>78</v>
@@ -34620,10 +34606,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -34649,10 +34635,10 @@
         <v>233</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="N269" s="2"/>
       <c r="O269" s="2"/>
@@ -34683,7 +34669,7 @@
       </c>
       <c r="Y269" s="2"/>
       <c r="Z269" t="s" s="2">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="AA269" t="s" s="2">
         <v>78</v>
@@ -34701,7 +34687,7 @@
         <v>78</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>90</v>
@@ -34722,10 +34708,10 @@
         <v>78</v>
       </c>
       <c r="AM269" t="s" s="2">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="AN269" t="s" s="2">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="AO269" t="s" s="2">
         <v>78</v>
@@ -34733,10 +34719,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -34848,10 +34834,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -34942,7 +34928,7 @@
         <v>80</v>
       </c>
       <c r="AI271" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ271" t="s" s="2">
         <v>119</v>
@@ -34954,7 +34940,7 @@
         <v>78</v>
       </c>
       <c r="AM271" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN271" t="s" s="2">
         <v>78</v>
@@ -34965,10 +34951,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -35040,14 +35026,14 @@
         <v>78</v>
       </c>
       <c r="AB272" t="s" s="2">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="AC272" s="2"/>
       <c r="AD272" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE272" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="AF272" t="s" s="2">
         <v>398</v>
@@ -35059,7 +35045,7 @@
         <v>80</v>
       </c>
       <c r="AI272" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ272" t="s" s="2">
         <v>102</v>
@@ -35082,13 +35068,13 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>78</v>
@@ -35113,7 +35099,7 @@
         <v>154</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="M273" t="s" s="2">
         <v>395</v>
@@ -35151,7 +35137,7 @@
       </c>
       <c r="Y273" s="2"/>
       <c r="Z273" t="s" s="2">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="AA273" t="s" s="2">
         <v>78</v>
@@ -35178,7 +35164,7 @@
         <v>80</v>
       </c>
       <c r="AI273" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ273" t="s" s="2">
         <v>102</v>
@@ -35201,10 +35187,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C274" t="s" s="2">
         <v>337</v>
@@ -35232,7 +35218,7 @@
         <v>154</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="M274" t="s" s="2">
         <v>395</v>
@@ -35297,7 +35283,7 @@
         <v>80</v>
       </c>
       <c r="AI274" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ274" t="s" s="2">
         <v>102</v>
@@ -35320,10 +35306,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -35416,7 +35402,7 @@
         <v>90</v>
       </c>
       <c r="AI275" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ275" t="s" s="2">
         <v>102</v>
@@ -35439,10 +35425,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -35468,14 +35454,14 @@
         <v>253</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="N276" s="2"/>
       <c r="O276" t="s" s="2">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="P276" t="s" s="2">
         <v>78</v>
@@ -35524,7 +35510,7 @@
         <v>78</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>79</v>
@@ -35545,10 +35531,10 @@
         <v>78</v>
       </c>
       <c r="AM276" t="s" s="2">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="AN276" t="s" s="2">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="AO276" t="s" s="2">
         <v>78</v>
@@ -35556,10 +35542,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -35671,10 +35657,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35765,7 +35751,7 @@
         <v>80</v>
       </c>
       <c r="AI278" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ278" t="s" s="2">
         <v>119</v>
@@ -35777,7 +35763,7 @@
         <v>78</v>
       </c>
       <c r="AM278" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN278" t="s" s="2">
         <v>78</v>
@@ -35788,10 +35774,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35817,7 +35803,7 @@
         <v>260</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="M279" t="s" s="2">
         <v>262</v>
@@ -35905,10 +35891,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -35934,7 +35920,7 @@
         <v>260</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="M280" t="s" s="2">
         <v>271</v>
@@ -36024,10 +36010,10 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -36053,10 +36039,10 @@
         <v>476</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="N281" s="2"/>
       <c r="O281" s="2"/>
@@ -36107,7 +36093,7 @@
         <v>78</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>79</v>
@@ -36128,7 +36114,7 @@
         <v>78</v>
       </c>
       <c r="AM281" t="s" s="2">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="AN281" t="s" s="2">
         <v>78</v>
@@ -36139,13 +36125,13 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="D282" t="s" s="2">
         <v>78</v>
@@ -36167,13 +36153,13 @@
         <v>78</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="N282" s="2"/>
       <c r="O282" s="2"/>
@@ -36224,7 +36210,7 @@
         <v>78</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>79</v>
@@ -36242,13 +36228,13 @@
         <v>78</v>
       </c>
       <c r="AL282" t="s" s="2">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="AM282" t="s" s="2">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="AN282" t="s" s="2">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="AO282" t="s" s="2">
         <v>78</v>
@@ -36256,10 +36242,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -36371,10 +36357,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -36488,14 +36474,14 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="E285" s="2"/>
       <c r="F285" t="s" s="2">
@@ -36517,10 +36503,10 @@
         <v>111</v>
       </c>
       <c r="L285" t="s" s="2">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="M285" t="s" s="2">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="N285" t="s" s="2">
         <v>114</v>
@@ -36575,7 +36561,7 @@
         <v>78</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="AG285" t="s" s="2">
         <v>79</v>
@@ -36607,10 +36593,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -36636,14 +36622,14 @@
         <v>362</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="N286" s="2"/>
       <c r="O286" t="s" s="2">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="P286" t="s" s="2">
         <v>78</v>
@@ -36692,7 +36678,7 @@
         <v>78</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>79</v>
@@ -36713,7 +36699,7 @@
         <v>78</v>
       </c>
       <c r="AM286" t="s" s="2">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="AN286" t="s" s="2">
         <v>78</v>
@@ -36724,10 +36710,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -36753,10 +36739,10 @@
         <v>233</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="N287" s="2"/>
       <c r="O287" s="2"/>
@@ -36787,7 +36773,7 @@
       </c>
       <c r="Y287" s="2"/>
       <c r="Z287" t="s" s="2">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="AA287" t="s" s="2">
         <v>78</v>
@@ -36805,7 +36791,7 @@
         <v>78</v>
       </c>
       <c r="AF287" t="s" s="2">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>90</v>
@@ -36820,16 +36806,16 @@
         <v>102</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM287" t="s" s="2">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="AN287" t="s" s="2">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="AO287" t="s" s="2">
         <v>78</v>
@@ -36837,10 +36823,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -36952,10 +36938,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -37046,7 +37032,7 @@
         <v>80</v>
       </c>
       <c r="AI289" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ289" t="s" s="2">
         <v>119</v>
@@ -37058,7 +37044,7 @@
         <v>78</v>
       </c>
       <c r="AM289" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN289" t="s" s="2">
         <v>78</v>
@@ -37069,10 +37055,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -37144,7 +37130,7 @@
         <v>78</v>
       </c>
       <c r="AB290" t="s" s="2">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="AC290" s="2"/>
       <c r="AD290" t="s" s="2">
@@ -37163,7 +37149,7 @@
         <v>80</v>
       </c>
       <c r="AI290" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ290" t="s" s="2">
         <v>102</v>
@@ -37186,13 +37172,13 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="D291" t="s" s="2">
         <v>78</v>
@@ -37217,7 +37203,7 @@
         <v>154</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="M291" t="s" s="2">
         <v>395</v>
@@ -37255,7 +37241,7 @@
       </c>
       <c r="Y291" s="2"/>
       <c r="Z291" t="s" s="2">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="AA291" t="s" s="2">
         <v>78</v>
@@ -37282,7 +37268,7 @@
         <v>80</v>
       </c>
       <c r="AI291" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ291" t="s" s="2">
         <v>102</v>
@@ -37305,13 +37291,13 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="D292" t="s" s="2">
         <v>78</v>
@@ -37336,7 +37322,7 @@
         <v>154</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="M292" t="s" s="2">
         <v>395</v>
@@ -37374,7 +37360,7 @@
       </c>
       <c r="Y292" s="2"/>
       <c r="Z292" t="s" s="2">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="AA292" t="s" s="2">
         <v>78</v>
@@ -37401,7 +37387,7 @@
         <v>80</v>
       </c>
       <c r="AI292" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ292" t="s" s="2">
         <v>102</v>
@@ -37424,10 +37410,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -37520,7 +37506,7 @@
         <v>90</v>
       </c>
       <c r="AI293" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ293" t="s" s="2">
         <v>102</v>
@@ -37543,10 +37529,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -37572,14 +37558,14 @@
         <v>253</v>
       </c>
       <c r="L294" t="s" s="2">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="M294" t="s" s="2">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="N294" s="2"/>
       <c r="O294" t="s" s="2">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="P294" t="s" s="2">
         <v>78</v>
@@ -37628,7 +37614,7 @@
         <v>78</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>79</v>
@@ -37649,10 +37635,10 @@
         <v>78</v>
       </c>
       <c r="AM294" t="s" s="2">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="AN294" t="s" s="2">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="AO294" t="s" s="2">
         <v>78</v>
@@ -37660,10 +37646,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -37775,10 +37761,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -37869,7 +37855,7 @@
         <v>80</v>
       </c>
       <c r="AI296" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ296" t="s" s="2">
         <v>119</v>
@@ -37881,7 +37867,7 @@
         <v>78</v>
       </c>
       <c r="AM296" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN296" t="s" s="2">
         <v>78</v>
@@ -37892,10 +37878,10 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -37921,7 +37907,7 @@
         <v>260</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="M297" t="s" s="2">
         <v>262</v>
@@ -37992,7 +37978,7 @@
         <v>102</v>
       </c>
       <c r="AK297" t="s" s="2">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="AL297" t="s" s="2">
         <v>266</v>
@@ -38009,10 +37995,10 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -38038,7 +38024,7 @@
         <v>260</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="M298" t="s" s="2">
         <v>271</v>
@@ -38111,7 +38097,7 @@
         <v>102</v>
       </c>
       <c r="AK298" t="s" s="2">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="AL298" t="s" s="2">
         <v>275</v>
@@ -38128,10 +38114,10 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -38157,10 +38143,10 @@
         <v>476</v>
       </c>
       <c r="L299" t="s" s="2">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="M299" t="s" s="2">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="N299" s="2"/>
       <c r="O299" s="2"/>
@@ -38211,7 +38197,7 @@
         <v>78</v>
       </c>
       <c r="AF299" t="s" s="2">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="AG299" t="s" s="2">
         <v>79</v>
@@ -38232,7 +38218,7 @@
         <v>78</v>
       </c>
       <c r="AM299" t="s" s="2">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="AN299" t="s" s="2">
         <v>78</v>
@@ -38243,10 +38229,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -38269,19 +38255,19 @@
         <v>78</v>
       </c>
       <c r="K300" t="s" s="2">
+        <v>967</v>
+      </c>
+      <c r="L300" t="s" s="2">
+        <v>968</v>
+      </c>
+      <c r="M300" t="s" s="2">
+        <v>969</v>
+      </c>
+      <c r="N300" t="s" s="2">
         <v>970</v>
       </c>
-      <c r="L300" t="s" s="2">
+      <c r="O300" t="s" s="2">
         <v>971</v>
-      </c>
-      <c r="M300" t="s" s="2">
-        <v>972</v>
-      </c>
-      <c r="N300" t="s" s="2">
-        <v>973</v>
-      </c>
-      <c r="O300" t="s" s="2">
-        <v>974</v>
       </c>
       <c r="P300" t="s" s="2">
         <v>78</v>
@@ -38310,7 +38296,7 @@
       </c>
       <c r="Y300" s="2"/>
       <c r="Z300" t="s" s="2">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="AA300" t="s" s="2">
         <v>78</v>
@@ -38328,7 +38314,7 @@
         <v>78</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>79</v>
@@ -38346,10 +38332,10 @@
         <v>78</v>
       </c>
       <c r="AL300" t="s" s="2">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="AM300" t="s" s="2">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="AN300" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11057" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="979">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -842,8 +842,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -1537,9 +1537,13 @@
     <t>Practitioner.identifier:idNatPs.type</t>
   </si>
   <si>
+    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
+Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+  </si>
+  <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="IDNPS"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1599,7 +1603,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="RPPS"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1608,7 +1612,7 @@
     <t>Practitioner.identifier:rpps.system</t>
   </si>
   <si>
-    <t>http://rpps.esante.gouv.fr</t>
+    <t>https://rpps.esante.gouv.fr</t>
   </si>
   <si>
     <t>Practitioner.identifier:rpps.value</t>
@@ -1643,7 +1647,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="ADELI"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1652,7 +1656,7 @@
     <t>Practitioner.identifier:adeli.system</t>
   </si>
   <si>
-    <t>http://adeli.esante.gouv.fr</t>
+    <t>https://adeli.esante.gouv.fr</t>
   </si>
   <si>
     <t>Practitioner.identifier:adeli.value</t>
@@ -1711,7 +1715,19 @@
     <t>Practitioner.identifier:identifiantInterne.period</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
     <t>Practitioner.identifier:identifiantInterne.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Practitioner.active</t>
@@ -6072,7 +6088,7 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>119</v>
@@ -6084,7 +6100,7 @@
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -6189,7 +6205,7 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>119</v>
@@ -6419,7 +6435,7 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>119</v>
@@ -6649,7 +6665,7 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>102</v>
@@ -6766,7 +6782,7 @@
         <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>119</v>
@@ -6996,7 +7012,7 @@
         <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>119</v>
@@ -7226,7 +7242,7 @@
         <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>102</v>
@@ -7343,7 +7359,7 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>119</v>
@@ -7573,7 +7589,7 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>119</v>
@@ -7805,7 +7821,7 @@
         <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>102</v>
@@ -8037,7 +8053,7 @@
         <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>119</v>
@@ -8049,7 +8065,7 @@
         <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -8390,7 +8406,7 @@
         <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>119</v>
@@ -8620,7 +8636,7 @@
         <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>119</v>
@@ -8850,7 +8866,7 @@
         <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>102</v>
@@ -8967,7 +8983,7 @@
         <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>119</v>
@@ -9197,7 +9213,7 @@
         <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>119</v>
@@ -9427,7 +9443,7 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
@@ -9544,7 +9560,7 @@
         <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>119</v>
@@ -9774,7 +9790,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>119</v>
@@ -10006,7 +10022,7 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -10238,7 +10254,7 @@
         <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>102</v>
@@ -10587,7 +10603,7 @@
         <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>119</v>
@@ -10599,7 +10615,7 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -10704,7 +10720,7 @@
         <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>119</v>
@@ -10934,7 +10950,7 @@
         <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>119</v>
@@ -11164,7 +11180,7 @@
         <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>102</v>
@@ -11281,7 +11297,7 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>119</v>
@@ -11511,7 +11527,7 @@
         <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>119</v>
@@ -11743,7 +11759,7 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -11975,7 +11991,7 @@
         <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>119</v>
@@ -11987,7 +12003,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -12328,7 +12344,7 @@
         <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>119</v>
@@ -12558,7 +12574,7 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>119</v>
@@ -12788,7 +12804,7 @@
         <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>102</v>
@@ -12905,7 +12921,7 @@
         <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>119</v>
@@ -13135,7 +13151,7 @@
         <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>119</v>
@@ -13365,7 +13381,7 @@
         <v>90</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>102</v>
@@ -13597,7 +13613,7 @@
         <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>102</v>
@@ -16816,7 +16832,7 @@
         <v>233</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>384</v>
+        <v>491</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>385</v>
@@ -16835,7 +16851,7 @@
         <v>78</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>78</v>
@@ -16853,10 +16869,10 @@
         <v>158</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>78</v>
@@ -16906,7 +16922,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>449</v>
@@ -16938,7 +16954,7 @@
         <v>450</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>452</v>
@@ -16954,7 +16970,7 @@
         <v>78</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>454</v>
@@ -17025,7 +17041,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>459</v>
@@ -17054,7 +17070,7 @@
         <v>104</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M118" t="s" s="2">
         <v>461</v>
@@ -17142,7 +17158,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>468</v>
@@ -17257,7 +17273,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>475</v>
@@ -17374,13 +17390,13 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>78</v>
@@ -17405,7 +17421,7 @@
         <v>362</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M121" t="s" s="2">
         <v>364</v>
@@ -17493,7 +17509,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>372</v>
@@ -17608,7 +17624,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>373</v>
@@ -17725,7 +17741,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>374</v>
@@ -17844,7 +17860,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>383</v>
@@ -17873,7 +17889,7 @@
         <v>233</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>385</v>
@@ -17892,7 +17908,7 @@
         <v>78</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>78</v>
@@ -17910,10 +17926,10 @@
         <v>158</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>78</v>
@@ -17963,7 +17979,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>449</v>
@@ -17995,7 +18011,7 @@
         <v>450</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>452</v>
@@ -18011,7 +18027,7 @@
         <v>78</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>454</v>
@@ -18082,7 +18098,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>459</v>
@@ -18199,7 +18215,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>468</v>
@@ -18314,7 +18330,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>475</v>
@@ -18431,13 +18447,13 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>78</v>
@@ -18462,7 +18478,7 @@
         <v>362</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M130" t="s" s="2">
         <v>364</v>
@@ -18550,7 +18566,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>372</v>
@@ -18665,7 +18681,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>373</v>
@@ -18782,7 +18798,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>374</v>
@@ -18901,7 +18917,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>383</v>
@@ -18930,7 +18946,7 @@
         <v>233</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M134" t="s" s="2">
         <v>385</v>
@@ -18949,7 +18965,7 @@
         <v>78</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>78</v>
@@ -18967,10 +18983,10 @@
         <v>158</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>78</v>
@@ -19020,7 +19036,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>449</v>
@@ -19052,7 +19068,7 @@
         <v>450</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>452</v>
@@ -19068,7 +19084,7 @@
         <v>78</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>454</v>
@@ -19139,7 +19155,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>459</v>
@@ -19256,7 +19272,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>468</v>
@@ -19371,7 +19387,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>475</v>
@@ -19488,13 +19504,13 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>78</v>
@@ -19519,7 +19535,7 @@
         <v>362</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M139" t="s" s="2">
         <v>364</v>
@@ -19607,7 +19623,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>372</v>
@@ -19722,7 +19738,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>373</v>
@@ -19816,7 +19832,7 @@
         <v>80</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>119</v>
@@ -19828,7 +19844,7 @@
         <v>78</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>78</v>
@@ -19839,7 +19855,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>374</v>
@@ -19935,7 +19951,7 @@
         <v>90</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>102</v>
@@ -19958,7 +19974,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>383</v>
@@ -19987,7 +20003,7 @@
         <v>233</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M143" t="s" s="2">
         <v>385</v>
@@ -20006,7 +20022,7 @@
         <v>78</v>
       </c>
       <c r="S143" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>78</v>
@@ -20024,10 +20040,10 @@
         <v>158</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>78</v>
@@ -20054,7 +20070,7 @@
         <v>90</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>102</v>
@@ -20077,7 +20093,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>449</v>
@@ -20106,10 +20122,10 @@
         <v>137</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>452</v>
@@ -20144,7 +20160,7 @@
       </c>
       <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>78</v>
@@ -20171,7 +20187,7 @@
         <v>90</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>102</v>
@@ -20194,7 +20210,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>459</v>
@@ -20223,7 +20239,7 @@
         <v>104</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M145" t="s" s="2">
         <v>461</v>
@@ -20288,7 +20304,7 @@
         <v>90</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>102</v>
@@ -20311,7 +20327,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>468</v>
@@ -20345,7 +20361,9 @@
       <c r="M146" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="N146" s="2"/>
+      <c r="N146" t="s" s="2">
+        <v>543</v>
+      </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -20403,10 +20421,10 @@
         <v>90</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>102</v>
+        <v>544</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>78</v>
@@ -20426,7 +20444,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>475</v>
@@ -20520,10 +20538,10 @@
         <v>90</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>102</v>
+        <v>546</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>78</v>
@@ -20543,10 +20561,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20572,67 +20590,67 @@
         <v>297</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="O148" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="P148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q148" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="R148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF148" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="P148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q148" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="R148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20653,21 +20671,21 @@
         <v>78</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20690,19 +20708,19 @@
         <v>78</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>78</v>
@@ -20751,7 +20769,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20769,13 +20787,13 @@
         <v>78</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>78</v>
@@ -20783,10 +20801,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20898,10 +20916,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21015,13 +21033,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>78</v>
@@ -21043,13 +21061,13 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21132,10 +21150,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21161,16 +21179,16 @@
         <v>176</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>78</v>
@@ -21199,7 +21217,7 @@
       </c>
       <c r="Y153" s="2"/>
       <c r="Z153" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>78</v>
@@ -21217,7 +21235,7 @@
         <v>78</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -21235,13 +21253,13 @@
         <v>78</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>78</v>
@@ -21249,10 +21267,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21278,16 +21296,16 @@
         <v>104</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>78</v>
@@ -21336,7 +21354,7 @@
         <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21354,10 +21372,10 @@
         <v>78</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>78</v>
@@ -21368,14 +21386,14 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -21397,13 +21415,13 @@
         <v>104</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21453,7 +21471,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21471,13 +21489,13 @@
         <v>78</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>78</v>
@@ -21485,14 +21503,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -21514,13 +21532,13 @@
         <v>104</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -21570,7 +21588,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21588,13 +21606,13 @@
         <v>78</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>78</v>
@@ -21602,10 +21620,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21631,10 +21649,10 @@
         <v>104</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -21664,10 +21682,10 @@
         <v>158</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>78</v>
@@ -21685,7 +21703,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21703,13 +21721,13 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>78</v>
@@ -21717,10 +21735,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21746,10 +21764,10 @@
         <v>104</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -21779,10 +21797,10 @@
         <v>158</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>78</v>
@@ -21800,7 +21818,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21818,10 +21836,10 @@
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>78</v>
@@ -21832,10 +21850,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21861,14 +21879,14 @@
         <v>253</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
@@ -21917,7 +21935,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21935,10 +21953,10 @@
         <v>78</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>474</v>
@@ -21949,10 +21967,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21975,19 +21993,19 @@
         <v>78</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>78</v>
@@ -22024,17 +22042,17 @@
         <v>78</v>
       </c>
       <c r="AB160" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="AC160" s="2"/>
       <c r="AD160" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE160" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -22046,19 +22064,19 @@
         <v>209</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>78</v>
@@ -22066,13 +22084,13 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>78</v>
@@ -22094,19 +22112,19 @@
         <v>78</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>78</v>
@@ -22155,7 +22173,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -22167,19 +22185,19 @@
         <v>209</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>78</v>
@@ -22187,10 +22205,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22302,10 +22320,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22419,13 +22437,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>78</v>
@@ -22447,13 +22465,13 @@
         <v>78</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -22536,10 +22554,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22651,10 +22669,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22766,10 +22784,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22809,7 +22827,7 @@
       </c>
       <c r="Q167" s="2"/>
       <c r="R167" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="S167" t="s" s="2">
         <v>78</v>
@@ -22883,10 +22901,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22927,7 +22945,7 @@
         <v>78</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>78</v>
@@ -22946,7 +22964,7 @@
       </c>
       <c r="Y168" s="2"/>
       <c r="Z168" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>78</v>
@@ -22996,13 +23014,13 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>78</v>
@@ -23024,13 +23042,13 @@
         <v>78</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23113,10 +23131,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23228,10 +23246,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23322,7 +23340,7 @@
         <v>80</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>119</v>
@@ -23334,7 +23352,7 @@
         <v>78</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>78</v>
@@ -23345,10 +23363,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C172" t="s" s="2">
         <v>312</v>
@@ -23376,7 +23394,7 @@
         <v>111</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>202</v>
@@ -23439,7 +23457,7 @@
         <v>80</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>119</v>
@@ -23462,10 +23480,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23577,10 +23595,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23669,7 +23687,7 @@
         <v>80</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>119</v>
@@ -23692,10 +23710,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23809,10 +23827,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23872,7 +23890,7 @@
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>78</v>
@@ -23899,7 +23917,7 @@
         <v>90</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>102</v>
@@ -23922,13 +23940,13 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>78</v>
@@ -23953,7 +23971,7 @@
         <v>111</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="M177" t="s" s="2">
         <v>202</v>
@@ -24016,7 +24034,7 @@
         <v>80</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>119</v>
@@ -24039,10 +24057,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24154,10 +24172,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24246,7 +24264,7 @@
         <v>80</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>119</v>
@@ -24269,10 +24287,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24312,7 +24330,7 @@
       </c>
       <c r="Q180" s="2"/>
       <c r="R180" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>78</v>
@@ -24386,10 +24404,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24478,7 +24496,7 @@
         <v>90</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>102</v>
@@ -24501,13 +24519,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>78</v>
@@ -24595,7 +24613,7 @@
         <v>80</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>119</v>
@@ -24618,10 +24636,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24733,10 +24751,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24825,7 +24843,7 @@
         <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>119</v>
@@ -24848,10 +24866,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24891,7 +24909,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>78</v>
@@ -24965,10 +24983,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25057,7 +25075,7 @@
         <v>90</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>102</v>
@@ -25080,13 +25098,13 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D187" t="s" s="2">
         <v>78</v>
@@ -25111,7 +25129,7 @@
         <v>111</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="M187" t="s" s="2">
         <v>202</v>
@@ -25174,7 +25192,7 @@
         <v>80</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>119</v>
@@ -25197,10 +25215,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25312,10 +25330,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25404,7 +25422,7 @@
         <v>80</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>119</v>
@@ -25427,10 +25445,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25470,7 +25488,7 @@
       </c>
       <c r="Q190" s="2"/>
       <c r="R190" t="s" s="2">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="S190" t="s" s="2">
         <v>78</v>
@@ -25544,10 +25562,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25636,7 +25654,7 @@
         <v>90</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>102</v>
@@ -25659,13 +25677,13 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="D192" t="s" s="2">
         <v>78</v>
@@ -25753,7 +25771,7 @@
         <v>80</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ192" t="s" s="2">
         <v>119</v>
@@ -25776,10 +25794,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25891,10 +25909,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25983,7 +26001,7 @@
         <v>80</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ194" t="s" s="2">
         <v>119</v>
@@ -26006,10 +26024,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26049,7 +26067,7 @@
       </c>
       <c r="Q195" s="2"/>
       <c r="R195" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="S195" t="s" s="2">
         <v>78</v>
@@ -26123,10 +26141,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26215,7 +26233,7 @@
         <v>90</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ196" t="s" s="2">
         <v>102</v>
@@ -26238,13 +26256,13 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="D197" t="s" s="2">
         <v>78</v>
@@ -26269,7 +26287,7 @@
         <v>111</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="M197" t="s" s="2">
         <v>202</v>
@@ -26332,7 +26350,7 @@
         <v>80</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>119</v>
@@ -26355,10 +26373,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26470,10 +26488,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26562,7 +26580,7 @@
         <v>80</v>
       </c>
       <c r="AI199" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ199" t="s" s="2">
         <v>119</v>
@@ -26585,10 +26603,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26628,7 +26646,7 @@
       </c>
       <c r="Q200" s="2"/>
       <c r="R200" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="S200" t="s" s="2">
         <v>78</v>
@@ -26702,10 +26720,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26794,7 +26812,7 @@
         <v>90</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ201" t="s" s="2">
         <v>102</v>
@@ -26817,13 +26835,13 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>78</v>
@@ -26848,7 +26866,7 @@
         <v>111</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="M202" t="s" s="2">
         <v>202</v>
@@ -26911,7 +26929,7 @@
         <v>80</v>
       </c>
       <c r="AI202" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ202" t="s" s="2">
         <v>119</v>
@@ -26934,10 +26952,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27049,10 +27067,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27141,7 +27159,7 @@
         <v>80</v>
       </c>
       <c r="AI204" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ204" t="s" s="2">
         <v>119</v>
@@ -27164,10 +27182,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27207,7 +27225,7 @@
       </c>
       <c r="Q205" s="2"/>
       <c r="R205" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="S205" t="s" s="2">
         <v>78</v>
@@ -27281,10 +27299,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27373,7 +27391,7 @@
         <v>90</v>
       </c>
       <c r="AI206" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ206" t="s" s="2">
         <v>102</v>
@@ -27396,10 +27414,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27439,7 +27457,7 @@
       </c>
       <c r="Q207" s="2"/>
       <c r="R207" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="S207" t="s" s="2">
         <v>78</v>
@@ -27513,10 +27531,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27605,7 +27623,7 @@
         <v>90</v>
       </c>
       <c r="AI208" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ208" t="s" s="2">
         <v>102</v>
@@ -27628,10 +27646,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27657,10 +27675,10 @@
         <v>176</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -27672,7 +27690,7 @@
         <v>78</v>
       </c>
       <c r="S209" t="s" s="2">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="T209" t="s" s="2">
         <v>78</v>
@@ -27690,10 +27708,10 @@
         <v>236</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>78</v>
@@ -27711,7 +27729,7 @@
         <v>78</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
@@ -27720,7 +27738,7 @@
         <v>90</v>
       </c>
       <c r="AI209" t="s" s="2">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="AJ209" t="s" s="2">
         <v>102</v>
@@ -27729,13 +27747,13 @@
         <v>78</v>
       </c>
       <c r="AL209" t="s" s="2">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="AM209" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>78</v>
@@ -27743,10 +27761,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27772,16 +27790,16 @@
         <v>104</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>78</v>
@@ -27830,7 +27848,7 @@
         <v>78</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>79</v>
@@ -27848,10 +27866,10 @@
         <v>78</v>
       </c>
       <c r="AL210" t="s" s="2">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="AM210" t="s" s="2">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="AN210" t="s" s="2">
         <v>467</v>
@@ -27862,10 +27880,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27891,16 +27909,16 @@
         <v>176</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>78</v>
@@ -27928,10 +27946,10 @@
         <v>236</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>78</v>
@@ -27949,7 +27967,7 @@
         <v>78</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>79</v>
@@ -27967,13 +27985,13 @@
         <v>78</v>
       </c>
       <c r="AL211" t="s" s="2">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="AM211" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>78</v>
@@ -27981,10 +27999,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28007,16 +28025,16 @@
         <v>91</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
@@ -28066,7 +28084,7 @@
         <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
@@ -28098,10 +28116,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28127,10 +28145,10 @@
         <v>253</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -28181,7 +28199,7 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>79</v>
@@ -28202,7 +28220,7 @@
         <v>199</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="AN213" t="s" s="2">
         <v>474</v>
@@ -28213,10 +28231,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28239,19 +28257,19 @@
         <v>78</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="O214" t="s" s="2">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -28300,7 +28318,7 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
@@ -28318,13 +28336,13 @@
         <v>78</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>78</v>
@@ -28332,10 +28350,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28361,14 +28379,14 @@
         <v>176</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>78</v>
@@ -28396,28 +28414,28 @@
         <v>236</v>
       </c>
       <c r="Y215" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="Z215" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="AA215" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB215" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC215" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD215" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE215" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF215" t="s" s="2">
         <v>781</v>
-      </c>
-      <c r="Z215" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="AA215" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB215" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC215" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD215" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE215" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF215" t="s" s="2">
-        <v>777</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -28435,13 +28453,13 @@
         <v>78</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>78</v>
@@ -28449,10 +28467,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28475,17 +28493,17 @@
         <v>91</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" t="s" s="2">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>78</v>
@@ -28534,7 +28552,7 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28552,13 +28570,13 @@
         <v>78</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>78</v>
@@ -28566,10 +28584,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28592,17 +28610,17 @@
         <v>78</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
@@ -28651,7 +28669,7 @@
         <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>
@@ -28672,10 +28690,10 @@
         <v>78</v>
       </c>
       <c r="AM217" t="s" s="2">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>78</v>
@@ -28683,10 +28701,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28709,13 +28727,13 @@
         <v>78</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -28754,7 +28772,7 @@
         <v>78</v>
       </c>
       <c r="AB218" t="s" s="2">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="AC218" s="2"/>
       <c r="AD218" t="s" s="2">
@@ -28764,7 +28782,7 @@
         <v>117</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>79</v>
@@ -28782,13 +28800,13 @@
         <v>78</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="AM218" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="AO218" t="s" s="2">
         <v>78</v>
@@ -28796,10 +28814,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -28911,10 +28929,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29028,14 +29046,14 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="E221" s="2"/>
       <c r="F221" t="s" s="2">
@@ -29057,10 +29075,10 @@
         <v>111</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="N221" t="s" s="2">
         <v>114</v>
@@ -29115,7 +29133,7 @@
         <v>78</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>79</v>
@@ -29147,10 +29165,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29176,14 +29194,14 @@
         <v>362</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>78</v>
@@ -29232,7 +29250,7 @@
         <v>78</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>79</v>
@@ -29253,7 +29271,7 @@
         <v>78</v>
       </c>
       <c r="AM222" t="s" s="2">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="AN222" t="s" s="2">
         <v>78</v>
@@ -29264,10 +29282,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29293,10 +29311,10 @@
         <v>233</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -29327,7 +29345,7 @@
       </c>
       <c r="Y223" s="2"/>
       <c r="Z223" t="s" s="2">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>78</v>
@@ -29345,7 +29363,7 @@
         <v>78</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>90</v>
@@ -29366,10 +29384,10 @@
         <v>78</v>
       </c>
       <c r="AM223" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="AO223" t="s" s="2">
         <v>78</v>
@@ -29377,10 +29395,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29406,14 +29424,14 @@
         <v>253</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" t="s" s="2">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>78</v>
@@ -29462,7 +29480,7 @@
         <v>78</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>79</v>
@@ -29483,10 +29501,10 @@
         <v>78</v>
       </c>
       <c r="AM224" t="s" s="2">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>78</v>
@@ -29494,10 +29512,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29523,10 +29541,10 @@
         <v>476</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -29577,7 +29595,7 @@
         <v>78</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>79</v>
@@ -29598,7 +29616,7 @@
         <v>78</v>
       </c>
       <c r="AM225" t="s" s="2">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="AN225" t="s" s="2">
         <v>78</v>
@@ -29609,13 +29627,13 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="D226" t="s" s="2">
         <v>78</v>
@@ -29637,13 +29655,13 @@
         <v>78</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -29694,7 +29712,7 @@
         <v>78</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>79</v>
@@ -29712,13 +29730,13 @@
         <v>78</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="AM226" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="AN226" t="s" s="2">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="AO226" t="s" s="2">
         <v>78</v>
@@ -29726,10 +29744,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -29841,10 +29859,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -29954,13 +29972,13 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="D229" t="s" s="2">
         <v>78</v>
@@ -29982,13 +30000,13 @@
         <v>78</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -30071,10 +30089,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30186,10 +30204,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30280,7 +30298,7 @@
         <v>80</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ231" t="s" s="2">
         <v>119</v>
@@ -30292,7 +30310,7 @@
         <v>78</v>
       </c>
       <c r="AM231" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN231" t="s" s="2">
         <v>78</v>
@@ -30303,13 +30321,13 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="D232" t="s" s="2">
         <v>78</v>
@@ -30397,7 +30415,7 @@
         <v>80</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>119</v>
@@ -30420,10 +30438,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30535,10 +30553,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30627,7 +30645,7 @@
         <v>80</v>
       </c>
       <c r="AI234" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ234" t="s" s="2">
         <v>119</v>
@@ -30650,10 +30668,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30693,7 +30711,7 @@
       </c>
       <c r="Q235" s="2"/>
       <c r="R235" t="s" s="2">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="S235" t="s" s="2">
         <v>78</v>
@@ -30767,10 +30785,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -30830,7 +30848,7 @@
       </c>
       <c r="Y236" s="2"/>
       <c r="Z236" t="s" s="2">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="AA236" t="s" s="2">
         <v>78</v>
@@ -30857,7 +30875,7 @@
         <v>90</v>
       </c>
       <c r="AI236" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ236" t="s" s="2">
         <v>102</v>
@@ -30880,13 +30898,13 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="D237" t="s" s="2">
         <v>78</v>
@@ -30974,7 +30992,7 @@
         <v>80</v>
       </c>
       <c r="AI237" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ237" t="s" s="2">
         <v>119</v>
@@ -30997,10 +31015,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -31112,10 +31130,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31204,7 +31222,7 @@
         <v>80</v>
       </c>
       <c r="AI239" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ239" t="s" s="2">
         <v>119</v>
@@ -31227,10 +31245,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31270,7 +31288,7 @@
       </c>
       <c r="Q240" s="2"/>
       <c r="R240" t="s" s="2">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="S240" t="s" s="2">
         <v>78</v>
@@ -31344,10 +31362,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31407,7 +31425,7 @@
       </c>
       <c r="Y241" s="2"/>
       <c r="Z241" t="s" s="2">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="AA241" t="s" s="2">
         <v>78</v>
@@ -31434,7 +31452,7 @@
         <v>90</v>
       </c>
       <c r="AI241" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ241" t="s" s="2">
         <v>102</v>
@@ -31457,13 +31475,13 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="D242" t="s" s="2">
         <v>78</v>
@@ -31551,7 +31569,7 @@
         <v>80</v>
       </c>
       <c r="AI242" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ242" t="s" s="2">
         <v>119</v>
@@ -31574,10 +31592,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31689,10 +31707,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31781,7 +31799,7 @@
         <v>80</v>
       </c>
       <c r="AI244" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ244" t="s" s="2">
         <v>119</v>
@@ -31804,10 +31822,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -31847,7 +31865,7 @@
       </c>
       <c r="Q245" s="2"/>
       <c r="R245" t="s" s="2">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="S245" t="s" s="2">
         <v>78</v>
@@ -31921,10 +31939,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -31984,7 +32002,7 @@
       </c>
       <c r="Y246" s="2"/>
       <c r="Z246" t="s" s="2">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>78</v>
@@ -32011,7 +32029,7 @@
         <v>90</v>
       </c>
       <c r="AI246" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ246" t="s" s="2">
         <v>102</v>
@@ -32034,10 +32052,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32077,7 +32095,7 @@
       </c>
       <c r="Q247" s="2"/>
       <c r="R247" t="s" s="2">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="S247" t="s" s="2">
         <v>78</v>
@@ -32151,10 +32169,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32243,7 +32261,7 @@
         <v>90</v>
       </c>
       <c r="AI248" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ248" t="s" s="2">
         <v>102</v>
@@ -32266,14 +32284,14 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="E249" s="2"/>
       <c r="F249" t="s" s="2">
@@ -32295,10 +32313,10 @@
         <v>111</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="N249" t="s" s="2">
         <v>114</v>
@@ -32353,7 +32371,7 @@
         <v>78</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>79</v>
@@ -32385,10 +32403,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32414,14 +32432,14 @@
         <v>362</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" t="s" s="2">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="P250" t="s" s="2">
         <v>78</v>
@@ -32470,7 +32488,7 @@
         <v>78</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>79</v>
@@ -32491,7 +32509,7 @@
         <v>78</v>
       </c>
       <c r="AM250" t="s" s="2">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="AN250" t="s" s="2">
         <v>78</v>
@@ -32502,10 +32520,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32531,10 +32549,10 @@
         <v>233</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="N251" s="2"/>
       <c r="O251" s="2"/>
@@ -32565,7 +32583,7 @@
       </c>
       <c r="Y251" s="2"/>
       <c r="Z251" t="s" s="2">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="AA251" t="s" s="2">
         <v>78</v>
@@ -32583,7 +32601,7 @@
         <v>78</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>90</v>
@@ -32604,10 +32622,10 @@
         <v>78</v>
       </c>
       <c r="AM251" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="AN251" t="s" s="2">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="AO251" t="s" s="2">
         <v>78</v>
@@ -32615,10 +32633,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32730,10 +32748,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -32824,7 +32842,7 @@
         <v>80</v>
       </c>
       <c r="AI253" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ253" t="s" s="2">
         <v>119</v>
@@ -32836,7 +32854,7 @@
         <v>78</v>
       </c>
       <c r="AM253" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN253" t="s" s="2">
         <v>78</v>
@@ -32847,10 +32865,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -32922,14 +32940,14 @@
         <v>78</v>
       </c>
       <c r="AB254" t="s" s="2">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="AC254" s="2"/>
       <c r="AD254" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE254" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="AF254" t="s" s="2">
         <v>398</v>
@@ -32941,7 +32959,7 @@
         <v>80</v>
       </c>
       <c r="AI254" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ254" t="s" s="2">
         <v>102</v>
@@ -32964,13 +32982,13 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>78</v>
@@ -33033,7 +33051,7 @@
       </c>
       <c r="Y255" s="2"/>
       <c r="Z255" t="s" s="2">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="AA255" t="s" s="2">
         <v>78</v>
@@ -33060,7 +33078,7 @@
         <v>80</v>
       </c>
       <c r="AI255" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ255" t="s" s="2">
         <v>102</v>
@@ -33083,13 +33101,13 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="D256" t="s" s="2">
         <v>78</v>
@@ -33152,7 +33170,7 @@
       </c>
       <c r="Y256" s="2"/>
       <c r="Z256" t="s" s="2">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="AA256" t="s" s="2">
         <v>78</v>
@@ -33179,7 +33197,7 @@
         <v>80</v>
       </c>
       <c r="AI256" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ256" t="s" s="2">
         <v>102</v>
@@ -33202,10 +33220,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -33298,7 +33316,7 @@
         <v>90</v>
       </c>
       <c r="AI257" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ257" t="s" s="2">
         <v>102</v>
@@ -33321,10 +33339,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33350,14 +33368,14 @@
         <v>253</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" t="s" s="2">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>78</v>
@@ -33406,7 +33424,7 @@
         <v>78</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>79</v>
@@ -33427,10 +33445,10 @@
         <v>78</v>
       </c>
       <c r="AM258" t="s" s="2">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="AN258" t="s" s="2">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="AO258" t="s" s="2">
         <v>78</v>
@@ -33438,10 +33456,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33553,10 +33571,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33647,7 +33665,7 @@
         <v>80</v>
       </c>
       <c r="AI260" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ260" t="s" s="2">
         <v>119</v>
@@ -33659,7 +33677,7 @@
         <v>78</v>
       </c>
       <c r="AM260" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN260" t="s" s="2">
         <v>78</v>
@@ -33670,10 +33688,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33699,7 +33717,7 @@
         <v>260</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="M261" t="s" s="2">
         <v>262</v>
@@ -33787,10 +33805,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33816,7 +33834,7 @@
         <v>260</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="M262" t="s" s="2">
         <v>271</v>
@@ -33906,10 +33924,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -33932,13 +33950,13 @@
         <v>78</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="N263" s="2"/>
       <c r="O263" s="2"/>
@@ -33989,7 +34007,7 @@
         <v>78</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>79</v>
@@ -34010,7 +34028,7 @@
         <v>78</v>
       </c>
       <c r="AM263" t="s" s="2">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="AN263" t="s" s="2">
         <v>78</v>
@@ -34021,13 +34039,13 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="D264" t="s" s="2">
         <v>78</v>
@@ -34049,13 +34067,13 @@
         <v>78</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="N264" s="2"/>
       <c r="O264" s="2"/>
@@ -34106,7 +34124,7 @@
         <v>78</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>79</v>
@@ -34124,13 +34142,13 @@
         <v>78</v>
       </c>
       <c r="AL264" t="s" s="2">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="AM264" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="AN264" t="s" s="2">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="AO264" t="s" s="2">
         <v>78</v>
@@ -34138,10 +34156,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -34253,10 +34271,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34370,14 +34388,14 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="E267" s="2"/>
       <c r="F267" t="s" s="2">
@@ -34399,10 +34417,10 @@
         <v>111</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="N267" t="s" s="2">
         <v>114</v>
@@ -34457,7 +34475,7 @@
         <v>78</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>79</v>
@@ -34489,10 +34507,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34518,14 +34536,14 @@
         <v>362</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="N268" s="2"/>
       <c r="O268" t="s" s="2">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="P268" t="s" s="2">
         <v>78</v>
@@ -34574,7 +34592,7 @@
         <v>78</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>79</v>
@@ -34595,7 +34613,7 @@
         <v>78</v>
       </c>
       <c r="AM268" t="s" s="2">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="AN268" t="s" s="2">
         <v>78</v>
@@ -34606,10 +34624,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -34635,10 +34653,10 @@
         <v>233</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="N269" s="2"/>
       <c r="O269" s="2"/>
@@ -34669,7 +34687,7 @@
       </c>
       <c r="Y269" s="2"/>
       <c r="Z269" t="s" s="2">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="AA269" t="s" s="2">
         <v>78</v>
@@ -34687,7 +34705,7 @@
         <v>78</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>90</v>
@@ -34708,10 +34726,10 @@
         <v>78</v>
       </c>
       <c r="AM269" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="AN269" t="s" s="2">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="AO269" t="s" s="2">
         <v>78</v>
@@ -34719,10 +34737,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -34834,10 +34852,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -34928,7 +34946,7 @@
         <v>80</v>
       </c>
       <c r="AI271" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ271" t="s" s="2">
         <v>119</v>
@@ -34940,7 +34958,7 @@
         <v>78</v>
       </c>
       <c r="AM271" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN271" t="s" s="2">
         <v>78</v>
@@ -34951,10 +34969,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -35026,14 +35044,14 @@
         <v>78</v>
       </c>
       <c r="AB272" t="s" s="2">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="AC272" s="2"/>
       <c r="AD272" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE272" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="AF272" t="s" s="2">
         <v>398</v>
@@ -35045,7 +35063,7 @@
         <v>80</v>
       </c>
       <c r="AI272" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ272" t="s" s="2">
         <v>102</v>
@@ -35068,13 +35086,13 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>78</v>
@@ -35099,7 +35117,7 @@
         <v>154</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="M273" t="s" s="2">
         <v>395</v>
@@ -35137,7 +35155,7 @@
       </c>
       <c r="Y273" s="2"/>
       <c r="Z273" t="s" s="2">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="AA273" t="s" s="2">
         <v>78</v>
@@ -35164,7 +35182,7 @@
         <v>80</v>
       </c>
       <c r="AI273" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ273" t="s" s="2">
         <v>102</v>
@@ -35187,10 +35205,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C274" t="s" s="2">
         <v>337</v>
@@ -35218,7 +35236,7 @@
         <v>154</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="M274" t="s" s="2">
         <v>395</v>
@@ -35283,7 +35301,7 @@
         <v>80</v>
       </c>
       <c r="AI274" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ274" t="s" s="2">
         <v>102</v>
@@ -35306,10 +35324,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -35402,7 +35420,7 @@
         <v>90</v>
       </c>
       <c r="AI275" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ275" t="s" s="2">
         <v>102</v>
@@ -35425,10 +35443,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -35454,14 +35472,14 @@
         <v>253</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="N276" s="2"/>
       <c r="O276" t="s" s="2">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="P276" t="s" s="2">
         <v>78</v>
@@ -35510,7 +35528,7 @@
         <v>78</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>79</v>
@@ -35531,10 +35549,10 @@
         <v>78</v>
       </c>
       <c r="AM276" t="s" s="2">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="AN276" t="s" s="2">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="AO276" t="s" s="2">
         <v>78</v>
@@ -35542,10 +35560,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -35657,10 +35675,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35751,7 +35769,7 @@
         <v>80</v>
       </c>
       <c r="AI278" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ278" t="s" s="2">
         <v>119</v>
@@ -35763,7 +35781,7 @@
         <v>78</v>
       </c>
       <c r="AM278" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN278" t="s" s="2">
         <v>78</v>
@@ -35774,10 +35792,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35803,7 +35821,7 @@
         <v>260</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="M279" t="s" s="2">
         <v>262</v>
@@ -35891,10 +35909,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -35920,7 +35938,7 @@
         <v>260</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="M280" t="s" s="2">
         <v>271</v>
@@ -36010,10 +36028,10 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -36039,10 +36057,10 @@
         <v>476</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="N281" s="2"/>
       <c r="O281" s="2"/>
@@ -36093,7 +36111,7 @@
         <v>78</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>79</v>
@@ -36114,7 +36132,7 @@
         <v>78</v>
       </c>
       <c r="AM281" t="s" s="2">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="AN281" t="s" s="2">
         <v>78</v>
@@ -36125,13 +36143,13 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="D282" t="s" s="2">
         <v>78</v>
@@ -36153,13 +36171,13 @@
         <v>78</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="N282" s="2"/>
       <c r="O282" s="2"/>
@@ -36210,7 +36228,7 @@
         <v>78</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>79</v>
@@ -36228,13 +36246,13 @@
         <v>78</v>
       </c>
       <c r="AL282" t="s" s="2">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="AM282" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="AN282" t="s" s="2">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="AO282" t="s" s="2">
         <v>78</v>
@@ -36242,10 +36260,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -36357,10 +36375,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -36474,14 +36492,14 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="E285" s="2"/>
       <c r="F285" t="s" s="2">
@@ -36503,10 +36521,10 @@
         <v>111</v>
       </c>
       <c r="L285" t="s" s="2">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="M285" t="s" s="2">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="N285" t="s" s="2">
         <v>114</v>
@@ -36561,7 +36579,7 @@
         <v>78</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="AG285" t="s" s="2">
         <v>79</v>
@@ -36593,10 +36611,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -36622,14 +36640,14 @@
         <v>362</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="N286" s="2"/>
       <c r="O286" t="s" s="2">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="P286" t="s" s="2">
         <v>78</v>
@@ -36678,7 +36696,7 @@
         <v>78</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>79</v>
@@ -36699,7 +36717,7 @@
         <v>78</v>
       </c>
       <c r="AM286" t="s" s="2">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="AN286" t="s" s="2">
         <v>78</v>
@@ -36710,10 +36728,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -36739,10 +36757,10 @@
         <v>233</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="N287" s="2"/>
       <c r="O287" s="2"/>
@@ -36773,7 +36791,7 @@
       </c>
       <c r="Y287" s="2"/>
       <c r="Z287" t="s" s="2">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="AA287" t="s" s="2">
         <v>78</v>
@@ -36791,7 +36809,7 @@
         <v>78</v>
       </c>
       <c r="AF287" t="s" s="2">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>90</v>
@@ -36806,16 +36824,16 @@
         <v>102</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM287" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="AN287" t="s" s="2">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="AO287" t="s" s="2">
         <v>78</v>
@@ -36823,10 +36841,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -36938,10 +36956,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -37032,7 +37050,7 @@
         <v>80</v>
       </c>
       <c r="AI289" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ289" t="s" s="2">
         <v>119</v>
@@ -37044,7 +37062,7 @@
         <v>78</v>
       </c>
       <c r="AM289" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN289" t="s" s="2">
         <v>78</v>
@@ -37055,10 +37073,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -37130,7 +37148,7 @@
         <v>78</v>
       </c>
       <c r="AB290" t="s" s="2">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="AC290" s="2"/>
       <c r="AD290" t="s" s="2">
@@ -37149,7 +37167,7 @@
         <v>80</v>
       </c>
       <c r="AI290" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ290" t="s" s="2">
         <v>102</v>
@@ -37172,13 +37190,13 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
+        <v>953</v>
+      </c>
+      <c r="B291" t="s" s="2">
+        <v>892</v>
+      </c>
+      <c r="C291" t="s" s="2">
         <v>949</v>
-      </c>
-      <c r="B291" t="s" s="2">
-        <v>888</v>
-      </c>
-      <c r="C291" t="s" s="2">
-        <v>945</v>
       </c>
       <c r="D291" t="s" s="2">
         <v>78</v>
@@ -37203,7 +37221,7 @@
         <v>154</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="M291" t="s" s="2">
         <v>395</v>
@@ -37241,7 +37259,7 @@
       </c>
       <c r="Y291" s="2"/>
       <c r="Z291" t="s" s="2">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="AA291" t="s" s="2">
         <v>78</v>
@@ -37268,7 +37286,7 @@
         <v>80</v>
       </c>
       <c r="AI291" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ291" t="s" s="2">
         <v>102</v>
@@ -37291,13 +37309,13 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="D292" t="s" s="2">
         <v>78</v>
@@ -37322,7 +37340,7 @@
         <v>154</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="M292" t="s" s="2">
         <v>395</v>
@@ -37360,7 +37378,7 @@
       </c>
       <c r="Y292" s="2"/>
       <c r="Z292" t="s" s="2">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="AA292" t="s" s="2">
         <v>78</v>
@@ -37387,7 +37405,7 @@
         <v>80</v>
       </c>
       <c r="AI292" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ292" t="s" s="2">
         <v>102</v>
@@ -37410,10 +37428,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -37506,7 +37524,7 @@
         <v>90</v>
       </c>
       <c r="AI293" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ293" t="s" s="2">
         <v>102</v>
@@ -37529,10 +37547,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -37558,14 +37576,14 @@
         <v>253</v>
       </c>
       <c r="L294" t="s" s="2">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="M294" t="s" s="2">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="N294" s="2"/>
       <c r="O294" t="s" s="2">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="P294" t="s" s="2">
         <v>78</v>
@@ -37614,7 +37632,7 @@
         <v>78</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>79</v>
@@ -37635,10 +37653,10 @@
         <v>78</v>
       </c>
       <c r="AM294" t="s" s="2">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="AN294" t="s" s="2">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="AO294" t="s" s="2">
         <v>78</v>
@@ -37646,10 +37664,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -37761,10 +37779,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -37855,7 +37873,7 @@
         <v>80</v>
       </c>
       <c r="AI296" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ296" t="s" s="2">
         <v>119</v>
@@ -37867,7 +37885,7 @@
         <v>78</v>
       </c>
       <c r="AM296" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN296" t="s" s="2">
         <v>78</v>
@@ -37878,10 +37896,10 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -37907,7 +37925,7 @@
         <v>260</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="M297" t="s" s="2">
         <v>262</v>
@@ -37978,7 +37996,7 @@
         <v>102</v>
       </c>
       <c r="AK297" t="s" s="2">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="AL297" t="s" s="2">
         <v>266</v>
@@ -37995,10 +38013,10 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -38024,7 +38042,7 @@
         <v>260</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="M298" t="s" s="2">
         <v>271</v>
@@ -38097,7 +38115,7 @@
         <v>102</v>
       </c>
       <c r="AK298" t="s" s="2">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="AL298" t="s" s="2">
         <v>275</v>
@@ -38114,10 +38132,10 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -38143,10 +38161,10 @@
         <v>476</v>
       </c>
       <c r="L299" t="s" s="2">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="M299" t="s" s="2">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="N299" s="2"/>
       <c r="O299" s="2"/>
@@ -38197,7 +38215,7 @@
         <v>78</v>
       </c>
       <c r="AF299" t="s" s="2">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="AG299" t="s" s="2">
         <v>79</v>
@@ -38218,7 +38236,7 @@
         <v>78</v>
       </c>
       <c r="AM299" t="s" s="2">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="AN299" t="s" s="2">
         <v>78</v>
@@ -38229,10 +38247,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -38255,19 +38273,19 @@
         <v>78</v>
       </c>
       <c r="K300" t="s" s="2">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="L300" t="s" s="2">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="M300" t="s" s="2">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="N300" t="s" s="2">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="O300" t="s" s="2">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="P300" t="s" s="2">
         <v>78</v>
@@ -38296,7 +38314,7 @@
       </c>
       <c r="Y300" s="2"/>
       <c r="Z300" t="s" s="2">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="AA300" t="s" s="2">
         <v>78</v>
@@ -38314,7 +38332,7 @@
         <v>78</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>79</v>
@@ -38332,10 +38350,10 @@
         <v>78</v>
       </c>
       <c r="AL300" t="s" s="2">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="AM300" t="s" s="2">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="AN300" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="978">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1212,7 +1212,7 @@
   </si>
   <si>
     <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
@@ -1535,10 +1535,6 @@
   </si>
   <si>
     <t>Practitioner.identifier:idNatPs.type</t>
-  </si>
-  <si>
-    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1691,7 +1687,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="INTRN"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -16832,7 +16828,7 @@
         <v>233</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>491</v>
+        <v>384</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>385</v>
@@ -16851,7 +16847,7 @@
         <v>78</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>78</v>
@@ -16869,10 +16865,10 @@
         <v>158</v>
       </c>
       <c r="Y116" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z116" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>78</v>
@@ -16922,7 +16918,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>449</v>
@@ -16954,7 +16950,7 @@
         <v>450</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>452</v>
@@ -16970,7 +16966,7 @@
         <v>78</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>454</v>
@@ -17041,7 +17037,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>459</v>
@@ -17070,7 +17066,7 @@
         <v>104</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="M118" t="s" s="2">
         <v>461</v>
@@ -17158,7 +17154,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>468</v>
@@ -17273,7 +17269,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>475</v>
@@ -17390,13 +17386,13 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>78</v>
@@ -17421,7 +17417,7 @@
         <v>362</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M121" t="s" s="2">
         <v>364</v>
@@ -17509,7 +17505,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>372</v>
@@ -17624,7 +17620,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>373</v>
@@ -17741,7 +17737,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>374</v>
@@ -17860,7 +17856,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>383</v>
@@ -17889,7 +17885,7 @@
         <v>233</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>385</v>
@@ -17908,7 +17904,7 @@
         <v>78</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>78</v>
@@ -17926,10 +17922,10 @@
         <v>158</v>
       </c>
       <c r="Y125" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z125" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>78</v>
@@ -17979,7 +17975,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>449</v>
@@ -18011,7 +18007,7 @@
         <v>450</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>452</v>
@@ -18027,7 +18023,7 @@
         <v>78</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>454</v>
@@ -18098,7 +18094,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>459</v>
@@ -18215,7 +18211,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>468</v>
@@ -18330,7 +18326,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>475</v>
@@ -18447,13 +18443,13 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>78</v>
@@ -18478,7 +18474,7 @@
         <v>362</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M130" t="s" s="2">
         <v>364</v>
@@ -18566,7 +18562,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>372</v>
@@ -18681,7 +18677,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>373</v>
@@ -18798,7 +18794,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>374</v>
@@ -18917,7 +18913,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>383</v>
@@ -18946,7 +18942,7 @@
         <v>233</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M134" t="s" s="2">
         <v>385</v>
@@ -18965,7 +18961,7 @@
         <v>78</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>78</v>
@@ -18983,10 +18979,10 @@
         <v>158</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z134" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>78</v>
@@ -19036,7 +19032,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>449</v>
@@ -19068,7 +19064,7 @@
         <v>450</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>452</v>
@@ -19084,7 +19080,7 @@
         <v>78</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>454</v>
@@ -19155,7 +19151,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>459</v>
@@ -19272,7 +19268,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>468</v>
@@ -19387,7 +19383,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>475</v>
@@ -19504,13 +19500,13 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>78</v>
@@ -19535,7 +19531,7 @@
         <v>362</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="M139" t="s" s="2">
         <v>364</v>
@@ -19623,7 +19619,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>372</v>
@@ -19738,7 +19734,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>373</v>
@@ -19855,7 +19851,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>374</v>
@@ -19974,7 +19970,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>383</v>
@@ -20003,7 +19999,7 @@
         <v>233</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M143" t="s" s="2">
         <v>385</v>
@@ -20022,7 +20018,7 @@
         <v>78</v>
       </c>
       <c r="S143" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>78</v>
@@ -20040,10 +20036,10 @@
         <v>158</v>
       </c>
       <c r="Y143" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z143" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>78</v>
@@ -20093,7 +20089,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>449</v>
@@ -20122,10 +20118,10 @@
         <v>137</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>452</v>
@@ -20160,7 +20156,7 @@
       </c>
       <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>78</v>
@@ -20210,7 +20206,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>459</v>
@@ -20239,7 +20235,7 @@
         <v>104</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="M145" t="s" s="2">
         <v>461</v>
@@ -20327,7 +20323,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>468</v>
@@ -20362,7 +20358,7 @@
         <v>470</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -20424,7 +20420,7 @@
         <v>209</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>78</v>
@@ -20444,7 +20440,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>475</v>
@@ -20541,7 +20537,7 @@
         <v>209</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>78</v>
@@ -20561,10 +20557,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20590,23 +20586,23 @@
         <v>297</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="N148" t="s" s="2">
+      <c r="O148" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="O148" t="s" s="2">
+      <c r="P148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q148" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="P148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q148" t="s" s="2">
-        <v>552</v>
-      </c>
       <c r="R148" t="s" s="2">
         <v>78</v>
       </c>
@@ -20650,7 +20646,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20671,21 +20667,21 @@
         <v>78</v>
       </c>
       <c r="AM148" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO148" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AN148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO148" t="s" s="2">
-        <v>554</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20708,19 +20704,19 @@
         <v>78</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L149" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="L149" t="s" s="2">
+      <c r="M149" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>78</v>
@@ -20769,7 +20765,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20787,13 +20783,13 @@
         <v>78</v>
       </c>
       <c r="AL149" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AM149" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="AM149" t="s" s="2">
+      <c r="AN149" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>78</v>
@@ -20801,10 +20797,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20916,10 +20912,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21033,13 +21029,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C152" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C152" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>78</v>
@@ -21061,13 +21057,13 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L152" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="L152" t="s" s="2">
+      <c r="M152" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21150,10 +21146,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21179,16 +21175,16 @@
         <v>176</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="N153" t="s" s="2">
+      <c r="O153" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>78</v>
@@ -21217,25 +21213,25 @@
       </c>
       <c r="Y153" s="2"/>
       <c r="Z153" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF153" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -21253,13 +21249,13 @@
         <v>78</v>
       </c>
       <c r="AL153" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AM153" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="AM153" t="s" s="2">
+      <c r="AN153" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>78</v>
@@ -21267,10 +21263,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21296,16 +21292,16 @@
         <v>104</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="N154" t="s" s="2">
+      <c r="O154" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>78</v>
@@ -21354,7 +21350,7 @@
         <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21372,10 +21368,10 @@
         <v>78</v>
       </c>
       <c r="AL154" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AM154" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>78</v>
@@ -21386,14 +21382,14 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -21415,13 +21411,13 @@
         <v>104</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="M155" t="s" s="2">
+      <c r="N155" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21471,7 +21467,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21489,13 +21485,13 @@
         <v>78</v>
       </c>
       <c r="AL155" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AM155" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="AM155" t="s" s="2">
+      <c r="AN155" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="AN155" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>78</v>
@@ -21503,14 +21499,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -21532,13 +21528,13 @@
         <v>104</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -21588,7 +21584,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21606,13 +21602,13 @@
         <v>78</v>
       </c>
       <c r="AL156" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AM156" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="AM156" t="s" s="2">
+      <c r="AN156" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="AN156" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>78</v>
@@ -21620,10 +21616,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21649,10 +21645,10 @@
         <v>104</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -21682,28 +21678,28 @@
         <v>158</v>
       </c>
       <c r="Y157" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="Z157" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="Z157" t="s" s="2">
+      <c r="AA157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF157" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AA157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF157" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21721,13 +21717,13 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AM157" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="AM157" t="s" s="2">
+      <c r="AN157" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="AN157" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>78</v>
@@ -21735,10 +21731,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21764,10 +21760,10 @@
         <v>104</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -21797,28 +21793,28 @@
         <v>158</v>
       </c>
       <c r="Y158" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="Z158" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="Z158" t="s" s="2">
+      <c r="AA158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF158" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21836,10 +21832,10 @@
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AM158" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="AM158" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>78</v>
@@ -21850,10 +21846,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21879,14 +21875,14 @@
         <v>253</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
@@ -21935,7 +21931,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21953,10 +21949,10 @@
         <v>78</v>
       </c>
       <c r="AL159" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AM159" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="AM159" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>474</v>
@@ -21967,10 +21963,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21993,19 +21989,19 @@
         <v>78</v>
       </c>
       <c r="K160" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="L160" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="L160" t="s" s="2">
+      <c r="M160" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="M160" t="s" s="2">
+      <c r="N160" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="N160" t="s" s="2">
+      <c r="O160" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>78</v>
@@ -22042,17 +22038,17 @@
         <v>78</v>
       </c>
       <c r="AB160" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AC160" s="2"/>
       <c r="AD160" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE160" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -22064,19 +22060,19 @@
         <v>209</v>
       </c>
       <c r="AJ160" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AK160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL160" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="AK160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL160" t="s" s="2">
+      <c r="AM160" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="AM160" t="s" s="2">
+      <c r="AN160" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>78</v>
@@ -22084,13 +22080,13 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C161" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="C161" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>78</v>
@@ -22112,19 +22108,19 @@
         <v>78</v>
       </c>
       <c r="K161" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="L161" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="L161" t="s" s="2">
-        <v>646</v>
-      </c>
       <c r="M161" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N161" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="N161" t="s" s="2">
+      <c r="O161" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>78</v>
@@ -22173,7 +22169,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -22185,19 +22181,19 @@
         <v>209</v>
       </c>
       <c r="AJ161" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AK161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL161" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="AK161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL161" t="s" s="2">
+      <c r="AM161" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="AM161" t="s" s="2">
+      <c r="AN161" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="AN161" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>78</v>
@@ -22205,10 +22201,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B162" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22320,10 +22316,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B163" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="B163" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22437,13 +22433,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="C164" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="C164" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>78</v>
@@ -22465,13 +22461,13 @@
         <v>78</v>
       </c>
       <c r="K164" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="L164" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="L164" t="s" s="2">
+      <c r="M164" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -22554,10 +22550,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B165" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22669,10 +22665,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B166" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="B166" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22784,10 +22780,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B167" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22827,7 +22823,7 @@
       </c>
       <c r="Q167" s="2"/>
       <c r="R167" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="S167" t="s" s="2">
         <v>78</v>
@@ -22901,10 +22897,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B168" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22945,7 +22941,7 @@
         <v>78</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>78</v>
@@ -22964,7 +22960,7 @@
       </c>
       <c r="Y168" s="2"/>
       <c r="Z168" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>78</v>
@@ -23014,13 +23010,13 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="C169" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="B169" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="C169" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>78</v>
@@ -23042,13 +23038,13 @@
         <v>78</v>
       </c>
       <c r="K169" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="L169" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="L169" t="s" s="2">
+      <c r="M169" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23131,10 +23127,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23246,10 +23242,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23363,10 +23359,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C172" t="s" s="2">
         <v>312</v>
@@ -23394,7 +23390,7 @@
         <v>111</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>202</v>
@@ -23480,10 +23476,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B173" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="B173" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23595,10 +23591,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="B174" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>679</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23710,10 +23706,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="B175" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23827,10 +23823,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="B176" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23890,7 +23886,7 @@
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>78</v>
@@ -23940,13 +23936,13 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C177" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C177" t="s" s="2">
-        <v>686</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>78</v>
@@ -23971,7 +23967,7 @@
         <v>111</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="M177" t="s" s="2">
         <v>202</v>
@@ -24057,10 +24053,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24172,10 +24168,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24287,10 +24283,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24330,7 +24326,7 @@
       </c>
       <c r="Q180" s="2"/>
       <c r="R180" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>78</v>
@@ -24404,10 +24400,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24519,13 +24515,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C182" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C182" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>78</v>
@@ -24636,10 +24632,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24751,10 +24747,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24866,10 +24862,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24909,7 +24905,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>78</v>
@@ -24983,10 +24979,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25098,13 +25094,13 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C187" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C187" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="D187" t="s" s="2">
         <v>78</v>
@@ -25129,7 +25125,7 @@
         <v>111</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M187" t="s" s="2">
         <v>202</v>
@@ -25215,10 +25211,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25330,10 +25326,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25445,10 +25441,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25488,7 +25484,7 @@
       </c>
       <c r="Q190" s="2"/>
       <c r="R190" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="S190" t="s" s="2">
         <v>78</v>
@@ -25562,10 +25558,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25677,13 +25673,13 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C192" t="s" s="2">
         <v>705</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C192" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="D192" t="s" s="2">
         <v>78</v>
@@ -25794,10 +25790,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25909,10 +25905,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26024,10 +26020,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26067,7 +26063,7 @@
       </c>
       <c r="Q195" s="2"/>
       <c r="R195" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="S195" t="s" s="2">
         <v>78</v>
@@ -26141,10 +26137,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26256,13 +26252,13 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C197" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C197" t="s" s="2">
-        <v>712</v>
       </c>
       <c r="D197" t="s" s="2">
         <v>78</v>
@@ -26287,7 +26283,7 @@
         <v>111</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="M197" t="s" s="2">
         <v>202</v>
@@ -26373,10 +26369,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26488,10 +26484,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26603,10 +26599,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26646,7 +26642,7 @@
       </c>
       <c r="Q200" s="2"/>
       <c r="R200" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="S200" t="s" s="2">
         <v>78</v>
@@ -26720,10 +26716,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26835,13 +26831,13 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C202" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C202" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>78</v>
@@ -26866,7 +26862,7 @@
         <v>111</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="M202" t="s" s="2">
         <v>202</v>
@@ -26952,10 +26948,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27067,10 +27063,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27182,10 +27178,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27225,7 +27221,7 @@
       </c>
       <c r="Q205" s="2"/>
       <c r="R205" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="S205" t="s" s="2">
         <v>78</v>
@@ -27299,10 +27295,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27414,10 +27410,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27457,7 +27453,7 @@
       </c>
       <c r="Q207" s="2"/>
       <c r="R207" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="S207" t="s" s="2">
         <v>78</v>
@@ -27531,10 +27527,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27646,10 +27642,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="B209" t="s" s="2">
         <v>728</v>
-      </c>
-      <c r="B209" t="s" s="2">
-        <v>729</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27675,10 +27671,10 @@
         <v>176</v>
       </c>
       <c r="L209" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M209" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="M209" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -27690,7 +27686,7 @@
         <v>78</v>
       </c>
       <c r="S209" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="T209" t="s" s="2">
         <v>78</v>
@@ -27708,37 +27704,37 @@
         <v>236</v>
       </c>
       <c r="Y209" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="Z209" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="Z209" t="s" s="2">
+      <c r="AA209" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB209" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC209" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD209" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE209" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF209" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="AA209" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB209" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC209" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD209" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE209" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF209" t="s" s="2">
+      <c r="AG209" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH209" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI209" t="s" s="2">
         <v>735</v>
-      </c>
-      <c r="AG209" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH209" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI209" t="s" s="2">
-        <v>736</v>
       </c>
       <c r="AJ209" t="s" s="2">
         <v>102</v>
@@ -27747,13 +27743,13 @@
         <v>78</v>
       </c>
       <c r="AL209" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="AM209" t="s" s="2">
         <v>737</v>
       </c>
-      <c r="AM209" t="s" s="2">
+      <c r="AN209" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="AN209" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>78</v>
@@ -27761,10 +27757,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="B210" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="B210" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27790,16 +27786,16 @@
         <v>104</v>
       </c>
       <c r="L210" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="M210" t="s" s="2">
         <v>742</v>
       </c>
-      <c r="M210" t="s" s="2">
+      <c r="N210" t="s" s="2">
         <v>743</v>
       </c>
-      <c r="N210" t="s" s="2">
+      <c r="O210" t="s" s="2">
         <v>744</v>
-      </c>
-      <c r="O210" t="s" s="2">
-        <v>745</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>78</v>
@@ -27848,7 +27844,7 @@
         <v>78</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>79</v>
@@ -27866,10 +27862,10 @@
         <v>78</v>
       </c>
       <c r="AL210" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="AM210" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="AM210" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="AN210" t="s" s="2">
         <v>467</v>
@@ -27880,10 +27876,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="B211" t="s" s="2">
         <v>749</v>
-      </c>
-      <c r="B211" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27909,16 +27905,16 @@
         <v>176</v>
       </c>
       <c r="L211" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="M211" t="s" s="2">
         <v>751</v>
       </c>
-      <c r="M211" t="s" s="2">
+      <c r="N211" t="s" s="2">
         <v>752</v>
       </c>
-      <c r="N211" t="s" s="2">
+      <c r="O211" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="O211" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>78</v>
@@ -27946,28 +27942,28 @@
         <v>236</v>
       </c>
       <c r="Y211" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="Z211" t="s" s="2">
         <v>755</v>
       </c>
-      <c r="Z211" t="s" s="2">
+      <c r="AA211" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB211" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC211" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD211" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE211" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF211" t="s" s="2">
         <v>756</v>
-      </c>
-      <c r="AA211" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB211" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC211" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD211" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE211" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF211" t="s" s="2">
-        <v>757</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>79</v>
@@ -27985,13 +27981,13 @@
         <v>78</v>
       </c>
       <c r="AL211" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="AM211" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AN211" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="AM211" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="AN211" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>78</v>
@@ -27999,10 +27995,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="B212" t="s" s="2">
         <v>760</v>
-      </c>
-      <c r="B212" t="s" s="2">
-        <v>761</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28025,16 +28021,16 @@
         <v>91</v>
       </c>
       <c r="K212" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="L212" t="s" s="2">
         <v>762</v>
       </c>
-      <c r="L212" t="s" s="2">
+      <c r="M212" t="s" s="2">
         <v>763</v>
       </c>
-      <c r="M212" t="s" s="2">
+      <c r="N212" t="s" s="2">
         <v>764</v>
-      </c>
-      <c r="N212" t="s" s="2">
-        <v>765</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
@@ -28084,7 +28080,7 @@
         <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
@@ -28116,10 +28112,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="B213" t="s" s="2">
         <v>767</v>
-      </c>
-      <c r="B213" t="s" s="2">
-        <v>768</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28145,10 +28141,10 @@
         <v>253</v>
       </c>
       <c r="L213" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="M213" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="M213" t="s" s="2">
-        <v>770</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -28199,7 +28195,7 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>79</v>
@@ -28220,7 +28216,7 @@
         <v>199</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AN213" t="s" s="2">
         <v>474</v>
@@ -28231,10 +28227,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28257,19 +28253,19 @@
         <v>78</v>
       </c>
       <c r="K214" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="L214" t="s" s="2">
         <v>773</v>
       </c>
-      <c r="L214" t="s" s="2">
+      <c r="M214" t="s" s="2">
         <v>774</v>
       </c>
-      <c r="M214" t="s" s="2">
+      <c r="N214" t="s" s="2">
         <v>775</v>
       </c>
-      <c r="N214" t="s" s="2">
+      <c r="O214" t="s" s="2">
         <v>776</v>
-      </c>
-      <c r="O214" t="s" s="2">
-        <v>777</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -28318,7 +28314,7 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
@@ -28336,13 +28332,13 @@
         <v>78</v>
       </c>
       <c r="AL214" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="AM214" t="s" s="2">
         <v>778</v>
       </c>
-      <c r="AM214" t="s" s="2">
+      <c r="AN214" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="AN214" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>78</v>
@@ -28350,10 +28346,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28379,14 +28375,14 @@
         <v>176</v>
       </c>
       <c r="L215" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="M215" t="s" s="2">
         <v>782</v>
-      </c>
-      <c r="M215" t="s" s="2">
-        <v>783</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>78</v>
@@ -28414,11 +28410,11 @@
         <v>236</v>
       </c>
       <c r="Y215" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="Z215" t="s" s="2">
         <v>785</v>
       </c>
-      <c r="Z215" t="s" s="2">
-        <v>786</v>
-      </c>
       <c r="AA215" t="s" s="2">
         <v>78</v>
       </c>
@@ -28435,7 +28431,7 @@
         <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -28453,13 +28449,13 @@
         <v>78</v>
       </c>
       <c r="AL215" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="AM215" t="s" s="2">
         <v>787</v>
       </c>
-      <c r="AM215" t="s" s="2">
+      <c r="AN215" t="s" s="2">
         <v>788</v>
-      </c>
-      <c r="AN215" t="s" s="2">
-        <v>789</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>78</v>
@@ -28467,10 +28463,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28493,17 +28489,17 @@
         <v>91</v>
       </c>
       <c r="K216" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="L216" t="s" s="2">
         <v>791</v>
       </c>
-      <c r="L216" t="s" s="2">
+      <c r="M216" t="s" s="2">
         <v>792</v>
-      </c>
-      <c r="M216" t="s" s="2">
-        <v>793</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>78</v>
@@ -28552,7 +28548,7 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28570,13 +28566,13 @@
         <v>78</v>
       </c>
       <c r="AL216" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="AM216" t="s" s="2">
         <v>795</v>
       </c>
-      <c r="AM216" t="s" s="2">
+      <c r="AN216" t="s" s="2">
         <v>796</v>
-      </c>
-      <c r="AN216" t="s" s="2">
-        <v>797</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>78</v>
@@ -28584,10 +28580,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28610,17 +28606,17 @@
         <v>78</v>
       </c>
       <c r="K217" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="L217" t="s" s="2">
         <v>799</v>
       </c>
-      <c r="L217" t="s" s="2">
+      <c r="M217" t="s" s="2">
         <v>800</v>
-      </c>
-      <c r="M217" t="s" s="2">
-        <v>801</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
@@ -28669,7 +28665,7 @@
         <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>
@@ -28690,10 +28686,10 @@
         <v>78</v>
       </c>
       <c r="AM217" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="AN217" t="s" s="2">
         <v>803</v>
-      </c>
-      <c r="AN217" t="s" s="2">
-        <v>804</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>78</v>
@@ -28701,10 +28697,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28727,13 +28723,13 @@
         <v>78</v>
       </c>
       <c r="K218" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="L218" t="s" s="2">
         <v>806</v>
       </c>
-      <c r="L218" t="s" s="2">
+      <c r="M218" t="s" s="2">
         <v>807</v>
-      </c>
-      <c r="M218" t="s" s="2">
-        <v>808</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -28772,7 +28768,7 @@
         <v>78</v>
       </c>
       <c r="AB218" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AC218" s="2"/>
       <c r="AD218" t="s" s="2">
@@ -28782,7 +28778,7 @@
         <v>117</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>79</v>
@@ -28800,13 +28796,13 @@
         <v>78</v>
       </c>
       <c r="AL218" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="AM218" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="AM218" t="s" s="2">
+      <c r="AN218" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="AN218" t="s" s="2">
-        <v>812</v>
       </c>
       <c r="AO218" t="s" s="2">
         <v>78</v>
@@ -28814,10 +28810,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -28929,10 +28925,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29046,14 +29042,14 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E221" s="2"/>
       <c r="F221" t="s" s="2">
@@ -29075,10 +29071,10 @@
         <v>111</v>
       </c>
       <c r="L221" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="M221" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="M221" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="N221" t="s" s="2">
         <v>114</v>
@@ -29133,7 +29129,7 @@
         <v>78</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>79</v>
@@ -29165,10 +29161,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29194,14 +29190,14 @@
         <v>362</v>
       </c>
       <c r="L222" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M222" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="M222" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>78</v>
@@ -29250,7 +29246,7 @@
         <v>78</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>79</v>
@@ -29271,7 +29267,7 @@
         <v>78</v>
       </c>
       <c r="AM222" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AN222" t="s" s="2">
         <v>78</v>
@@ -29282,10 +29278,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29311,10 +29307,10 @@
         <v>233</v>
       </c>
       <c r="L223" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="M223" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="M223" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -29345,7 +29341,7 @@
       </c>
       <c r="Y223" s="2"/>
       <c r="Z223" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>78</v>
@@ -29363,7 +29359,7 @@
         <v>78</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>90</v>
@@ -29384,10 +29380,10 @@
         <v>78</v>
       </c>
       <c r="AM223" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AO223" t="s" s="2">
         <v>78</v>
@@ -29395,10 +29391,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29424,14 +29420,14 @@
         <v>253</v>
       </c>
       <c r="L224" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="M224" t="s" s="2">
         <v>831</v>
-      </c>
-      <c r="M224" t="s" s="2">
-        <v>832</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>78</v>
@@ -29480,7 +29476,7 @@
         <v>78</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>79</v>
@@ -29501,10 +29497,10 @@
         <v>78</v>
       </c>
       <c r="AM224" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="AN224" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="AN224" t="s" s="2">
-        <v>835</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>78</v>
@@ -29512,10 +29508,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29541,10 +29537,10 @@
         <v>476</v>
       </c>
       <c r="L225" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="M225" t="s" s="2">
         <v>837</v>
-      </c>
-      <c r="M225" t="s" s="2">
-        <v>838</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -29595,7 +29591,7 @@
         <v>78</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>79</v>
@@ -29616,7 +29612,7 @@
         <v>78</v>
       </c>
       <c r="AM225" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="AN225" t="s" s="2">
         <v>78</v>
@@ -29627,13 +29623,13 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C226" t="s" s="2">
         <v>840</v>
-      </c>
-      <c r="B226" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C226" t="s" s="2">
-        <v>841</v>
       </c>
       <c r="D226" t="s" s="2">
         <v>78</v>
@@ -29655,13 +29651,13 @@
         <v>78</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -29712,7 +29708,7 @@
         <v>78</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>79</v>
@@ -29730,13 +29726,13 @@
         <v>78</v>
       </c>
       <c r="AL226" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="AM226" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="AM226" t="s" s="2">
+      <c r="AN226" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="AN226" t="s" s="2">
-        <v>812</v>
       </c>
       <c r="AO226" t="s" s="2">
         <v>78</v>
@@ -29744,10 +29740,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -29859,10 +29855,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -29972,13 +29968,13 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="C229" t="s" s="2">
         <v>845</v>
-      </c>
-      <c r="B229" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="C229" t="s" s="2">
-        <v>846</v>
       </c>
       <c r="D229" t="s" s="2">
         <v>78</v>
@@ -30000,13 +29996,13 @@
         <v>78</v>
       </c>
       <c r="K229" t="s" s="2">
+        <v>846</v>
+      </c>
+      <c r="L229" t="s" s="2">
         <v>847</v>
       </c>
-      <c r="L229" t="s" s="2">
+      <c r="M229" t="s" s="2">
         <v>848</v>
-      </c>
-      <c r="M229" t="s" s="2">
-        <v>849</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -30089,10 +30085,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="B230" t="s" s="2">
         <v>850</v>
-      </c>
-      <c r="B230" t="s" s="2">
-        <v>851</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30204,10 +30200,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="B231" t="s" s="2">
         <v>852</v>
-      </c>
-      <c r="B231" t="s" s="2">
-        <v>853</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30321,13 +30317,13 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="C232" t="s" s="2">
         <v>854</v>
-      </c>
-      <c r="B232" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="C232" t="s" s="2">
-        <v>855</v>
       </c>
       <c r="D232" t="s" s="2">
         <v>78</v>
@@ -30438,10 +30434,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="B233" t="s" s="2">
         <v>856</v>
-      </c>
-      <c r="B233" t="s" s="2">
-        <v>857</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30553,10 +30549,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="B234" t="s" s="2">
         <v>858</v>
-      </c>
-      <c r="B234" t="s" s="2">
-        <v>859</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30668,10 +30664,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="B235" t="s" s="2">
         <v>860</v>
-      </c>
-      <c r="B235" t="s" s="2">
-        <v>861</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30711,7 +30707,7 @@
       </c>
       <c r="Q235" s="2"/>
       <c r="R235" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="S235" t="s" s="2">
         <v>78</v>
@@ -30785,10 +30781,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="B236" t="s" s="2">
         <v>862</v>
-      </c>
-      <c r="B236" t="s" s="2">
-        <v>863</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -30848,7 +30844,7 @@
       </c>
       <c r="Y236" s="2"/>
       <c r="Z236" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="AA236" t="s" s="2">
         <v>78</v>
@@ -30898,13 +30894,13 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="C237" t="s" s="2">
         <v>865</v>
-      </c>
-      <c r="B237" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="C237" t="s" s="2">
-        <v>866</v>
       </c>
       <c r="D237" t="s" s="2">
         <v>78</v>
@@ -31015,10 +31011,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -31130,10 +31126,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31245,10 +31241,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31288,7 +31284,7 @@
       </c>
       <c r="Q240" s="2"/>
       <c r="R240" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="S240" t="s" s="2">
         <v>78</v>
@@ -31362,10 +31358,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31425,7 +31421,7 @@
       </c>
       <c r="Y241" s="2"/>
       <c r="Z241" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AA241" t="s" s="2">
         <v>78</v>
@@ -31475,13 +31471,13 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="B242" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="C242" t="s" s="2">
         <v>872</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="C242" t="s" s="2">
-        <v>873</v>
       </c>
       <c r="D242" t="s" s="2">
         <v>78</v>
@@ -31592,10 +31588,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31707,10 +31703,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31822,10 +31818,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -31865,7 +31861,7 @@
       </c>
       <c r="Q245" s="2"/>
       <c r="R245" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="S245" t="s" s="2">
         <v>78</v>
@@ -31939,10 +31935,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -32002,7 +31998,7 @@
       </c>
       <c r="Y246" s="2"/>
       <c r="Z246" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>78</v>
@@ -32052,10 +32048,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="B247" t="s" s="2">
         <v>879</v>
-      </c>
-      <c r="B247" t="s" s="2">
-        <v>880</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32095,7 +32091,7 @@
       </c>
       <c r="Q247" s="2"/>
       <c r="R247" t="s" s="2">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="S247" t="s" s="2">
         <v>78</v>
@@ -32169,10 +32165,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="B248" t="s" s="2">
         <v>882</v>
-      </c>
-      <c r="B248" t="s" s="2">
-        <v>883</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32284,14 +32280,14 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E249" s="2"/>
       <c r="F249" t="s" s="2">
@@ -32313,10 +32309,10 @@
         <v>111</v>
       </c>
       <c r="L249" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="M249" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="M249" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="N249" t="s" s="2">
         <v>114</v>
@@ -32371,7 +32367,7 @@
         <v>78</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>79</v>
@@ -32403,10 +32399,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32432,14 +32428,14 @@
         <v>362</v>
       </c>
       <c r="L250" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M250" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="M250" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="P250" t="s" s="2">
         <v>78</v>
@@ -32488,7 +32484,7 @@
         <v>78</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>79</v>
@@ -32509,7 +32505,7 @@
         <v>78</v>
       </c>
       <c r="AM250" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AN250" t="s" s="2">
         <v>78</v>
@@ -32520,10 +32516,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32549,10 +32545,10 @@
         <v>233</v>
       </c>
       <c r="L251" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="M251" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="M251" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="N251" s="2"/>
       <c r="O251" s="2"/>
@@ -32583,7 +32579,7 @@
       </c>
       <c r="Y251" s="2"/>
       <c r="Z251" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AA251" t="s" s="2">
         <v>78</v>
@@ -32601,7 +32597,7 @@
         <v>78</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>90</v>
@@ -32622,10 +32618,10 @@
         <v>78</v>
       </c>
       <c r="AM251" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AN251" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AO251" t="s" s="2">
         <v>78</v>
@@ -32633,10 +32629,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="B252" t="s" s="2">
         <v>887</v>
-      </c>
-      <c r="B252" t="s" s="2">
-        <v>888</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32748,10 +32744,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="B253" t="s" s="2">
         <v>889</v>
-      </c>
-      <c r="B253" t="s" s="2">
-        <v>890</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -32865,10 +32861,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="B254" t="s" s="2">
         <v>891</v>
-      </c>
-      <c r="B254" t="s" s="2">
-        <v>892</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -32940,14 +32936,14 @@
         <v>78</v>
       </c>
       <c r="AB254" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="AC254" s="2"/>
       <c r="AD254" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE254" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AF254" t="s" s="2">
         <v>398</v>
@@ -32982,13 +32978,13 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="C255" t="s" s="2">
         <v>894</v>
-      </c>
-      <c r="B255" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="C255" t="s" s="2">
-        <v>895</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>78</v>
@@ -33051,7 +33047,7 @@
       </c>
       <c r="Y255" s="2"/>
       <c r="Z255" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="AA255" t="s" s="2">
         <v>78</v>
@@ -33101,13 +33097,13 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D256" t="s" s="2">
         <v>78</v>
@@ -33170,7 +33166,7 @@
       </c>
       <c r="Y256" s="2"/>
       <c r="Z256" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AA256" t="s" s="2">
         <v>78</v>
@@ -33220,10 +33216,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="B257" t="s" s="2">
         <v>898</v>
-      </c>
-      <c r="B257" t="s" s="2">
-        <v>899</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -33339,10 +33335,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33368,14 +33364,14 @@
         <v>253</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>78</v>
@@ -33424,7 +33420,7 @@
         <v>78</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>79</v>
@@ -33445,10 +33441,10 @@
         <v>78</v>
       </c>
       <c r="AM258" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="AN258" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="AN258" t="s" s="2">
-        <v>835</v>
       </c>
       <c r="AO258" t="s" s="2">
         <v>78</v>
@@ -33456,10 +33452,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
+        <v>901</v>
+      </c>
+      <c r="B259" t="s" s="2">
         <v>902</v>
-      </c>
-      <c r="B259" t="s" s="2">
-        <v>903</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33571,10 +33567,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
+        <v>903</v>
+      </c>
+      <c r="B260" t="s" s="2">
         <v>904</v>
-      </c>
-      <c r="B260" t="s" s="2">
-        <v>905</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33688,10 +33684,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="B261" t="s" s="2">
         <v>906</v>
-      </c>
-      <c r="B261" t="s" s="2">
-        <v>907</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33717,7 +33713,7 @@
         <v>260</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="M261" t="s" s="2">
         <v>262</v>
@@ -33805,10 +33801,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="B262" t="s" s="2">
         <v>909</v>
-      </c>
-      <c r="B262" t="s" s="2">
-        <v>910</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33834,7 +33830,7 @@
         <v>260</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="M262" t="s" s="2">
         <v>271</v>
@@ -33924,10 +33920,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -33950,13 +33946,13 @@
         <v>78</v>
       </c>
       <c r="K263" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="L263" t="s" s="2">
         <v>913</v>
       </c>
-      <c r="L263" t="s" s="2">
-        <v>914</v>
-      </c>
       <c r="M263" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="N263" s="2"/>
       <c r="O263" s="2"/>
@@ -34007,7 +34003,7 @@
         <v>78</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>79</v>
@@ -34028,7 +34024,7 @@
         <v>78</v>
       </c>
       <c r="AM263" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="AN263" t="s" s="2">
         <v>78</v>
@@ -34039,13 +34035,13 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
+        <v>914</v>
+      </c>
+      <c r="B264" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C264" t="s" s="2">
         <v>915</v>
-      </c>
-      <c r="B264" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C264" t="s" s="2">
-        <v>916</v>
       </c>
       <c r="D264" t="s" s="2">
         <v>78</v>
@@ -34067,13 +34063,13 @@
         <v>78</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="N264" s="2"/>
       <c r="O264" s="2"/>
@@ -34124,7 +34120,7 @@
         <v>78</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>79</v>
@@ -34142,13 +34138,13 @@
         <v>78</v>
       </c>
       <c r="AL264" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="AM264" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="AM264" t="s" s="2">
+      <c r="AN264" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="AN264" t="s" s="2">
-        <v>812</v>
       </c>
       <c r="AO264" t="s" s="2">
         <v>78</v>
@@ -34156,10 +34152,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -34271,10 +34267,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34388,14 +34384,14 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E267" s="2"/>
       <c r="F267" t="s" s="2">
@@ -34417,10 +34413,10 @@
         <v>111</v>
       </c>
       <c r="L267" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="M267" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="M267" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="N267" t="s" s="2">
         <v>114</v>
@@ -34475,7 +34471,7 @@
         <v>78</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>79</v>
@@ -34507,10 +34503,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34536,14 +34532,14 @@
         <v>362</v>
       </c>
       <c r="L268" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M268" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="M268" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="N268" s="2"/>
       <c r="O268" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="P268" t="s" s="2">
         <v>78</v>
@@ -34592,7 +34588,7 @@
         <v>78</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>79</v>
@@ -34613,7 +34609,7 @@
         <v>78</v>
       </c>
       <c r="AM268" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AN268" t="s" s="2">
         <v>78</v>
@@ -34624,10 +34620,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -34653,10 +34649,10 @@
         <v>233</v>
       </c>
       <c r="L269" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="M269" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="M269" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="N269" s="2"/>
       <c r="O269" s="2"/>
@@ -34687,7 +34683,7 @@
       </c>
       <c r="Y269" s="2"/>
       <c r="Z269" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AA269" t="s" s="2">
         <v>78</v>
@@ -34705,7 +34701,7 @@
         <v>78</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>90</v>
@@ -34726,10 +34722,10 @@
         <v>78</v>
       </c>
       <c r="AM269" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AN269" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AO269" t="s" s="2">
         <v>78</v>
@@ -34737,10 +34733,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -34852,10 +34848,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -34969,10 +34965,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -35044,14 +35040,14 @@
         <v>78</v>
       </c>
       <c r="AB272" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="AC272" s="2"/>
       <c r="AD272" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE272" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AF272" t="s" s="2">
         <v>398</v>
@@ -35086,13 +35082,13 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
+        <v>925</v>
+      </c>
+      <c r="B273" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="C273" t="s" s="2">
         <v>926</v>
-      </c>
-      <c r="B273" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="C273" t="s" s="2">
-        <v>927</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>78</v>
@@ -35117,7 +35113,7 @@
         <v>154</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="M273" t="s" s="2">
         <v>395</v>
@@ -35155,7 +35151,7 @@
       </c>
       <c r="Y273" s="2"/>
       <c r="Z273" t="s" s="2">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="AA273" t="s" s="2">
         <v>78</v>
@@ -35205,10 +35201,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C274" t="s" s="2">
         <v>337</v>
@@ -35236,7 +35232,7 @@
         <v>154</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="M274" t="s" s="2">
         <v>395</v>
@@ -35324,10 +35320,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -35443,10 +35439,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -35472,14 +35468,14 @@
         <v>253</v>
       </c>
       <c r="L276" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="M276" t="s" s="2">
         <v>831</v>
-      </c>
-      <c r="M276" t="s" s="2">
-        <v>832</v>
       </c>
       <c r="N276" s="2"/>
       <c r="O276" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="P276" t="s" s="2">
         <v>78</v>
@@ -35528,7 +35524,7 @@
         <v>78</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>79</v>
@@ -35549,10 +35545,10 @@
         <v>78</v>
       </c>
       <c r="AM276" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="AN276" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="AN276" t="s" s="2">
-        <v>835</v>
       </c>
       <c r="AO276" t="s" s="2">
         <v>78</v>
@@ -35560,10 +35556,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -35675,10 +35671,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35792,10 +35788,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35821,7 +35817,7 @@
         <v>260</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="M279" t="s" s="2">
         <v>262</v>
@@ -35909,10 +35905,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -35938,7 +35934,7 @@
         <v>260</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="M280" t="s" s="2">
         <v>271</v>
@@ -36028,10 +36024,10 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -36057,10 +36053,10 @@
         <v>476</v>
       </c>
       <c r="L281" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="M281" t="s" s="2">
         <v>837</v>
-      </c>
-      <c r="M281" t="s" s="2">
-        <v>838</v>
       </c>
       <c r="N281" s="2"/>
       <c r="O281" s="2"/>
@@ -36111,7 +36107,7 @@
         <v>78</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>79</v>
@@ -36132,7 +36128,7 @@
         <v>78</v>
       </c>
       <c r="AM281" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="AN281" t="s" s="2">
         <v>78</v>
@@ -36143,13 +36139,13 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
+        <v>940</v>
+      </c>
+      <c r="B282" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C282" t="s" s="2">
         <v>941</v>
-      </c>
-      <c r="B282" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C282" t="s" s="2">
-        <v>942</v>
       </c>
       <c r="D282" t="s" s="2">
         <v>78</v>
@@ -36171,13 +36167,13 @@
         <v>78</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="N282" s="2"/>
       <c r="O282" s="2"/>
@@ -36228,7 +36224,7 @@
         <v>78</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>79</v>
@@ -36246,13 +36242,13 @@
         <v>78</v>
       </c>
       <c r="AL282" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="AM282" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="AM282" t="s" s="2">
+      <c r="AN282" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="AN282" t="s" s="2">
-        <v>812</v>
       </c>
       <c r="AO282" t="s" s="2">
         <v>78</v>
@@ -36260,10 +36256,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -36375,10 +36371,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -36492,14 +36488,14 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E285" s="2"/>
       <c r="F285" t="s" s="2">
@@ -36521,10 +36517,10 @@
         <v>111</v>
       </c>
       <c r="L285" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="M285" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="M285" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="N285" t="s" s="2">
         <v>114</v>
@@ -36579,7 +36575,7 @@
         <v>78</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AG285" t="s" s="2">
         <v>79</v>
@@ -36611,10 +36607,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -36640,14 +36636,14 @@
         <v>362</v>
       </c>
       <c r="L286" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M286" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="M286" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="N286" s="2"/>
       <c r="O286" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="P286" t="s" s="2">
         <v>78</v>
@@ -36696,7 +36692,7 @@
         <v>78</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>79</v>
@@ -36717,7 +36713,7 @@
         <v>78</v>
       </c>
       <c r="AM286" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AN286" t="s" s="2">
         <v>78</v>
@@ -36728,10 +36724,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -36757,10 +36753,10 @@
         <v>233</v>
       </c>
       <c r="L287" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="M287" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="M287" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="N287" s="2"/>
       <c r="O287" s="2"/>
@@ -36791,7 +36787,7 @@
       </c>
       <c r="Y287" s="2"/>
       <c r="Z287" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AA287" t="s" s="2">
         <v>78</v>
@@ -36809,7 +36805,7 @@
         <v>78</v>
       </c>
       <c r="AF287" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>90</v>
@@ -36824,16 +36820,16 @@
         <v>102</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM287" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AN287" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AO287" t="s" s="2">
         <v>78</v>
@@ -36841,10 +36837,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -36956,10 +36952,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -37073,10 +37069,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -37148,7 +37144,7 @@
         <v>78</v>
       </c>
       <c r="AB290" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="AC290" s="2"/>
       <c r="AD290" t="s" s="2">
@@ -37190,13 +37186,13 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D291" t="s" s="2">
         <v>78</v>
@@ -37221,7 +37217,7 @@
         <v>154</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="M291" t="s" s="2">
         <v>395</v>
@@ -37259,7 +37255,7 @@
       </c>
       <c r="Y291" s="2"/>
       <c r="Z291" t="s" s="2">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AA291" t="s" s="2">
         <v>78</v>
@@ -37309,13 +37305,13 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D292" t="s" s="2">
         <v>78</v>
@@ -37340,7 +37336,7 @@
         <v>154</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="M292" t="s" s="2">
         <v>395</v>
@@ -37378,7 +37374,7 @@
       </c>
       <c r="Y292" s="2"/>
       <c r="Z292" t="s" s="2">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="AA292" t="s" s="2">
         <v>78</v>
@@ -37428,10 +37424,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -37547,10 +37543,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -37576,14 +37572,14 @@
         <v>253</v>
       </c>
       <c r="L294" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="M294" t="s" s="2">
         <v>831</v>
-      </c>
-      <c r="M294" t="s" s="2">
-        <v>832</v>
       </c>
       <c r="N294" s="2"/>
       <c r="O294" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="P294" t="s" s="2">
         <v>78</v>
@@ -37632,7 +37628,7 @@
         <v>78</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>79</v>
@@ -37653,10 +37649,10 @@
         <v>78</v>
       </c>
       <c r="AM294" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="AN294" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="AN294" t="s" s="2">
-        <v>835</v>
       </c>
       <c r="AO294" t="s" s="2">
         <v>78</v>
@@ -37664,10 +37660,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -37779,10 +37775,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -37896,10 +37892,10 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -37925,7 +37921,7 @@
         <v>260</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="M297" t="s" s="2">
         <v>262</v>
@@ -37996,7 +37992,7 @@
         <v>102</v>
       </c>
       <c r="AK297" t="s" s="2">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="AL297" t="s" s="2">
         <v>266</v>
@@ -38013,10 +38009,10 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -38042,7 +38038,7 @@
         <v>260</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="M298" t="s" s="2">
         <v>271</v>
@@ -38115,7 +38111,7 @@
         <v>102</v>
       </c>
       <c r="AK298" t="s" s="2">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="AL298" t="s" s="2">
         <v>275</v>
@@ -38132,10 +38128,10 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -38161,10 +38157,10 @@
         <v>476</v>
       </c>
       <c r="L299" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="M299" t="s" s="2">
         <v>837</v>
-      </c>
-      <c r="M299" t="s" s="2">
-        <v>838</v>
       </c>
       <c r="N299" s="2"/>
       <c r="O299" s="2"/>
@@ -38215,7 +38211,7 @@
         <v>78</v>
       </c>
       <c r="AF299" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AG299" t="s" s="2">
         <v>79</v>
@@ -38236,7 +38232,7 @@
         <v>78</v>
       </c>
       <c r="AM299" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="AN299" t="s" s="2">
         <v>78</v>
@@ -38247,10 +38243,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -38273,19 +38269,19 @@
         <v>78</v>
       </c>
       <c r="K300" t="s" s="2">
+        <v>970</v>
+      </c>
+      <c r="L300" t="s" s="2">
         <v>971</v>
       </c>
-      <c r="L300" t="s" s="2">
+      <c r="M300" t="s" s="2">
         <v>972</v>
       </c>
-      <c r="M300" t="s" s="2">
+      <c r="N300" t="s" s="2">
         <v>973</v>
       </c>
-      <c r="N300" t="s" s="2">
+      <c r="O300" t="s" s="2">
         <v>974</v>
-      </c>
-      <c r="O300" t="s" s="2">
-        <v>975</v>
       </c>
       <c r="P300" t="s" s="2">
         <v>78</v>
@@ -38314,7 +38310,7 @@
       </c>
       <c r="Y300" s="2"/>
       <c r="Z300" t="s" s="2">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="AA300" t="s" s="2">
         <v>78</v>
@@ -38332,7 +38328,7 @@
         <v>78</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>79</v>
@@ -38350,10 +38346,10 @@
         <v>78</v>
       </c>
       <c r="AL300" t="s" s="2">
+        <v>976</v>
+      </c>
+      <c r="AM300" t="s" s="2">
         <v>977</v>
-      </c>
-      <c r="AM300" t="s" s="2">
-        <v>978</v>
       </c>
       <c r="AN300" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="979">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -686,7 +686,7 @@
     <t>InscriptionOrdre : Eléments permettant de retrouver les informations d'inscription à un ordre par rapport à la profession de la personne physique sur une période et un département donné.</t>
   </si>
   <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la première inscription si "isFirst = true".</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la première inscription si "isFirst = true". Ces données sont uniquement accessibles en accès restreint.</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-registration.id</t>
@@ -2538,7 +2538,7 @@
     <t>The official certifications, training, and licenses that authorize or otherwise pertain to the provision of care by the practitioner.  For example, a medical license issued by a medical board authorizing the practitioner to practice medicine within a certian locality.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:code}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -2794,108 +2794,108 @@
     <t>Practitioner.qualification.code.coding</t>
   </si>
   <si>
+    <t>Practitioner.qualification:degree.code.coding:degreeType</t>
+  </si>
+  <si>
+    <t>degreeType</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.coding:degree</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period</t>
+  </si>
+  <si>
+    <t>[Donnée restreinte] : Période durant laquelle le niveau de formation est actif.</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.start</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.start</t>
+  </si>
+  <si>
+    <t>dateDebut : Date d’obtention du diplôme (dateDiplome)
+cette date est renseignée par l’ordre à la clôture de l’exercice professionnel.</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.end</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.end</t>
+  </si>
+  <si>
+    <t>dateFin : Date à laquelle le niveau de formation n’est plus actif (non visible hormis dans les données historisées).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.issuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+</t>
+  </si>
+  <si>
+    <t>[Donnée restreinte] : Lieu de formation pour l'obtention du diplôme (lieuFormation).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro : exercice professionnel décrivant la profession exercée, l'identité d'exercice d'un professionnel et le cadre de son exercice (civil, militaire, etc.).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
-    <t>Practitioner.qualification:degree.code.coding:degreeType</t>
-  </si>
-  <si>
-    <t>degreeType</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.code.coding:degree</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period</t>
-  </si>
-  <si>
-    <t>[Donnée restreinte] : Période durant laquelle le niveau de formation est actif.</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.start</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.start</t>
-  </si>
-  <si>
-    <t>dateDebut : Date d’obtention du diplôme (dateDiplome)
-cette date est renseignée par l’ordre à la clôture de l’exercice professionnel.</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.end</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.end</t>
-  </si>
-  <si>
-    <t>dateFin : Date à laquelle le niveau de formation n’est plus actif (non visible hormis dans les données historisées).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.issuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
-</t>
-  </si>
-  <si>
-    <t>[Donnée restreinte] : Lieu de formation pour l'obtention du diplôme (lieuFormation).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro</t>
-  </si>
-  <si>
-    <t>exercicePro</t>
-  </si>
-  <si>
-    <t>exercicePro : exercice professionnel décrivant la profession exercée, l'identité d'exercice d'un professionnel et le cadre de son exercice (civil, militaire, etc.).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code.coding</t>
-  </si>
-  <si>
     <t>Practitioner.qualification:exercicePro.code.coding:categorieProfession</t>
   </si>
   <si>
@@ -2947,7 +2947,7 @@
     <t>savoirFaire</t>
   </si>
   <si>
-    <t>savoirFAire : Prérogatives d'exercice d'un professionnel reconnues par une autorité d'enregistrement sur une période donnée de son exercice professionnel, par exemple les spécialités ordinales, etc.</t>
+    <t>savoirFaire : Prérogatives d'exercice d'un professionnel reconnues par une autorité d'enregistrement sur une période donnée de son exercice professionnel, par exemple les spécialités ordinales, etc.</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.id</t>
@@ -2965,19 +2965,22 @@
     <t>Practitioner.qualification:savoirFaire.code</t>
   </si>
   <si>
+    <t>SavoirFaire.typeSavoirFaire</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.coding:typeSavoirFaire</t>
+  </si>
+  <si>
     <t>typeSavoirFaire</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.coding:typeSavoirFaire</t>
   </si>
   <si>
     <t>Le type de savoir-faire (qualifications/autres attributions).
@@ -3014,7 +3017,7 @@
     <t>Starting time with inclusive boundary</t>
   </si>
   <si>
-    <t>dateReconnaissance</t>
+    <t>SavoirFaire.dateReconnaissance</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.period.end</t>
@@ -3023,7 +3026,7 @@
     <t>End time with inclusive boundary, if not ongoing</t>
   </si>
   <si>
-    <t>dateAbandon</t>
+    <t>SavoirFaire.dateAbandon</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.issuer</t>
@@ -32936,7 +32939,7 @@
         <v>78</v>
       </c>
       <c r="AB254" t="s" s="2">
-        <v>892</v>
+        <v>808</v>
       </c>
       <c r="AC254" s="2"/>
       <c r="AD254" t="s" s="2">
@@ -32978,13 +32981,13 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>891</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>78</v>
@@ -33047,7 +33050,7 @@
       </c>
       <c r="Y255" s="2"/>
       <c r="Z255" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="AA255" t="s" s="2">
         <v>78</v>
@@ -33097,7 +33100,7 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>891</v>
@@ -33216,10 +33219,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
+        <v>896</v>
+      </c>
+      <c r="B257" t="s" s="2">
         <v>897</v>
-      </c>
-      <c r="B257" t="s" s="2">
-        <v>898</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -33335,7 +33338,7 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>829</v>
@@ -33364,7 +33367,7 @@
         <v>253</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M258" t="s" s="2">
         <v>831</v>
@@ -33452,10 +33455,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
+        <v>900</v>
+      </c>
+      <c r="B259" t="s" s="2">
         <v>901</v>
-      </c>
-      <c r="B259" t="s" s="2">
-        <v>902</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33567,10 +33570,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
+        <v>902</v>
+      </c>
+      <c r="B260" t="s" s="2">
         <v>903</v>
-      </c>
-      <c r="B260" t="s" s="2">
-        <v>904</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33684,10 +33687,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
+        <v>904</v>
+      </c>
+      <c r="B261" t="s" s="2">
         <v>905</v>
-      </c>
-      <c r="B261" t="s" s="2">
-        <v>906</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33713,7 +33716,7 @@
         <v>260</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="M261" t="s" s="2">
         <v>262</v>
@@ -33801,10 +33804,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="B262" t="s" s="2">
         <v>908</v>
-      </c>
-      <c r="B262" t="s" s="2">
-        <v>909</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33830,7 +33833,7 @@
         <v>260</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="M262" t="s" s="2">
         <v>271</v>
@@ -33920,7 +33923,7 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>835</v>
@@ -33946,10 +33949,10 @@
         <v>78</v>
       </c>
       <c r="K263" t="s" s="2">
+        <v>911</v>
+      </c>
+      <c r="L263" t="s" s="2">
         <v>912</v>
-      </c>
-      <c r="L263" t="s" s="2">
-        <v>913</v>
       </c>
       <c r="M263" t="s" s="2">
         <v>837</v>
@@ -34035,13 +34038,13 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>804</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D264" t="s" s="2">
         <v>78</v>
@@ -34066,7 +34069,7 @@
         <v>805</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M264" t="s" s="2">
         <v>807</v>
@@ -34152,7 +34155,7 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>812</v>
@@ -34267,7 +34270,7 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>813</v>
@@ -34384,7 +34387,7 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>814</v>
@@ -34503,7 +34506,7 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>819</v>
@@ -34620,7 +34623,7 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>824</v>
@@ -34733,7 +34736,7 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>887</v>
@@ -34848,7 +34851,7 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>889</v>
@@ -34965,7 +34968,7 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>891</v>
@@ -35040,7 +35043,7 @@
         <v>78</v>
       </c>
       <c r="AB272" t="s" s="2">
-        <v>892</v>
+        <v>924</v>
       </c>
       <c r="AC272" s="2"/>
       <c r="AD272" t="s" s="2">
@@ -35323,7 +35326,7 @@
         <v>931</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -35559,7 +35562,7 @@
         <v>933</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -35674,7 +35677,7 @@
         <v>934</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35791,7 +35794,7 @@
         <v>935</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35908,7 +35911,7 @@
         <v>937</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -37144,7 +37147,7 @@
         <v>78</v>
       </c>
       <c r="AB290" t="s" s="2">
-        <v>892</v>
+        <v>924</v>
       </c>
       <c r="AC290" s="2"/>
       <c r="AD290" t="s" s="2">
@@ -37192,7 +37195,7 @@
         <v>891</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="D291" t="s" s="2">
         <v>78</v>
@@ -37217,7 +37220,7 @@
         <v>154</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="M291" t="s" s="2">
         <v>395</v>
@@ -37255,7 +37258,7 @@
       </c>
       <c r="Y291" s="2"/>
       <c r="Z291" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AA291" t="s" s="2">
         <v>78</v>
@@ -37305,7 +37308,7 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>891</v>
@@ -37336,7 +37339,7 @@
         <v>154</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="M292" t="s" s="2">
         <v>395</v>
@@ -37374,7 +37377,7 @@
       </c>
       <c r="Y292" s="2"/>
       <c r="Z292" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="AA292" t="s" s="2">
         <v>78</v>
@@ -37424,10 +37427,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -37543,7 +37546,7 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>829</v>
@@ -37660,10 +37663,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -37775,10 +37778,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -37892,10 +37895,10 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -37921,7 +37924,7 @@
         <v>260</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M297" t="s" s="2">
         <v>262</v>
@@ -37992,7 +37995,7 @@
         <v>102</v>
       </c>
       <c r="AK297" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AL297" t="s" s="2">
         <v>266</v>
@@ -38009,10 +38012,10 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -38038,7 +38041,7 @@
         <v>260</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="M298" t="s" s="2">
         <v>271</v>
@@ -38111,7 +38114,7 @@
         <v>102</v>
       </c>
       <c r="AK298" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="AL298" t="s" s="2">
         <v>275</v>
@@ -38128,7 +38131,7 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>835</v>
@@ -38243,10 +38246,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -38269,19 +38272,19 @@
         <v>78</v>
       </c>
       <c r="K300" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="L300" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="M300" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="N300" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="O300" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="P300" t="s" s="2">
         <v>78</v>
@@ -38310,7 +38313,7 @@
       </c>
       <c r="Y300" s="2"/>
       <c r="Z300" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="AA300" t="s" s="2">
         <v>78</v>
@@ -38328,7 +38331,7 @@
         <v>78</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>79</v>
@@ -38346,10 +38349,10 @@
         <v>78</v>
       </c>
       <c r="AL300" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="AM300" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="AN300" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0-snapshot</t>
+    <t>1.1.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:20:03+00:00</t>
+    <t>2024-07-11T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -25610,7 +25610,7 @@
         <v>85</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>84</v>
@@ -26559,7 +26559,7 @@
         <v>85</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>84</v>
@@ -26692,7 +26692,7 @@
         <v>85</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>84</v>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G150" t="s" s="2">
         <v>102</v>
@@ -24928,7 +24928,7 @@
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G159" t="s" s="2">
         <v>102</v>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2351,10 +2351,7 @@
   </si>
   <si>
     <t>typeBAL : Type de boîte aux lettres.
-Valeurs possibles :
-ORG pour une BAL organisationnelle;
-APP pour une BAL applicative;
-PER pour une BAL personnelle, rattachée à une personne physique</t>
+Valeurs possibles : ORG | APP | PER | CAB</t>
   </si>
   <si>
     <t>Practitioner.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.id</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -15637,7 +15637,7 @@
         <v>85</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>103</v>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -27569,7 +27569,7 @@
         <v>85</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>84</v>
@@ -33328,7 +33328,7 @@
         <v>85</v>
       </c>
       <c r="G222" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="H222" t="s" s="2">
         <v>84</v>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AU$290</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AU$295</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12416" uniqueCount="976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12627" uniqueCount="981">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2658,6 +2658,30 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J88-AnneeUniversitaire-RASS/FHIR/JDV-J88-AnneeUniversitaire-RASS|20251016120000</t>
   </si>
   <si>
+    <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:trainingLocation</t>
+  </si>
+  <si>
+    <t>trainingLocation</t>
+  </si>
+  <si>
+    <t>Diplome.lieuFormation</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:trainingLocation.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:trainingLocation.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:trainingLocation.url</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:trainingLocation.value[x]</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J235-LieuFormation-EPARS/FHIR/JDV-J235-LieuFormation-EPARS|20240726120000</t>
+  </si>
+  <si>
     <t>Practitioner.qualification:degree.extension:as-ext-education-level.url</t>
   </si>
   <si>
@@ -2807,16 +2831,6 @@
   </si>
   <si>
     <t>Practitioner.qualification:degree.issuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
-</t>
-  </si>
-  <si>
-    <t>[Donnée restreinte] : Lieu de formation pour l'obtention du diplôme (lieuFormation).</t>
-  </si>
-  <si>
-    <t>Diplome.lieuFormation</t>
   </si>
   <si>
     <t>Practitioner.qualification:exercicePro</t>
@@ -3351,7 +3365,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AU290"/>
+  <dimension ref="A1:AU295"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="82.7265625" customWidth="true" bestFit="true"/>
@@ -35080,26 +35094,28 @@
         <v>84</v>
       </c>
     </row>
-    <row r="237" hidden="true">
+    <row r="237">
       <c r="A237" t="s" s="2">
         <v>851</v>
       </c>
       <c r="B237" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="C237" t="s" s="2">
         <v>852</v>
       </c>
-      <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E237" s="2"/>
       <c r="F237" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G237" t="s" s="2">
         <v>102</v>
       </c>
       <c r="H237" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I237" t="s" s="2">
         <v>84</v>
@@ -35108,91 +35124,89 @@
         <v>84</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N237" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N237" s="2"/>
       <c r="O237" s="2"/>
       <c r="P237" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q237" s="2"/>
       <c r="R237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF237" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AG237" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH237" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ237" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AK237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM237" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN237" t="s" s="2">
         <v>853</v>
       </c>
-      <c r="S237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF237" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AG237" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AH237" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM237" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN237" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AO237" t="s" s="2">
         <v>84</v>
       </c>
@@ -35206,7 +35220,7 @@
         <v>84</v>
       </c>
       <c r="AS237" t="s" s="2">
-        <v>216</v>
+        <v>84</v>
       </c>
       <c r="AT237" t="s" s="2">
         <v>84</v>
@@ -35220,7 +35234,7 @@
         <v>854</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>855</v>
+        <v>827</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -35231,7 +35245,7 @@
         <v>85</v>
       </c>
       <c r="G238" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="H238" t="s" s="2">
         <v>84</v>
@@ -35243,13 +35257,13 @@
         <v>84</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>325</v>
+        <v>116</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>252</v>
+        <v>117</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
@@ -35300,7 +35314,7 @@
         <v>84</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>256</v>
+        <v>119</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>85</v>
@@ -35312,7 +35326,7 @@
         <v>84</v>
       </c>
       <c r="AJ238" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK238" t="s" s="2">
         <v>84</v>
@@ -35339,7 +35353,7 @@
         <v>84</v>
       </c>
       <c r="AS238" t="s" s="2">
-        <v>216</v>
+        <v>120</v>
       </c>
       <c r="AT238" t="s" s="2">
         <v>84</v>
@@ -35350,46 +35364,42 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>781</v>
+        <v>829</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
-        <v>782</v>
+        <v>84</v>
       </c>
       <c r="E239" s="2"/>
       <c r="F239" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G239" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H239" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I239" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="J239" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K239" t="s" s="2">
         <v>123</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>783</v>
+        <v>218</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="N239" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O239" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N239" s="2"/>
+      <c r="O239" s="2"/>
       <c r="P239" t="s" s="2">
         <v>84</v>
       </c>
@@ -35425,19 +35435,19 @@
         <v>84</v>
       </c>
       <c r="AB239" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC239" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD239" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE239" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>785</v>
+        <v>130</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>85</v>
@@ -35476,7 +35486,7 @@
         <v>84</v>
       </c>
       <c r="AS239" t="s" s="2">
-        <v>216</v>
+        <v>84</v>
       </c>
       <c r="AT239" t="s" s="2">
         <v>84</v>
@@ -35487,10 +35497,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>786</v>
+        <v>831</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -35498,10 +35508,10 @@
       </c>
       <c r="E240" s="2"/>
       <c r="F240" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G240" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H240" t="s" s="2">
         <v>84</v>
@@ -35513,24 +35523,24 @@
         <v>84</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>428</v>
+        <v>149</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>787</v>
+        <v>245</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="N240" s="2"/>
-      <c r="O240" t="s" s="2">
-        <v>789</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N240" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q240" s="2"/>
       <c r="R240" t="s" s="2">
-        <v>84</v>
+        <v>852</v>
       </c>
       <c r="S240" t="s" s="2">
         <v>84</v>
@@ -35572,19 +35582,19 @@
         <v>84</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>786</v>
+        <v>248</v>
       </c>
       <c r="AG240" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH240" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI240" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ240" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK240" t="s" s="2">
         <v>84</v>
@@ -35611,7 +35621,7 @@
         <v>84</v>
       </c>
       <c r="AS240" t="s" s="2">
-        <v>790</v>
+        <v>216</v>
       </c>
       <c r="AT240" t="s" s="2">
         <v>84</v>
@@ -35622,10 +35632,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>791</v>
+        <v>833</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -35633,7 +35643,7 @@
       </c>
       <c r="E241" s="2"/>
       <c r="F241" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G241" t="s" s="2">
         <v>102</v>
@@ -35651,10 +35661,10 @@
         <v>251</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>792</v>
+        <v>252</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>793</v>
+        <v>253</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
@@ -35681,13 +35691,11 @@
         <v>84</v>
       </c>
       <c r="X241" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y241" t="s" s="2">
-        <v>794</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y241" s="2"/>
       <c r="Z241" t="s" s="2">
-        <v>795</v>
+        <v>858</v>
       </c>
       <c r="AA241" t="s" s="2">
         <v>84</v>
@@ -35705,10 +35713,10 @@
         <v>84</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>791</v>
+        <v>256</v>
       </c>
       <c r="AG241" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="AH241" t="s" s="2">
         <v>102</v>
@@ -35744,10 +35752,10 @@
         <v>84</v>
       </c>
       <c r="AS241" t="s" s="2">
-        <v>777</v>
+        <v>216</v>
       </c>
       <c r="AT241" t="s" s="2">
-        <v>797</v>
+        <v>84</v>
       </c>
       <c r="AU241" t="s" s="2">
         <v>84</v>
@@ -35766,7 +35774,7 @@
       </c>
       <c r="E242" s="2"/>
       <c r="F242" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G242" t="s" s="2">
         <v>102</v>
@@ -35781,22 +35789,24 @@
         <v>84</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>117</v>
+        <v>245</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N242" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N242" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="O242" s="2"/>
       <c r="P242" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q242" s="2"/>
       <c r="R242" t="s" s="2">
-        <v>84</v>
+        <v>861</v>
       </c>
       <c r="S242" t="s" s="2">
         <v>84</v>
@@ -35838,10 +35848,10 @@
         <v>84</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>119</v>
+        <v>248</v>
       </c>
       <c r="AG242" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH242" t="s" s="2">
         <v>102</v>
@@ -35877,7 +35887,7 @@
         <v>84</v>
       </c>
       <c r="AS242" t="s" s="2">
-        <v>120</v>
+        <v>216</v>
       </c>
       <c r="AT242" t="s" s="2">
         <v>84</v>
@@ -35888,21 +35898,21 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E243" s="2"/>
       <c r="F243" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G243" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H243" t="s" s="2">
         <v>84</v>
@@ -35914,17 +35924,15 @@
         <v>84</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>123</v>
+        <v>325</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>124</v>
+        <v>252</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N243" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N243" s="2"/>
       <c r="O243" s="2"/>
       <c r="P243" t="s" s="2">
         <v>84</v>
@@ -35961,31 +35969,31 @@
         <v>84</v>
       </c>
       <c r="AB243" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC243" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD243" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE243" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>130</v>
+        <v>256</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH243" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI243" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ243" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK243" t="s" s="2">
         <v>84</v>
@@ -36012,7 +36020,7 @@
         <v>84</v>
       </c>
       <c r="AS243" t="s" s="2">
-        <v>120</v>
+        <v>216</v>
       </c>
       <c r="AT243" t="s" s="2">
         <v>84</v>
@@ -36023,14 +36031,14 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>864</v>
+        <v>781</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
-        <v>84</v>
+        <v>782</v>
       </c>
       <c r="E244" s="2"/>
       <c r="F244" t="s" s="2">
@@ -36043,25 +36051,25 @@
         <v>84</v>
       </c>
       <c r="I244" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J244" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>865</v>
+        <v>783</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>866</v>
+        <v>784</v>
       </c>
       <c r="N244" t="s" s="2">
-        <v>867</v>
+        <v>126</v>
       </c>
       <c r="O244" t="s" s="2">
-        <v>868</v>
+        <v>425</v>
       </c>
       <c r="P244" t="s" s="2">
         <v>84</v>
@@ -36098,17 +36106,19 @@
         <v>84</v>
       </c>
       <c r="AB244" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AC244" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC244" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD244" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE244" t="s" s="2">
-        <v>618</v>
+        <v>84</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>869</v>
+        <v>785</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>85</v>
@@ -36120,7 +36130,7 @@
         <v>84</v>
       </c>
       <c r="AJ244" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK244" t="s" s="2">
         <v>84</v>
@@ -36144,10 +36154,10 @@
         <v>84</v>
       </c>
       <c r="AR244" t="s" s="2">
-        <v>870</v>
+        <v>84</v>
       </c>
       <c r="AS244" t="s" s="2">
-        <v>871</v>
+        <v>216</v>
       </c>
       <c r="AT244" t="s" s="2">
         <v>84</v>
@@ -36156,16 +36166,14 @@
         <v>84</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="C245" t="s" s="2">
-        <v>873</v>
-      </c>
+        <v>786</v>
+      </c>
+      <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
         <v>84</v>
       </c>
@@ -36174,31 +36182,29 @@
         <v>85</v>
       </c>
       <c r="G245" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H245" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I245" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J245" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>171</v>
+        <v>428</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>865</v>
+        <v>787</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="N245" t="s" s="2">
-        <v>867</v>
-      </c>
+        <v>788</v>
+      </c>
+      <c r="N245" s="2"/>
       <c r="O245" t="s" s="2">
-        <v>868</v>
+        <v>789</v>
       </c>
       <c r="P245" t="s" s="2">
         <v>84</v>
@@ -36223,11 +36229,13 @@
         <v>84</v>
       </c>
       <c r="X245" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y245" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y245" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z245" t="s" s="2">
-        <v>874</v>
+        <v>84</v>
       </c>
       <c r="AA245" t="s" s="2">
         <v>84</v>
@@ -36245,7 +36253,7 @@
         <v>84</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>869</v>
+        <v>786</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>85</v>
@@ -36281,10 +36289,10 @@
         <v>84</v>
       </c>
       <c r="AR245" t="s" s="2">
-        <v>870</v>
+        <v>84</v>
       </c>
       <c r="AS245" t="s" s="2">
-        <v>871</v>
+        <v>790</v>
       </c>
       <c r="AT245" t="s" s="2">
         <v>84</v>
@@ -36293,50 +36301,44 @@
         <v>84</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="C246" t="s" s="2">
-        <v>809</v>
-      </c>
+        <v>791</v>
+      </c>
+      <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E246" s="2"/>
       <c r="F246" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G246" t="s" s="2">
         <v>102</v>
       </c>
       <c r="H246" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I246" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J246" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>171</v>
+        <v>251</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>865</v>
+        <v>792</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="N246" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="O246" t="s" s="2">
-        <v>868</v>
-      </c>
+        <v>793</v>
+      </c>
+      <c r="N246" s="2"/>
+      <c r="O246" s="2"/>
       <c r="P246" t="s" s="2">
         <v>84</v>
       </c>
@@ -36360,11 +36362,13 @@
         <v>84</v>
       </c>
       <c r="X246" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y246" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="Y246" t="s" s="2">
+        <v>794</v>
+      </c>
       <c r="Z246" t="s" s="2">
-        <v>876</v>
+        <v>795</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>84</v>
@@ -36382,13 +36386,13 @@
         <v>84</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>869</v>
+        <v>791</v>
       </c>
       <c r="AG246" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH246" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI246" t="s" s="2">
         <v>84</v>
@@ -36418,13 +36422,13 @@
         <v>84</v>
       </c>
       <c r="AR246" t="s" s="2">
-        <v>870</v>
+        <v>84</v>
       </c>
       <c r="AS246" t="s" s="2">
-        <v>871</v>
+        <v>777</v>
       </c>
       <c r="AT246" t="s" s="2">
-        <v>84</v>
+        <v>797</v>
       </c>
       <c r="AU246" t="s" s="2">
         <v>84</v>
@@ -36432,10 +36436,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>877</v>
+        <v>867</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>878</v>
+        <v>868</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -36455,23 +36459,19 @@
         <v>84</v>
       </c>
       <c r="J247" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K247" t="s" s="2">
         <v>116</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>879</v>
+        <v>117</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="N247" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="O247" t="s" s="2">
-        <v>882</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N247" s="2"/>
+      <c r="O247" s="2"/>
       <c r="P247" t="s" s="2">
         <v>84</v>
       </c>
@@ -36519,7 +36519,7 @@
         <v>84</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>883</v>
+        <v>119</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>85</v>
@@ -36531,7 +36531,7 @@
         <v>84</v>
       </c>
       <c r="AJ247" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK247" t="s" s="2">
         <v>84</v>
@@ -36555,10 +36555,10 @@
         <v>84</v>
       </c>
       <c r="AR247" t="s" s="2">
-        <v>884</v>
+        <v>84</v>
       </c>
       <c r="AS247" t="s" s="2">
-        <v>885</v>
+        <v>120</v>
       </c>
       <c r="AT247" t="s" s="2">
         <v>84</v>
@@ -36569,21 +36569,21 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>886</v>
+        <v>869</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>798</v>
+        <v>870</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E248" s="2"/>
       <c r="F248" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G248" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H248" t="s" s="2">
         <v>84</v>
@@ -36595,18 +36595,18 @@
         <v>84</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>271</v>
+        <v>123</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>887</v>
+        <v>124</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="N248" s="2"/>
-      <c r="O248" t="s" s="2">
-        <v>801</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="N248" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O248" s="2"/>
       <c r="P248" t="s" s="2">
         <v>84</v>
       </c>
@@ -36642,31 +36642,31 @@
         <v>84</v>
       </c>
       <c r="AB248" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC248" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD248" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE248" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>798</v>
+        <v>130</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH248" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI248" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ248" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK248" t="s" s="2">
         <v>84</v>
@@ -36693,10 +36693,10 @@
         <v>84</v>
       </c>
       <c r="AS248" t="s" s="2">
-        <v>802</v>
+        <v>120</v>
       </c>
       <c r="AT248" t="s" s="2">
-        <v>803</v>
+        <v>84</v>
       </c>
       <c r="AU248" t="s" s="2">
         <v>84</v>
@@ -36704,10 +36704,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>888</v>
+        <v>871</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>889</v>
+        <v>872</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -36718,7 +36718,7 @@
         <v>85</v>
       </c>
       <c r="G249" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H249" t="s" s="2">
         <v>84</v>
@@ -36727,19 +36727,23 @@
         <v>84</v>
       </c>
       <c r="J249" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>117</v>
+        <v>873</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N249" s="2"/>
-      <c r="O249" s="2"/>
+        <v>874</v>
+      </c>
+      <c r="N249" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="O249" t="s" s="2">
+        <v>876</v>
+      </c>
       <c r="P249" t="s" s="2">
         <v>84</v>
       </c>
@@ -36775,31 +36779,29 @@
         <v>84</v>
       </c>
       <c r="AB249" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC249" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="AC249" s="2"/>
       <c r="AD249" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE249" t="s" s="2">
-        <v>84</v>
+        <v>618</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>119</v>
+        <v>877</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH249" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI249" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ249" t="s" s="2">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="AK249" t="s" s="2">
         <v>84</v>
@@ -36823,10 +36825,10 @@
         <v>84</v>
       </c>
       <c r="AR249" t="s" s="2">
-        <v>84</v>
+        <v>878</v>
       </c>
       <c r="AS249" t="s" s="2">
-        <v>120</v>
+        <v>879</v>
       </c>
       <c r="AT249" t="s" s="2">
         <v>84</v>
@@ -36835,46 +36837,50 @@
         <v>84</v>
       </c>
     </row>
-    <row r="250" hidden="true">
+    <row r="250">
       <c r="A250" t="s" s="2">
-        <v>890</v>
+        <v>880</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>891</v>
-      </c>
-      <c r="C250" s="2"/>
+        <v>872</v>
+      </c>
+      <c r="C250" t="s" s="2">
+        <v>881</v>
+      </c>
       <c r="D250" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E250" s="2"/>
       <c r="F250" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G250" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H250" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I250" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J250" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>124</v>
+        <v>873</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>125</v>
+        <v>874</v>
       </c>
       <c r="N250" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O250" s="2"/>
+        <v>875</v>
+      </c>
+      <c r="O250" t="s" s="2">
+        <v>876</v>
+      </c>
       <c r="P250" t="s" s="2">
         <v>84</v>
       </c>
@@ -36898,31 +36904,29 @@
         <v>84</v>
       </c>
       <c r="X250" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y250" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y250" s="2"/>
       <c r="Z250" t="s" s="2">
-        <v>84</v>
+        <v>882</v>
       </c>
       <c r="AA250" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB250" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC250" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD250" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE250" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>130</v>
+        <v>877</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>85</v>
@@ -36934,7 +36938,7 @@
         <v>84</v>
       </c>
       <c r="AJ250" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK250" t="s" s="2">
         <v>84</v>
@@ -36958,10 +36962,10 @@
         <v>84</v>
       </c>
       <c r="AR250" t="s" s="2">
-        <v>84</v>
+        <v>878</v>
       </c>
       <c r="AS250" t="s" s="2">
-        <v>120</v>
+        <v>879</v>
       </c>
       <c r="AT250" t="s" s="2">
         <v>84</v>
@@ -36970,14 +36974,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="251" hidden="true">
+    <row r="251">
       <c r="A251" t="s" s="2">
-        <v>892</v>
+        <v>883</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="C251" s="2"/>
+        <v>872</v>
+      </c>
+      <c r="C251" t="s" s="2">
+        <v>809</v>
+      </c>
       <c r="D251" t="s" s="2">
         <v>84</v>
       </c>
@@ -36989,7 +36995,7 @@
         <v>102</v>
       </c>
       <c r="H251" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I251" t="s" s="2">
         <v>84</v>
@@ -36998,18 +37004,20 @@
         <v>103</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>278</v>
+        <v>171</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>894</v>
+        <v>873</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>280</v>
+        <v>874</v>
       </c>
       <c r="N251" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O251" s="2"/>
+        <v>875</v>
+      </c>
+      <c r="O251" t="s" s="2">
+        <v>876</v>
+      </c>
       <c r="P251" t="s" s="2">
         <v>84</v>
       </c>
@@ -37033,13 +37041,11 @@
         <v>84</v>
       </c>
       <c r="X251" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y251" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y251" s="2"/>
       <c r="Z251" t="s" s="2">
-        <v>84</v>
+        <v>884</v>
       </c>
       <c r="AA251" t="s" s="2">
         <v>84</v>
@@ -37057,16 +37063,16 @@
         <v>84</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>282</v>
+        <v>877</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH251" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI251" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ251" t="s" s="2">
         <v>114</v>
@@ -37081,7 +37087,7 @@
         <v>84</v>
       </c>
       <c r="AN251" t="s" s="2">
-        <v>895</v>
+        <v>84</v>
       </c>
       <c r="AO251" t="s" s="2">
         <v>84</v>
@@ -37093,10 +37099,10 @@
         <v>84</v>
       </c>
       <c r="AR251" t="s" s="2">
-        <v>285</v>
+        <v>878</v>
       </c>
       <c r="AS251" t="s" s="2">
-        <v>286</v>
+        <v>879</v>
       </c>
       <c r="AT251" t="s" s="2">
         <v>84</v>
@@ -37107,10 +37113,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>896</v>
+        <v>885</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>897</v>
+        <v>886</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -37133,24 +37139,24 @@
         <v>103</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>278</v>
+        <v>116</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>898</v>
+        <v>887</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>290</v>
+        <v>888</v>
       </c>
       <c r="N252" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O252" s="2"/>
+        <v>889</v>
+      </c>
+      <c r="O252" t="s" s="2">
+        <v>890</v>
+      </c>
       <c r="P252" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q252" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="Q252" s="2"/>
       <c r="R252" t="s" s="2">
         <v>84</v>
       </c>
@@ -37194,7 +37200,7 @@
         <v>84</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>293</v>
+        <v>891</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>85</v>
@@ -37203,7 +37209,7 @@
         <v>102</v>
       </c>
       <c r="AI252" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ252" t="s" s="2">
         <v>114</v>
@@ -37218,7 +37224,7 @@
         <v>84</v>
       </c>
       <c r="AN252" t="s" s="2">
-        <v>899</v>
+        <v>84</v>
       </c>
       <c r="AO252" t="s" s="2">
         <v>84</v>
@@ -37230,10 +37236,10 @@
         <v>84</v>
       </c>
       <c r="AR252" t="s" s="2">
-        <v>295</v>
+        <v>892</v>
       </c>
       <c r="AS252" t="s" s="2">
-        <v>296</v>
+        <v>893</v>
       </c>
       <c r="AT252" t="s" s="2">
         <v>84</v>
@@ -37244,10 +37250,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -37270,16 +37276,18 @@
         <v>84</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>901</v>
+        <v>271</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="N253" s="2"/>
-      <c r="O253" s="2"/>
+      <c r="O253" t="s" s="2">
+        <v>801</v>
+      </c>
       <c r="P253" t="s" s="2">
         <v>84</v>
       </c>
@@ -37327,7 +37335,7 @@
         <v>84</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>85</v>
@@ -37351,7 +37359,7 @@
         <v>84</v>
       </c>
       <c r="AN253" t="s" s="2">
-        <v>903</v>
+        <v>84</v>
       </c>
       <c r="AO253" t="s" s="2">
         <v>84</v>
@@ -37366,10 +37374,10 @@
         <v>84</v>
       </c>
       <c r="AS253" t="s" s="2">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="AT253" t="s" s="2">
-        <v>84</v>
+        <v>803</v>
       </c>
       <c r="AU253" t="s" s="2">
         <v>84</v>
@@ -37377,14 +37385,12 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="C254" t="s" s="2">
-        <v>905</v>
-      </c>
+        <v>897</v>
+      </c>
+      <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
         <v>84</v>
       </c>
@@ -37405,13 +37411,13 @@
         <v>84</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>772</v>
+        <v>116</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>906</v>
+        <v>117</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>774</v>
+        <v>118</v>
       </c>
       <c r="N254" s="2"/>
       <c r="O254" s="2"/>
@@ -37462,19 +37468,19 @@
         <v>84</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>771</v>
+        <v>119</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH254" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI254" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ254" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK254" t="s" s="2">
         <v>84</v>
@@ -37498,13 +37504,13 @@
         <v>84</v>
       </c>
       <c r="AR254" t="s" s="2">
-        <v>776</v>
+        <v>84</v>
       </c>
       <c r="AS254" t="s" s="2">
-        <v>777</v>
+        <v>120</v>
       </c>
       <c r="AT254" t="s" s="2">
-        <v>778</v>
+        <v>84</v>
       </c>
       <c r="AU254" t="s" s="2">
         <v>84</v>
@@ -37512,21 +37518,21 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>907</v>
+        <v>898</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>779</v>
+        <v>899</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E255" s="2"/>
       <c r="F255" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G255" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H255" t="s" s="2">
         <v>84</v>
@@ -37538,15 +37544,17 @@
         <v>84</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N255" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="N255" t="s" s="2">
+        <v>126</v>
+      </c>
       <c r="O255" s="2"/>
       <c r="P255" t="s" s="2">
         <v>84</v>
@@ -37583,31 +37591,31 @@
         <v>84</v>
       </c>
       <c r="AB255" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC255" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD255" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE255" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH255" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI255" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ255" t="s" s="2">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="AK255" t="s" s="2">
         <v>84</v>
@@ -37645,21 +37653,21 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>780</v>
+        <v>901</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E256" s="2"/>
       <c r="F256" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G256" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H256" t="s" s="2">
         <v>84</v>
@@ -37668,19 +37676,19 @@
         <v>84</v>
       </c>
       <c r="J256" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>123</v>
+        <v>278</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>124</v>
+        <v>902</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="N256" t="s" s="2">
-        <v>126</v>
+        <v>281</v>
       </c>
       <c r="O256" s="2"/>
       <c r="P256" t="s" s="2">
@@ -37730,19 +37738,19 @@
         <v>84</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>130</v>
+        <v>282</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH256" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI256" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="AJ256" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK256" t="s" s="2">
         <v>84</v>
@@ -37754,7 +37762,7 @@
         <v>84</v>
       </c>
       <c r="AN256" t="s" s="2">
-        <v>84</v>
+        <v>903</v>
       </c>
       <c r="AO256" t="s" s="2">
         <v>84</v>
@@ -37766,10 +37774,10 @@
         <v>84</v>
       </c>
       <c r="AR256" t="s" s="2">
-        <v>84</v>
+        <v>285</v>
       </c>
       <c r="AS256" t="s" s="2">
-        <v>120</v>
+        <v>286</v>
       </c>
       <c r="AT256" t="s" s="2">
         <v>84</v>
@@ -37780,50 +37788,50 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>781</v>
+        <v>905</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
-        <v>782</v>
+        <v>84</v>
       </c>
       <c r="E257" s="2"/>
       <c r="F257" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G257" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H257" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I257" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="J257" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>123</v>
+        <v>278</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>783</v>
+        <v>906</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>784</v>
+        <v>290</v>
       </c>
       <c r="N257" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O257" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="O257" s="2"/>
       <c r="P257" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q257" s="2"/>
+      <c r="Q257" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="R257" t="s" s="2">
         <v>84</v>
       </c>
@@ -37867,19 +37875,19 @@
         <v>84</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>785</v>
+        <v>293</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH257" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI257" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="AJ257" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK257" t="s" s="2">
         <v>84</v>
@@ -37891,7 +37899,7 @@
         <v>84</v>
       </c>
       <c r="AN257" t="s" s="2">
-        <v>84</v>
+        <v>907</v>
       </c>
       <c r="AO257" t="s" s="2">
         <v>84</v>
@@ -37903,10 +37911,10 @@
         <v>84</v>
       </c>
       <c r="AR257" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AS257" t="s" s="2">
-        <v>216</v>
+        <v>296</v>
       </c>
       <c r="AT257" t="s" s="2">
         <v>84</v>
@@ -37917,10 +37925,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>786</v>
+        <v>804</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -37931,7 +37939,7 @@
         <v>85</v>
       </c>
       <c r="G258" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H258" t="s" s="2">
         <v>84</v>
@@ -37943,18 +37951,16 @@
         <v>84</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>428</v>
+        <v>484</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>787</v>
+        <v>805</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="N258" s="2"/>
-      <c r="O258" t="s" s="2">
-        <v>789</v>
-      </c>
+      <c r="O258" s="2"/>
       <c r="P258" t="s" s="2">
         <v>84</v>
       </c>
@@ -38002,13 +38008,13 @@
         <v>84</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>786</v>
+        <v>804</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH258" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI258" t="s" s="2">
         <v>84</v>
@@ -38041,7 +38047,7 @@
         <v>84</v>
       </c>
       <c r="AS258" t="s" s="2">
-        <v>790</v>
+        <v>807</v>
       </c>
       <c r="AT258" t="s" s="2">
         <v>84</v>
@@ -38052,18 +38058,20 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="C259" s="2"/>
+        <v>771</v>
+      </c>
+      <c r="C259" t="s" s="2">
+        <v>910</v>
+      </c>
       <c r="D259" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E259" s="2"/>
       <c r="F259" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G259" t="s" s="2">
         <v>102</v>
@@ -38078,13 +38086,13 @@
         <v>84</v>
       </c>
       <c r="K259" t="s" s="2">
-        <v>251</v>
+        <v>772</v>
       </c>
       <c r="L259" t="s" s="2">
-        <v>792</v>
+        <v>911</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>793</v>
+        <v>774</v>
       </c>
       <c r="N259" s="2"/>
       <c r="O259" s="2"/>
@@ -38111,13 +38119,13 @@
         <v>84</v>
       </c>
       <c r="X259" t="s" s="2">
-        <v>183</v>
+        <v>84</v>
       </c>
       <c r="Y259" t="s" s="2">
-        <v>794</v>
+        <v>84</v>
       </c>
       <c r="Z259" t="s" s="2">
-        <v>795</v>
+        <v>84</v>
       </c>
       <c r="AA259" t="s" s="2">
         <v>84</v>
@@ -38135,13 +38143,13 @@
         <v>84</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>791</v>
+        <v>771</v>
       </c>
       <c r="AG259" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="AH259" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI259" t="s" s="2">
         <v>84</v>
@@ -38171,13 +38179,13 @@
         <v>84</v>
       </c>
       <c r="AR259" t="s" s="2">
-        <v>84</v>
+        <v>776</v>
       </c>
       <c r="AS259" t="s" s="2">
         <v>777</v>
       </c>
       <c r="AT259" t="s" s="2">
-        <v>797</v>
+        <v>778</v>
       </c>
       <c r="AU259" t="s" s="2">
         <v>84</v>
@@ -38188,7 +38196,7 @@
         <v>912</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>860</v>
+        <v>779</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -38321,7 +38329,7 @@
         <v>913</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>862</v>
+        <v>780</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -38391,16 +38399,16 @@
         <v>84</v>
       </c>
       <c r="AB261" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC261" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD261" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE261" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF261" t="s" s="2">
         <v>130</v>
@@ -38456,11 +38464,11 @@
         <v>914</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>864</v>
+        <v>781</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
-        <v>84</v>
+        <v>782</v>
       </c>
       <c r="E262" s="2"/>
       <c r="F262" t="s" s="2">
@@ -38473,25 +38481,25 @@
         <v>84</v>
       </c>
       <c r="I262" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J262" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K262" t="s" s="2">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>865</v>
+        <v>783</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>866</v>
+        <v>784</v>
       </c>
       <c r="N262" t="s" s="2">
-        <v>867</v>
+        <v>126</v>
       </c>
       <c r="O262" t="s" s="2">
-        <v>868</v>
+        <v>425</v>
       </c>
       <c r="P262" t="s" s="2">
         <v>84</v>
@@ -38528,17 +38536,19 @@
         <v>84</v>
       </c>
       <c r="AB262" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AC262" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC262" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD262" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE262" t="s" s="2">
-        <v>618</v>
+        <v>84</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>869</v>
+        <v>785</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>85</v>
@@ -38550,7 +38560,7 @@
         <v>84</v>
       </c>
       <c r="AJ262" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK262" t="s" s="2">
         <v>84</v>
@@ -38574,10 +38584,10 @@
         <v>84</v>
       </c>
       <c r="AR262" t="s" s="2">
-        <v>870</v>
+        <v>84</v>
       </c>
       <c r="AS262" t="s" s="2">
-        <v>871</v>
+        <v>216</v>
       </c>
       <c r="AT262" t="s" s="2">
         <v>84</v>
@@ -38586,16 +38596,14 @@
         <v>84</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
         <v>915</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="C263" t="s" s="2">
-        <v>916</v>
-      </c>
+        <v>786</v>
+      </c>
+      <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
         <v>84</v>
       </c>
@@ -38604,31 +38612,29 @@
         <v>85</v>
       </c>
       <c r="G263" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H263" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I263" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J263" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>171</v>
+        <v>428</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>917</v>
+        <v>787</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="N263" t="s" s="2">
-        <v>867</v>
-      </c>
+        <v>788</v>
+      </c>
+      <c r="N263" s="2"/>
       <c r="O263" t="s" s="2">
-        <v>868</v>
+        <v>789</v>
       </c>
       <c r="P263" t="s" s="2">
         <v>84</v>
@@ -38653,11 +38659,13 @@
         <v>84</v>
       </c>
       <c r="X263" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y263" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y263" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z263" t="s" s="2">
-        <v>918</v>
+        <v>84</v>
       </c>
       <c r="AA263" t="s" s="2">
         <v>84</v>
@@ -38675,7 +38683,7 @@
         <v>84</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>869</v>
+        <v>786</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>85</v>
@@ -38693,7 +38701,7 @@
         <v>84</v>
       </c>
       <c r="AL263" t="s" s="2">
-        <v>919</v>
+        <v>84</v>
       </c>
       <c r="AM263" t="s" s="2">
         <v>84</v>
@@ -38711,10 +38719,10 @@
         <v>84</v>
       </c>
       <c r="AR263" t="s" s="2">
-        <v>870</v>
+        <v>84</v>
       </c>
       <c r="AS263" t="s" s="2">
-        <v>871</v>
+        <v>790</v>
       </c>
       <c r="AT263" t="s" s="2">
         <v>84</v>
@@ -38723,50 +38731,44 @@
         <v>84</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="C264" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>791</v>
+      </c>
+      <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E264" s="2"/>
       <c r="F264" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G264" t="s" s="2">
         <v>102</v>
       </c>
       <c r="H264" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I264" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J264" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>171</v>
+        <v>251</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>921</v>
+        <v>792</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="N264" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="O264" t="s" s="2">
-        <v>868</v>
-      </c>
+        <v>793</v>
+      </c>
+      <c r="N264" s="2"/>
+      <c r="O264" s="2"/>
       <c r="P264" t="s" s="2">
         <v>84</v>
       </c>
@@ -38790,11 +38792,13 @@
         <v>84</v>
       </c>
       <c r="X264" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y264" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="Y264" t="s" s="2">
+        <v>794</v>
+      </c>
       <c r="Z264" t="s" s="2">
-        <v>922</v>
+        <v>795</v>
       </c>
       <c r="AA264" t="s" s="2">
         <v>84</v>
@@ -38812,13 +38816,13 @@
         <v>84</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>869</v>
+        <v>791</v>
       </c>
       <c r="AG264" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH264" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI264" t="s" s="2">
         <v>84</v>
@@ -38830,7 +38834,7 @@
         <v>84</v>
       </c>
       <c r="AL264" t="s" s="2">
-        <v>923</v>
+        <v>84</v>
       </c>
       <c r="AM264" t="s" s="2">
         <v>84</v>
@@ -38848,13 +38852,13 @@
         <v>84</v>
       </c>
       <c r="AR264" t="s" s="2">
-        <v>870</v>
+        <v>84</v>
       </c>
       <c r="AS264" t="s" s="2">
-        <v>871</v>
+        <v>777</v>
       </c>
       <c r="AT264" t="s" s="2">
-        <v>84</v>
+        <v>797</v>
       </c>
       <c r="AU264" t="s" s="2">
         <v>84</v>
@@ -38862,10 +38866,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>924</v>
+        <v>917</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>878</v>
+        <v>868</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -38885,23 +38889,19 @@
         <v>84</v>
       </c>
       <c r="J265" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K265" t="s" s="2">
         <v>116</v>
       </c>
       <c r="L265" t="s" s="2">
-        <v>879</v>
+        <v>117</v>
       </c>
       <c r="M265" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="N265" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="O265" t="s" s="2">
-        <v>882</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N265" s="2"/>
+      <c r="O265" s="2"/>
       <c r="P265" t="s" s="2">
         <v>84</v>
       </c>
@@ -38949,7 +38949,7 @@
         <v>84</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>883</v>
+        <v>119</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>85</v>
@@ -38961,7 +38961,7 @@
         <v>84</v>
       </c>
       <c r="AJ265" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK265" t="s" s="2">
         <v>84</v>
@@ -38985,10 +38985,10 @@
         <v>84</v>
       </c>
       <c r="AR265" t="s" s="2">
-        <v>884</v>
+        <v>84</v>
       </c>
       <c r="AS265" t="s" s="2">
-        <v>885</v>
+        <v>120</v>
       </c>
       <c r="AT265" t="s" s="2">
         <v>84</v>
@@ -38997,26 +38997,26 @@
         <v>84</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>798</v>
+        <v>870</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E266" s="2"/>
       <c r="F266" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G266" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H266" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I266" t="s" s="2">
         <v>84</v>
@@ -39025,18 +39025,18 @@
         <v>84</v>
       </c>
       <c r="K266" t="s" s="2">
-        <v>271</v>
+        <v>123</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>799</v>
+        <v>124</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="N266" s="2"/>
-      <c r="O266" t="s" s="2">
-        <v>801</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="N266" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O266" s="2"/>
       <c r="P266" t="s" s="2">
         <v>84</v>
       </c>
@@ -39072,31 +39072,31 @@
         <v>84</v>
       </c>
       <c r="AB266" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC266" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD266" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE266" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>798</v>
+        <v>130</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH266" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI266" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ266" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK266" t="s" s="2">
         <v>84</v>
@@ -39123,10 +39123,10 @@
         <v>84</v>
       </c>
       <c r="AS266" t="s" s="2">
-        <v>802</v>
+        <v>120</v>
       </c>
       <c r="AT266" t="s" s="2">
-        <v>803</v>
+        <v>84</v>
       </c>
       <c r="AU266" t="s" s="2">
         <v>84</v>
@@ -39134,10 +39134,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>889</v>
+        <v>872</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -39148,7 +39148,7 @@
         <v>85</v>
       </c>
       <c r="G267" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H267" t="s" s="2">
         <v>84</v>
@@ -39157,19 +39157,23 @@
         <v>84</v>
       </c>
       <c r="J267" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K267" t="s" s="2">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>117</v>
+        <v>873</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N267" s="2"/>
-      <c r="O267" s="2"/>
+        <v>874</v>
+      </c>
+      <c r="N267" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="O267" t="s" s="2">
+        <v>876</v>
+      </c>
       <c r="P267" t="s" s="2">
         <v>84</v>
       </c>
@@ -39205,31 +39209,29 @@
         <v>84</v>
       </c>
       <c r="AB267" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC267" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="AC267" s="2"/>
       <c r="AD267" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE267" t="s" s="2">
-        <v>84</v>
+        <v>618</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>119</v>
+        <v>877</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH267" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI267" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ267" t="s" s="2">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="AK267" t="s" s="2">
         <v>84</v>
@@ -39253,10 +39255,10 @@
         <v>84</v>
       </c>
       <c r="AR267" t="s" s="2">
-        <v>84</v>
+        <v>878</v>
       </c>
       <c r="AS267" t="s" s="2">
-        <v>120</v>
+        <v>879</v>
       </c>
       <c r="AT267" t="s" s="2">
         <v>84</v>
@@ -39265,46 +39267,50 @@
         <v>84</v>
       </c>
     </row>
-    <row r="268" hidden="true">
+    <row r="268">
       <c r="A268" t="s" s="2">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>891</v>
-      </c>
-      <c r="C268" s="2"/>
+        <v>872</v>
+      </c>
+      <c r="C268" t="s" s="2">
+        <v>921</v>
+      </c>
       <c r="D268" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E268" s="2"/>
       <c r="F268" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G268" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H268" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I268" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J268" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K268" t="s" s="2">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>124</v>
+        <v>922</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>125</v>
+        <v>874</v>
       </c>
       <c r="N268" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O268" s="2"/>
+        <v>875</v>
+      </c>
+      <c r="O268" t="s" s="2">
+        <v>876</v>
+      </c>
       <c r="P268" t="s" s="2">
         <v>84</v>
       </c>
@@ -39328,31 +39334,29 @@
         <v>84</v>
       </c>
       <c r="X268" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y268" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y268" s="2"/>
       <c r="Z268" t="s" s="2">
-        <v>84</v>
+        <v>923</v>
       </c>
       <c r="AA268" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB268" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC268" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD268" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE268" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>130</v>
+        <v>877</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>85</v>
@@ -39364,13 +39368,13 @@
         <v>84</v>
       </c>
       <c r="AJ268" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK268" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL268" t="s" s="2">
-        <v>84</v>
+        <v>924</v>
       </c>
       <c r="AM268" t="s" s="2">
         <v>84</v>
@@ -39388,10 +39392,10 @@
         <v>84</v>
       </c>
       <c r="AR268" t="s" s="2">
-        <v>84</v>
+        <v>878</v>
       </c>
       <c r="AS268" t="s" s="2">
-        <v>120</v>
+        <v>879</v>
       </c>
       <c r="AT268" t="s" s="2">
         <v>84</v>
@@ -39400,14 +39404,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="269" hidden="true">
+    <row r="269">
       <c r="A269" t="s" s="2">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="C269" s="2"/>
+        <v>872</v>
+      </c>
+      <c r="C269" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="D269" t="s" s="2">
         <v>84</v>
       </c>
@@ -39419,7 +39425,7 @@
         <v>102</v>
       </c>
       <c r="H269" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I269" t="s" s="2">
         <v>84</v>
@@ -39428,18 +39434,20 @@
         <v>103</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>278</v>
+        <v>171</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>280</v>
+        <v>874</v>
       </c>
       <c r="N269" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O269" s="2"/>
+        <v>875</v>
+      </c>
+      <c r="O269" t="s" s="2">
+        <v>876</v>
+      </c>
       <c r="P269" t="s" s="2">
         <v>84</v>
       </c>
@@ -39463,13 +39471,11 @@
         <v>84</v>
       </c>
       <c r="X269" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y269" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y269" s="2"/>
       <c r="Z269" t="s" s="2">
-        <v>84</v>
+        <v>927</v>
       </c>
       <c r="AA269" t="s" s="2">
         <v>84</v>
@@ -39487,16 +39493,16 @@
         <v>84</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>282</v>
+        <v>877</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH269" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI269" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ269" t="s" s="2">
         <v>114</v>
@@ -39505,7 +39511,7 @@
         <v>84</v>
       </c>
       <c r="AL269" t="s" s="2">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="AM269" t="s" s="2">
         <v>84</v>
@@ -39523,10 +39529,10 @@
         <v>84</v>
       </c>
       <c r="AR269" t="s" s="2">
-        <v>285</v>
+        <v>878</v>
       </c>
       <c r="AS269" t="s" s="2">
-        <v>286</v>
+        <v>879</v>
       </c>
       <c r="AT269" t="s" s="2">
         <v>84</v>
@@ -39537,10 +39543,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>897</v>
+        <v>886</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -39563,24 +39569,24 @@
         <v>103</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>278</v>
+        <v>116</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>932</v>
+        <v>887</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>290</v>
+        <v>888</v>
       </c>
       <c r="N270" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O270" s="2"/>
+        <v>889</v>
+      </c>
+      <c r="O270" t="s" s="2">
+        <v>890</v>
+      </c>
       <c r="P270" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q270" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="Q270" s="2"/>
       <c r="R270" t="s" s="2">
         <v>84</v>
       </c>
@@ -39624,7 +39630,7 @@
         <v>84</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>293</v>
+        <v>891</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>85</v>
@@ -39633,7 +39639,7 @@
         <v>102</v>
       </c>
       <c r="AI270" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ270" t="s" s="2">
         <v>114</v>
@@ -39642,7 +39648,7 @@
         <v>84</v>
       </c>
       <c r="AL270" t="s" s="2">
-        <v>933</v>
+        <v>84</v>
       </c>
       <c r="AM270" t="s" s="2">
         <v>84</v>
@@ -39660,10 +39666,10 @@
         <v>84</v>
       </c>
       <c r="AR270" t="s" s="2">
-        <v>295</v>
+        <v>892</v>
       </c>
       <c r="AS270" t="s" s="2">
-        <v>296</v>
+        <v>893</v>
       </c>
       <c r="AT270" t="s" s="2">
         <v>84</v>
@@ -39672,12 +39678,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="271" hidden="true">
+    <row r="271">
       <c r="A271" t="s" s="2">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -39688,10 +39694,10 @@
         <v>85</v>
       </c>
       <c r="G271" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="H271" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I271" t="s" s="2">
         <v>84</v>
@@ -39700,16 +39706,18 @@
         <v>84</v>
       </c>
       <c r="K271" t="s" s="2">
-        <v>484</v>
+        <v>271</v>
       </c>
       <c r="L271" t="s" s="2">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="M271" t="s" s="2">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="N271" s="2"/>
-      <c r="O271" s="2"/>
+      <c r="O271" t="s" s="2">
+        <v>801</v>
+      </c>
       <c r="P271" t="s" s="2">
         <v>84</v>
       </c>
@@ -39757,7 +39765,7 @@
         <v>84</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>85</v>
@@ -39796,10 +39804,10 @@
         <v>84</v>
       </c>
       <c r="AS271" t="s" s="2">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="AT271" t="s" s="2">
-        <v>84</v>
+        <v>803</v>
       </c>
       <c r="AU271" t="s" s="2">
         <v>84</v>
@@ -39807,14 +39815,12 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="C272" t="s" s="2">
-        <v>936</v>
-      </c>
+        <v>897</v>
+      </c>
+      <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
         <v>84</v>
       </c>
@@ -39823,7 +39829,7 @@
         <v>85</v>
       </c>
       <c r="G272" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H272" t="s" s="2">
         <v>84</v>
@@ -39835,13 +39841,13 @@
         <v>84</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>772</v>
+        <v>116</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>937</v>
+        <v>117</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>774</v>
+        <v>118</v>
       </c>
       <c r="N272" s="2"/>
       <c r="O272" s="2"/>
@@ -39892,19 +39898,19 @@
         <v>84</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>771</v>
+        <v>119</v>
       </c>
       <c r="AG272" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH272" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI272" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ272" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK272" t="s" s="2">
         <v>84</v>
@@ -39928,13 +39934,13 @@
         <v>84</v>
       </c>
       <c r="AR272" t="s" s="2">
-        <v>776</v>
+        <v>84</v>
       </c>
       <c r="AS272" t="s" s="2">
-        <v>777</v>
+        <v>120</v>
       </c>
       <c r="AT272" t="s" s="2">
-        <v>778</v>
+        <v>84</v>
       </c>
       <c r="AU272" t="s" s="2">
         <v>84</v>
@@ -39942,21 +39948,21 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>779</v>
+        <v>899</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E273" s="2"/>
       <c r="F273" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G273" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H273" t="s" s="2">
         <v>84</v>
@@ -39968,15 +39974,17 @@
         <v>84</v>
       </c>
       <c r="K273" t="s" s="2">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="M273" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N273" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="N273" t="s" s="2">
+        <v>126</v>
+      </c>
       <c r="O273" s="2"/>
       <c r="P273" t="s" s="2">
         <v>84</v>
@@ -40013,31 +40021,31 @@
         <v>84</v>
       </c>
       <c r="AB273" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC273" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD273" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE273" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH273" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI273" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ273" t="s" s="2">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="AK273" t="s" s="2">
         <v>84</v>
@@ -40075,21 +40083,21 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>780</v>
+        <v>901</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E274" s="2"/>
       <c r="F274" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G274" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H274" t="s" s="2">
         <v>84</v>
@@ -40098,19 +40106,19 @@
         <v>84</v>
       </c>
       <c r="J274" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K274" t="s" s="2">
-        <v>123</v>
+        <v>278</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>124</v>
+        <v>934</v>
       </c>
       <c r="M274" t="s" s="2">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="N274" t="s" s="2">
-        <v>126</v>
+        <v>281</v>
       </c>
       <c r="O274" s="2"/>
       <c r="P274" t="s" s="2">
@@ -40160,25 +40168,25 @@
         <v>84</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>130</v>
+        <v>282</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH274" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI274" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="AJ274" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK274" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL274" t="s" s="2">
-        <v>84</v>
+        <v>935</v>
       </c>
       <c r="AM274" t="s" s="2">
         <v>84</v>
@@ -40196,10 +40204,10 @@
         <v>84</v>
       </c>
       <c r="AR274" t="s" s="2">
-        <v>84</v>
+        <v>285</v>
       </c>
       <c r="AS274" t="s" s="2">
-        <v>120</v>
+        <v>286</v>
       </c>
       <c r="AT274" t="s" s="2">
         <v>84</v>
@@ -40210,50 +40218,50 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>781</v>
+        <v>905</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
-        <v>782</v>
+        <v>84</v>
       </c>
       <c r="E275" s="2"/>
       <c r="F275" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G275" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H275" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I275" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="J275" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K275" t="s" s="2">
-        <v>123</v>
+        <v>278</v>
       </c>
       <c r="L275" t="s" s="2">
-        <v>783</v>
+        <v>937</v>
       </c>
       <c r="M275" t="s" s="2">
-        <v>784</v>
+        <v>290</v>
       </c>
       <c r="N275" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O275" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="O275" s="2"/>
       <c r="P275" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q275" s="2"/>
+      <c r="Q275" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="R275" t="s" s="2">
         <v>84</v>
       </c>
@@ -40297,25 +40305,25 @@
         <v>84</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>785</v>
+        <v>293</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH275" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI275" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="AJ275" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK275" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL275" t="s" s="2">
-        <v>84</v>
+        <v>938</v>
       </c>
       <c r="AM275" t="s" s="2">
         <v>84</v>
@@ -40333,10 +40341,10 @@
         <v>84</v>
       </c>
       <c r="AR275" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AS275" t="s" s="2">
-        <v>216</v>
+        <v>296</v>
       </c>
       <c r="AT275" t="s" s="2">
         <v>84</v>
@@ -40347,10 +40355,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>786</v>
+        <v>804</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -40361,7 +40369,7 @@
         <v>85</v>
       </c>
       <c r="G276" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H276" t="s" s="2">
         <v>84</v>
@@ -40373,18 +40381,16 @@
         <v>84</v>
       </c>
       <c r="K276" t="s" s="2">
-        <v>428</v>
+        <v>484</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>787</v>
+        <v>805</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="N276" s="2"/>
-      <c r="O276" t="s" s="2">
-        <v>789</v>
-      </c>
+      <c r="O276" s="2"/>
       <c r="P276" t="s" s="2">
         <v>84</v>
       </c>
@@ -40432,13 +40438,13 @@
         <v>84</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>786</v>
+        <v>804</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH276" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI276" t="s" s="2">
         <v>84</v>
@@ -40471,7 +40477,7 @@
         <v>84</v>
       </c>
       <c r="AS276" t="s" s="2">
-        <v>790</v>
+        <v>807</v>
       </c>
       <c r="AT276" t="s" s="2">
         <v>84</v>
@@ -40482,21 +40488,23 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="C277" s="2"/>
+        <v>771</v>
+      </c>
+      <c r="C277" t="s" s="2">
+        <v>941</v>
+      </c>
       <c r="D277" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E277" s="2"/>
       <c r="F277" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G277" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H277" t="s" s="2">
         <v>84</v>
@@ -40508,13 +40516,13 @@
         <v>84</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>251</v>
+        <v>772</v>
       </c>
       <c r="L277" t="s" s="2">
-        <v>792</v>
+        <v>942</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>793</v>
+        <v>774</v>
       </c>
       <c r="N277" s="2"/>
       <c r="O277" s="2"/>
@@ -40541,13 +40549,13 @@
         <v>84</v>
       </c>
       <c r="X277" t="s" s="2">
-        <v>183</v>
+        <v>84</v>
       </c>
       <c r="Y277" t="s" s="2">
-        <v>794</v>
+        <v>84</v>
       </c>
       <c r="Z277" t="s" s="2">
-        <v>795</v>
+        <v>84</v>
       </c>
       <c r="AA277" t="s" s="2">
         <v>84</v>
@@ -40565,13 +40573,13 @@
         <v>84</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>791</v>
+        <v>771</v>
       </c>
       <c r="AG277" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="AH277" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI277" t="s" s="2">
         <v>84</v>
@@ -40580,7 +40588,7 @@
         <v>114</v>
       </c>
       <c r="AK277" t="s" s="2">
-        <v>943</v>
+        <v>84</v>
       </c>
       <c r="AL277" t="s" s="2">
         <v>84</v>
@@ -40601,13 +40609,13 @@
         <v>84</v>
       </c>
       <c r="AR277" t="s" s="2">
-        <v>84</v>
+        <v>776</v>
       </c>
       <c r="AS277" t="s" s="2">
         <v>777</v>
       </c>
       <c r="AT277" t="s" s="2">
-        <v>797</v>
+        <v>778</v>
       </c>
       <c r="AU277" t="s" s="2">
         <v>84</v>
@@ -40615,10 +40623,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>860</v>
+        <v>779</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -40748,10 +40756,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>862</v>
+        <v>780</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -40821,16 +40829,16 @@
         <v>84</v>
       </c>
       <c r="AB279" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC279" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD279" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE279" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF279" t="s" s="2">
         <v>130</v>
@@ -40883,14 +40891,14 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>864</v>
+        <v>781</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
-        <v>84</v>
+        <v>782</v>
       </c>
       <c r="E280" s="2"/>
       <c r="F280" t="s" s="2">
@@ -40903,25 +40911,25 @@
         <v>84</v>
       </c>
       <c r="I280" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J280" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>865</v>
+        <v>783</v>
       </c>
       <c r="M280" t="s" s="2">
-        <v>866</v>
+        <v>784</v>
       </c>
       <c r="N280" t="s" s="2">
-        <v>867</v>
+        <v>126</v>
       </c>
       <c r="O280" t="s" s="2">
-        <v>868</v>
+        <v>425</v>
       </c>
       <c r="P280" t="s" s="2">
         <v>84</v>
@@ -40958,17 +40966,19 @@
         <v>84</v>
       </c>
       <c r="AB280" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AC280" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC280" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD280" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE280" t="s" s="2">
-        <v>618</v>
+        <v>84</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>869</v>
+        <v>785</v>
       </c>
       <c r="AG280" t="s" s="2">
         <v>85</v>
@@ -40980,7 +40990,7 @@
         <v>84</v>
       </c>
       <c r="AJ280" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK280" t="s" s="2">
         <v>84</v>
@@ -41004,10 +41014,10 @@
         <v>84</v>
       </c>
       <c r="AR280" t="s" s="2">
-        <v>870</v>
+        <v>84</v>
       </c>
       <c r="AS280" t="s" s="2">
-        <v>871</v>
+        <v>216</v>
       </c>
       <c r="AT280" t="s" s="2">
         <v>84</v>
@@ -41016,16 +41026,14 @@
         <v>84</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="C281" t="s" s="2">
-        <v>948</v>
-      </c>
+        <v>786</v>
+      </c>
+      <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
         <v>84</v>
       </c>
@@ -41034,31 +41042,29 @@
         <v>85</v>
       </c>
       <c r="G281" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H281" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I281" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J281" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>171</v>
+        <v>428</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>949</v>
+        <v>787</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="N281" t="s" s="2">
-        <v>867</v>
-      </c>
+        <v>788</v>
+      </c>
+      <c r="N281" s="2"/>
       <c r="O281" t="s" s="2">
-        <v>868</v>
+        <v>789</v>
       </c>
       <c r="P281" t="s" s="2">
         <v>84</v>
@@ -41083,11 +41089,13 @@
         <v>84</v>
       </c>
       <c r="X281" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y281" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y281" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z281" t="s" s="2">
-        <v>950</v>
+        <v>84</v>
       </c>
       <c r="AA281" t="s" s="2">
         <v>84</v>
@@ -41105,7 +41113,7 @@
         <v>84</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>869</v>
+        <v>786</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>85</v>
@@ -41120,7 +41128,7 @@
         <v>114</v>
       </c>
       <c r="AK281" t="s" s="2">
-        <v>951</v>
+        <v>84</v>
       </c>
       <c r="AL281" t="s" s="2">
         <v>84</v>
@@ -41141,10 +41149,10 @@
         <v>84</v>
       </c>
       <c r="AR281" t="s" s="2">
-        <v>870</v>
+        <v>84</v>
       </c>
       <c r="AS281" t="s" s="2">
-        <v>871</v>
+        <v>790</v>
       </c>
       <c r="AT281" t="s" s="2">
         <v>84</v>
@@ -41153,50 +41161,44 @@
         <v>84</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="C282" t="s" s="2">
-        <v>936</v>
-      </c>
+        <v>791</v>
+      </c>
+      <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E282" s="2"/>
       <c r="F282" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G282" t="s" s="2">
         <v>102</v>
       </c>
       <c r="H282" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I282" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J282" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>171</v>
+        <v>251</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>953</v>
+        <v>792</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="N282" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="O282" t="s" s="2">
-        <v>868</v>
-      </c>
+        <v>793</v>
+      </c>
+      <c r="N282" s="2"/>
+      <c r="O282" s="2"/>
       <c r="P282" t="s" s="2">
         <v>84</v>
       </c>
@@ -41220,11 +41222,13 @@
         <v>84</v>
       </c>
       <c r="X282" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y282" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="Y282" t="s" s="2">
+        <v>794</v>
+      </c>
       <c r="Z282" t="s" s="2">
-        <v>954</v>
+        <v>795</v>
       </c>
       <c r="AA282" t="s" s="2">
         <v>84</v>
@@ -41242,13 +41246,13 @@
         <v>84</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>869</v>
+        <v>791</v>
       </c>
       <c r="AG282" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH282" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI282" t="s" s="2">
         <v>84</v>
@@ -41257,7 +41261,7 @@
         <v>114</v>
       </c>
       <c r="AK282" t="s" s="2">
-        <v>84</v>
+        <v>948</v>
       </c>
       <c r="AL282" t="s" s="2">
         <v>84</v>
@@ -41278,13 +41282,13 @@
         <v>84</v>
       </c>
       <c r="AR282" t="s" s="2">
-        <v>870</v>
+        <v>84</v>
       </c>
       <c r="AS282" t="s" s="2">
-        <v>871</v>
+        <v>777</v>
       </c>
       <c r="AT282" t="s" s="2">
-        <v>84</v>
+        <v>797</v>
       </c>
       <c r="AU282" t="s" s="2">
         <v>84</v>
@@ -41292,10 +41296,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>878</v>
+        <v>868</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -41315,23 +41319,19 @@
         <v>84</v>
       </c>
       <c r="J283" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K283" t="s" s="2">
         <v>116</v>
       </c>
       <c r="L283" t="s" s="2">
-        <v>879</v>
+        <v>117</v>
       </c>
       <c r="M283" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="N283" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="O283" t="s" s="2">
-        <v>882</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N283" s="2"/>
+      <c r="O283" s="2"/>
       <c r="P283" t="s" s="2">
         <v>84</v>
       </c>
@@ -41379,7 +41379,7 @@
         <v>84</v>
       </c>
       <c r="AF283" t="s" s="2">
-        <v>883</v>
+        <v>119</v>
       </c>
       <c r="AG283" t="s" s="2">
         <v>85</v>
@@ -41391,7 +41391,7 @@
         <v>84</v>
       </c>
       <c r="AJ283" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK283" t="s" s="2">
         <v>84</v>
@@ -41415,10 +41415,10 @@
         <v>84</v>
       </c>
       <c r="AR283" t="s" s="2">
-        <v>884</v>
+        <v>84</v>
       </c>
       <c r="AS283" t="s" s="2">
-        <v>885</v>
+        <v>120</v>
       </c>
       <c r="AT283" t="s" s="2">
         <v>84</v>
@@ -41429,21 +41429,21 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>798</v>
+        <v>870</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E284" s="2"/>
       <c r="F284" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G284" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H284" t="s" s="2">
         <v>84</v>
@@ -41455,18 +41455,18 @@
         <v>84</v>
       </c>
       <c r="K284" t="s" s="2">
-        <v>271</v>
+        <v>123</v>
       </c>
       <c r="L284" t="s" s="2">
-        <v>799</v>
+        <v>124</v>
       </c>
       <c r="M284" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="N284" s="2"/>
-      <c r="O284" t="s" s="2">
-        <v>801</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="N284" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O284" s="2"/>
       <c r="P284" t="s" s="2">
         <v>84</v>
       </c>
@@ -41502,31 +41502,31 @@
         <v>84</v>
       </c>
       <c r="AB284" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC284" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD284" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE284" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF284" t="s" s="2">
-        <v>798</v>
+        <v>130</v>
       </c>
       <c r="AG284" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH284" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI284" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ284" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK284" t="s" s="2">
         <v>84</v>
@@ -41553,10 +41553,10 @@
         <v>84</v>
       </c>
       <c r="AS284" t="s" s="2">
-        <v>802</v>
+        <v>120</v>
       </c>
       <c r="AT284" t="s" s="2">
-        <v>803</v>
+        <v>84</v>
       </c>
       <c r="AU284" t="s" s="2">
         <v>84</v>
@@ -41564,10 +41564,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>889</v>
+        <v>872</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -41578,7 +41578,7 @@
         <v>85</v>
       </c>
       <c r="G285" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H285" t="s" s="2">
         <v>84</v>
@@ -41587,19 +41587,23 @@
         <v>84</v>
       </c>
       <c r="J285" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K285" t="s" s="2">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="L285" t="s" s="2">
-        <v>117</v>
+        <v>873</v>
       </c>
       <c r="M285" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N285" s="2"/>
-      <c r="O285" s="2"/>
+        <v>874</v>
+      </c>
+      <c r="N285" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="O285" t="s" s="2">
+        <v>876</v>
+      </c>
       <c r="P285" t="s" s="2">
         <v>84</v>
       </c>
@@ -41635,31 +41639,29 @@
         <v>84</v>
       </c>
       <c r="AB285" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC285" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="AC285" s="2"/>
       <c r="AD285" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE285" t="s" s="2">
-        <v>84</v>
+        <v>618</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>119</v>
+        <v>877</v>
       </c>
       <c r="AG285" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH285" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI285" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ285" t="s" s="2">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="AK285" t="s" s="2">
         <v>84</v>
@@ -41683,10 +41685,10 @@
         <v>84</v>
       </c>
       <c r="AR285" t="s" s="2">
-        <v>84</v>
+        <v>878</v>
       </c>
       <c r="AS285" t="s" s="2">
-        <v>120</v>
+        <v>879</v>
       </c>
       <c r="AT285" t="s" s="2">
         <v>84</v>
@@ -41695,46 +41697,50 @@
         <v>84</v>
       </c>
     </row>
-    <row r="286" hidden="true">
+    <row r="286">
       <c r="A286" t="s" s="2">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>891</v>
-      </c>
-      <c r="C286" s="2"/>
+        <v>872</v>
+      </c>
+      <c r="C286" t="s" s="2">
+        <v>953</v>
+      </c>
       <c r="D286" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E286" s="2"/>
       <c r="F286" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G286" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H286" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I286" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J286" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K286" t="s" s="2">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>124</v>
+        <v>954</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>125</v>
+        <v>874</v>
       </c>
       <c r="N286" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O286" s="2"/>
+        <v>875</v>
+      </c>
+      <c r="O286" t="s" s="2">
+        <v>876</v>
+      </c>
       <c r="P286" t="s" s="2">
         <v>84</v>
       </c>
@@ -41758,31 +41764,29 @@
         <v>84</v>
       </c>
       <c r="X286" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y286" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y286" s="2"/>
       <c r="Z286" t="s" s="2">
-        <v>84</v>
+        <v>955</v>
       </c>
       <c r="AA286" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB286" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC286" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD286" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE286" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>130</v>
+        <v>877</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>85</v>
@@ -41794,10 +41798,10 @@
         <v>84</v>
       </c>
       <c r="AJ286" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK286" t="s" s="2">
-        <v>84</v>
+        <v>956</v>
       </c>
       <c r="AL286" t="s" s="2">
         <v>84</v>
@@ -41818,10 +41822,10 @@
         <v>84</v>
       </c>
       <c r="AR286" t="s" s="2">
-        <v>84</v>
+        <v>878</v>
       </c>
       <c r="AS286" t="s" s="2">
-        <v>120</v>
+        <v>879</v>
       </c>
       <c r="AT286" t="s" s="2">
         <v>84</v>
@@ -41830,14 +41834,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="287" hidden="true">
+    <row r="287">
       <c r="A287" t="s" s="2">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="C287" s="2"/>
+        <v>872</v>
+      </c>
+      <c r="C287" t="s" s="2">
+        <v>941</v>
+      </c>
       <c r="D287" t="s" s="2">
         <v>84</v>
       </c>
@@ -41849,7 +41855,7 @@
         <v>102</v>
       </c>
       <c r="H287" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I287" t="s" s="2">
         <v>84</v>
@@ -41858,18 +41864,20 @@
         <v>103</v>
       </c>
       <c r="K287" t="s" s="2">
-        <v>278</v>
+        <v>171</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>280</v>
+        <v>874</v>
       </c>
       <c r="N287" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O287" s="2"/>
+        <v>875</v>
+      </c>
+      <c r="O287" t="s" s="2">
+        <v>876</v>
+      </c>
       <c r="P287" t="s" s="2">
         <v>84</v>
       </c>
@@ -41893,13 +41901,11 @@
         <v>84</v>
       </c>
       <c r="X287" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y287" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y287" s="2"/>
       <c r="Z287" t="s" s="2">
-        <v>84</v>
+        <v>959</v>
       </c>
       <c r="AA287" t="s" s="2">
         <v>84</v>
@@ -41917,22 +41923,22 @@
         <v>84</v>
       </c>
       <c r="AF287" t="s" s="2">
-        <v>282</v>
+        <v>877</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH287" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI287" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ287" t="s" s="2">
         <v>114</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>961</v>
+        <v>84</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>84</v>
@@ -41953,10 +41959,10 @@
         <v>84</v>
       </c>
       <c r="AR287" t="s" s="2">
-        <v>285</v>
+        <v>878</v>
       </c>
       <c r="AS287" t="s" s="2">
-        <v>286</v>
+        <v>879</v>
       </c>
       <c r="AT287" t="s" s="2">
         <v>84</v>
@@ -41967,10 +41973,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>897</v>
+        <v>886</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -41993,24 +41999,24 @@
         <v>103</v>
       </c>
       <c r="K288" t="s" s="2">
-        <v>278</v>
+        <v>116</v>
       </c>
       <c r="L288" t="s" s="2">
-        <v>963</v>
+        <v>887</v>
       </c>
       <c r="M288" t="s" s="2">
-        <v>290</v>
+        <v>888</v>
       </c>
       <c r="N288" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O288" s="2"/>
+        <v>889</v>
+      </c>
+      <c r="O288" t="s" s="2">
+        <v>890</v>
+      </c>
       <c r="P288" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q288" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="Q288" s="2"/>
       <c r="R288" t="s" s="2">
         <v>84</v>
       </c>
@@ -42054,7 +42060,7 @@
         <v>84</v>
       </c>
       <c r="AF288" t="s" s="2">
-        <v>293</v>
+        <v>891</v>
       </c>
       <c r="AG288" t="s" s="2">
         <v>85</v>
@@ -42063,13 +42069,13 @@
         <v>102</v>
       </c>
       <c r="AI288" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ288" t="s" s="2">
         <v>114</v>
       </c>
       <c r="AK288" t="s" s="2">
-        <v>964</v>
+        <v>84</v>
       </c>
       <c r="AL288" t="s" s="2">
         <v>84</v>
@@ -42090,10 +42096,10 @@
         <v>84</v>
       </c>
       <c r="AR288" t="s" s="2">
-        <v>295</v>
+        <v>892</v>
       </c>
       <c r="AS288" t="s" s="2">
-        <v>296</v>
+        <v>893</v>
       </c>
       <c r="AT288" t="s" s="2">
         <v>84</v>
@@ -42104,10 +42110,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -42118,7 +42124,7 @@
         <v>85</v>
       </c>
       <c r="G289" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="H289" t="s" s="2">
         <v>84</v>
@@ -42130,16 +42136,18 @@
         <v>84</v>
       </c>
       <c r="K289" t="s" s="2">
-        <v>484</v>
+        <v>271</v>
       </c>
       <c r="L289" t="s" s="2">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="M289" t="s" s="2">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="N289" s="2"/>
-      <c r="O289" s="2"/>
+      <c r="O289" t="s" s="2">
+        <v>801</v>
+      </c>
       <c r="P289" t="s" s="2">
         <v>84</v>
       </c>
@@ -42187,7 +42195,7 @@
         <v>84</v>
       </c>
       <c r="AF289" t="s" s="2">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="AG289" t="s" s="2">
         <v>85</v>
@@ -42226,21 +42234,21 @@
         <v>84</v>
       </c>
       <c r="AS289" t="s" s="2">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="AT289" t="s" s="2">
-        <v>84</v>
+        <v>803</v>
       </c>
       <c r="AU289" t="s" s="2">
         <v>84</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>966</v>
+        <v>897</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -42251,10 +42259,10 @@
         <v>85</v>
       </c>
       <c r="G290" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="H290" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I290" t="s" s="2">
         <v>84</v>
@@ -42263,20 +42271,16 @@
         <v>84</v>
       </c>
       <c r="K290" t="s" s="2">
-        <v>967</v>
+        <v>116</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>968</v>
+        <v>117</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>969</v>
-      </c>
-      <c r="N290" t="s" s="2">
-        <v>970</v>
-      </c>
-      <c r="O290" t="s" s="2">
-        <v>971</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N290" s="2"/>
+      <c r="O290" s="2"/>
       <c r="P290" t="s" s="2">
         <v>84</v>
       </c>
@@ -42300,78 +42304,755 @@
         <v>84</v>
       </c>
       <c r="X290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF290" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG290" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH290" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS290" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AT290" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU290" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="291" hidden="true">
+      <c r="A291" t="s" s="2">
+        <v>963</v>
+      </c>
+      <c r="B291" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="C291" s="2"/>
+      <c r="D291" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="E291" s="2"/>
+      <c r="F291" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G291" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K291" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L291" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M291" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="N291" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O291" s="2"/>
+      <c r="P291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q291" s="2"/>
+      <c r="R291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB291" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AC291" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AD291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE291" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AF291" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AG291" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH291" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ291" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AK291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS291" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AT291" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU291" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="292" hidden="true">
+      <c r="A292" t="s" s="2">
+        <v>964</v>
+      </c>
+      <c r="B292" t="s" s="2">
+        <v>901</v>
+      </c>
+      <c r="C292" s="2"/>
+      <c r="D292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E292" s="2"/>
+      <c r="F292" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G292" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="H292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J292" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K292" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L292" t="s" s="2">
+        <v>965</v>
+      </c>
+      <c r="M292" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N292" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O292" s="2"/>
+      <c r="P292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q292" s="2"/>
+      <c r="R292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF292" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AG292" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH292" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI292" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AJ292" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK292" t="s" s="2">
+        <v>966</v>
+      </c>
+      <c r="AL292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR292" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AS292" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AT292" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU292" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="293" hidden="true">
+      <c r="A293" t="s" s="2">
+        <v>967</v>
+      </c>
+      <c r="B293" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="C293" s="2"/>
+      <c r="D293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E293" s="2"/>
+      <c r="F293" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G293" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="H293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J293" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K293" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L293" t="s" s="2">
+        <v>968</v>
+      </c>
+      <c r="M293" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N293" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="O293" s="2"/>
+      <c r="P293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q293" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="R293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF293" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AG293" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH293" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI293" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AJ293" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK293" t="s" s="2">
+        <v>969</v>
+      </c>
+      <c r="AL293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR293" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AS293" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AT293" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU293" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="294" hidden="true">
+      <c r="A294" t="s" s="2">
+        <v>970</v>
+      </c>
+      <c r="B294" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C294" s="2"/>
+      <c r="D294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E294" s="2"/>
+      <c r="F294" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G294" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="H294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K294" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L294" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="M294" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="N294" s="2"/>
+      <c r="O294" s="2"/>
+      <c r="P294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q294" s="2"/>
+      <c r="R294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF294" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="AG294" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH294" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ294" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS294" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="AT294" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU294" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="2">
+        <v>971</v>
+      </c>
+      <c r="B295" t="s" s="2">
+        <v>971</v>
+      </c>
+      <c r="C295" s="2"/>
+      <c r="D295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E295" s="2"/>
+      <c r="F295" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G295" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H295" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K295" t="s" s="2">
+        <v>972</v>
+      </c>
+      <c r="L295" t="s" s="2">
+        <v>973</v>
+      </c>
+      <c r="M295" t="s" s="2">
+        <v>974</v>
+      </c>
+      <c r="N295" t="s" s="2">
+        <v>975</v>
+      </c>
+      <c r="O295" t="s" s="2">
+        <v>976</v>
+      </c>
+      <c r="P295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q295" s="2"/>
+      <c r="R295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X295" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="Y290" s="2"/>
-      <c r="Z290" t="s" s="2">
-        <v>972</v>
-      </c>
-      <c r="AA290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF290" t="s" s="2">
-        <v>966</v>
-      </c>
-      <c r="AG290" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH290" t="s" s="2">
+      <c r="Y295" s="2"/>
+      <c r="Z295" t="s" s="2">
+        <v>977</v>
+      </c>
+      <c r="AA295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF295" t="s" s="2">
+        <v>971</v>
+      </c>
+      <c r="AG295" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH295" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="AI290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ290" t="s" s="2">
+      <c r="AI295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ295" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AK290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ290" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR290" t="s" s="2">
-        <v>973</v>
-      </c>
-      <c r="AS290" t="s" s="2">
-        <v>974</v>
-      </c>
-      <c r="AT290" t="s" s="2">
-        <v>975</v>
-      </c>
-      <c r="AU290" t="s" s="2">
+      <c r="AK295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ295" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR295" t="s" s="2">
+        <v>978</v>
+      </c>
+      <c r="AS295" t="s" s="2">
+        <v>979</v>
+      </c>
+      <c r="AT295" t="s" s="2">
+        <v>980</v>
+      </c>
+      <c r="AU295" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AU290">
+  <autoFilter ref="A1:AU295">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -42381,7 +43062,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI289">
+  <conditionalFormatting sqref="A2:AI294">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-2</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -430,7 +430,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -729,7 +729,7 @@
     <t>as-ext-registration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-registration|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-registration|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1035,7 +1035,7 @@
     <t>as-ext-frpractitioner-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1177,7 +1177,7 @@
     <t>as-ext-smartcard</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-smartcard|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-smartcard|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1311,7 +1311,7 @@
     <t>as-ext-digital-certificate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1960,7 +1960,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-2}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2042,7 +2042,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2310,7 +2310,7 @@
     <t>Practitioner.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-2}
+    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2552,7 +2552,7 @@
     <t>as-ext-education-level</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-education-level|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-education-level|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -3023,7 +3023,7 @@
     <t>Practitioner.communication</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed|1.2.0-snapshot-2}
+    <t xml:space="preserve">CodeableConcept {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed|1.2.0-snapshot-3}
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
